--- a/Sindhi Muslim/Classes/GBPS SJCHS Student Data 2024-2025.xlsx
+++ b/Sindhi Muslim/Classes/GBPS SJCHS Student Data 2024-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E465E60-3630-4AC4-B73D-5BCF549A1822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21F35D1-949E-4382-B138-0BACB321B5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="209">
   <si>
     <t>STUDENT PROFILE 2024-2025</t>
   </si>
@@ -431,6 +431,237 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Abdullah Fattah</t>
+  </si>
+  <si>
+    <t>Manzoor Ahmed Memon</t>
+  </si>
+  <si>
+    <t>Class-5</t>
+  </si>
+  <si>
+    <t>Abdul Qayoom</t>
+  </si>
+  <si>
+    <t>Waheed Ahmed</t>
+  </si>
+  <si>
+    <t>Ahmed Ali</t>
+  </si>
+  <si>
+    <t>Nasrullah</t>
+  </si>
+  <si>
+    <t>Ahsan Raza</t>
+  </si>
+  <si>
+    <t>Meeral</t>
+  </si>
+  <si>
+    <t>Ayan Ali</t>
+  </si>
+  <si>
+    <t>Ghulam Muhammad</t>
+  </si>
+  <si>
+    <t>Pervez Hussain</t>
+  </si>
+  <si>
+    <t>Masab Ali</t>
+  </si>
+  <si>
+    <t>Meesam Abbas</t>
+  </si>
+  <si>
+    <t>Muhammad Hasan</t>
+  </si>
+  <si>
+    <t>Javed Ahmed</t>
+  </si>
+  <si>
+    <t>Muhammad Zaid</t>
+  </si>
+  <si>
+    <t>Khalid</t>
+  </si>
+  <si>
+    <t>Liaquat Ali</t>
+  </si>
+  <si>
+    <t>Muhammad Ali</t>
+  </si>
+  <si>
+    <t>Moula Bux</t>
+  </si>
+  <si>
+    <t>Muhammad Israr</t>
+  </si>
+  <si>
+    <t>Abdullah</t>
+  </si>
+  <si>
+    <t>Muhammad Raheem</t>
+  </si>
+  <si>
+    <t>Muhammad Azim</t>
+  </si>
+  <si>
+    <t>Mohsin Ali</t>
+  </si>
+  <si>
+    <t>Sajid Ali</t>
+  </si>
+  <si>
+    <t>Muhammad Amaad Uddin</t>
+  </si>
+  <si>
+    <t>Riaz</t>
+  </si>
+  <si>
+    <t>Noman</t>
+  </si>
+  <si>
+    <t>Rahib Hussain</t>
+  </si>
+  <si>
+    <t>Zahid</t>
+  </si>
+  <si>
+    <t>Shamas Din</t>
+  </si>
+  <si>
+    <t>Asghar Ali</t>
+  </si>
+  <si>
+    <t>Safdar Ali</t>
+  </si>
+  <si>
+    <t>Zohaib Ali</t>
+  </si>
+  <si>
+    <t>Faheem</t>
+  </si>
+  <si>
+    <t>Muhammad Hasnain</t>
+  </si>
+  <si>
+    <t>Ubaidullah</t>
+  </si>
+  <si>
+    <t>Aitaina</t>
+  </si>
+  <si>
+    <t>Sohail Sarwar</t>
+  </si>
+  <si>
+    <t>Ajwa</t>
+  </si>
+  <si>
+    <t>Alishba</t>
+  </si>
+  <si>
+    <t>Maqsood Ahmed</t>
+  </si>
+  <si>
+    <t>Anosha</t>
+  </si>
+  <si>
+    <t>Altaf Hussain</t>
+  </si>
+  <si>
+    <t>Dua Batool</t>
+  </si>
+  <si>
+    <t>Faiq Ali</t>
+  </si>
+  <si>
+    <t>Gulnaz</t>
+  </si>
+  <si>
+    <t>Zahid Hussain</t>
+  </si>
+  <si>
+    <t>Hina</t>
+  </si>
+  <si>
+    <t>Lutufullah</t>
+  </si>
+  <si>
+    <t>Iqra</t>
+  </si>
+  <si>
+    <t>Munawar Ali</t>
+  </si>
+  <si>
+    <t>Jawairia Batool</t>
+  </si>
+  <si>
+    <t>Imran Ali</t>
+  </si>
+  <si>
+    <t>Khadija Bibi</t>
+  </si>
+  <si>
+    <t>Laiba</t>
+  </si>
+  <si>
+    <t>Amjad Hussain</t>
+  </si>
+  <si>
+    <t>Maheen Nisa</t>
+  </si>
+  <si>
+    <t>Muhammad Maroof</t>
+  </si>
+  <si>
+    <t>Murk Fatima</t>
+  </si>
+  <si>
+    <t>Nayab</t>
+  </si>
+  <si>
+    <t>Sidra Bibi</t>
+  </si>
+  <si>
+    <t>Sidra Tul Muntaha</t>
+  </si>
+  <si>
+    <t>Sundas</t>
+  </si>
+  <si>
+    <t>Imran Qamar</t>
+  </si>
+  <si>
+    <t>Tayyaba Fatima</t>
+  </si>
+  <si>
+    <t>Urooj</t>
+  </si>
+  <si>
+    <t>Muhammad Khan</t>
+  </si>
+  <si>
+    <t>Zahra Batool</t>
+  </si>
+  <si>
+    <t>Zainab Bibi</t>
+  </si>
+  <si>
+    <t>Bakhshal Ali</t>
+  </si>
+  <si>
+    <t>Inshra</t>
+  </si>
+  <si>
+    <t>Abdul Albar</t>
+  </si>
+  <si>
+    <t>Rukhsana</t>
+  </si>
+  <si>
+    <t>Muhammad Sultan</t>
   </si>
 </sst>
 </file>
@@ -440,12 +671,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -692,68 +930,69 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1348,7 +1587,7 @@
     <col min="1" max="1" width="5.140625" style="17" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" style="17" customWidth="1"/>
     <col min="3" max="3" width="5.42578125" style="17" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" style="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.140625" style="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.140625" style="17" customWidth="1"/>
     <col min="7" max="7" width="7.140625" style="17" bestFit="1" customWidth="1"/>
@@ -3275,13 +3514,25 @@
       </c>
     </row>
     <row r="56" spans="1:14" ht="15.75">
-      <c r="A56" s="14"/>
-      <c r="B56" s="36"/>
+      <c r="A56" s="14">
+        <v>54</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C56" s="15"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="14"/>
+      <c r="D56" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F56" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G56" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H56" s="16"/>
       <c r="I56" s="15"/>
       <c r="J56" s="14"/>
@@ -3291,13 +3542,25 @@
       <c r="N56" s="7"/>
     </row>
     <row r="57" spans="1:14" ht="15.75">
-      <c r="A57" s="14"/>
-      <c r="B57" s="14"/>
+      <c r="A57" s="14">
+        <v>55</v>
+      </c>
+      <c r="B57" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C57" s="15"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
+      <c r="D57" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F57" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G57" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H57" s="16"/>
       <c r="I57" s="15"/>
       <c r="J57" s="14"/>
@@ -3307,13 +3570,25 @@
       <c r="N57" s="7"/>
     </row>
     <row r="58" spans="1:14" ht="15.75">
-      <c r="A58" s="14"/>
-      <c r="B58" s="14"/>
+      <c r="A58" s="14">
+        <v>56</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C58" s="15"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
+      <c r="D58" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F58" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G58" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H58" s="16"/>
       <c r="I58" s="15"/>
       <c r="J58" s="14"/>
@@ -3323,13 +3598,25 @@
       <c r="N58" s="14"/>
     </row>
     <row r="59" spans="1:14" ht="15.75">
-      <c r="A59" s="14"/>
-      <c r="B59" s="14"/>
+      <c r="A59" s="14">
+        <v>57</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C59" s="15"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
+      <c r="D59" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F59" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G59" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H59" s="16"/>
       <c r="I59" s="15"/>
       <c r="J59" s="14"/>
@@ -3339,13 +3626,25 @@
       <c r="N59" s="7"/>
     </row>
     <row r="60" spans="1:14" ht="15.75">
-      <c r="A60" s="14"/>
-      <c r="B60" s="14"/>
+      <c r="A60" s="14">
+        <v>58</v>
+      </c>
+      <c r="B60" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C60" s="15"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
+      <c r="D60" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F60" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G60" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H60" s="16"/>
       <c r="I60" s="15"/>
       <c r="J60" s="14"/>
@@ -3355,13 +3654,25 @@
       <c r="N60" s="14"/>
     </row>
     <row r="61" spans="1:14" ht="15.75">
-      <c r="A61" s="14"/>
-      <c r="B61" s="14"/>
+      <c r="A61" s="14">
+        <v>59</v>
+      </c>
+      <c r="B61" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C61" s="15"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
+      <c r="D61" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F61" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G61" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H61" s="5"/>
       <c r="I61" s="15"/>
       <c r="J61" s="14"/>
@@ -3371,13 +3682,25 @@
       <c r="N61" s="7"/>
     </row>
     <row r="62" spans="1:14" ht="15.75">
-      <c r="A62" s="14"/>
-      <c r="B62" s="14"/>
+      <c r="A62" s="14">
+        <v>60</v>
+      </c>
+      <c r="B62" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C62" s="15"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
+      <c r="D62" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F62" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G62" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H62" s="16"/>
       <c r="I62" s="15"/>
       <c r="J62" s="14"/>
@@ -3387,13 +3710,25 @@
       <c r="N62" s="7"/>
     </row>
     <row r="63" spans="1:14" ht="15.75">
-      <c r="A63" s="14"/>
-      <c r="B63" s="14"/>
+      <c r="A63" s="14">
+        <v>61</v>
+      </c>
+      <c r="B63" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C63" s="15"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
+      <c r="D63" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F63" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G63" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H63" s="16"/>
       <c r="I63" s="15"/>
       <c r="J63" s="14"/>
@@ -3403,13 +3738,25 @@
       <c r="N63" s="14"/>
     </row>
     <row r="64" spans="1:14" ht="15.75">
-      <c r="A64" s="14"/>
-      <c r="B64" s="14"/>
+      <c r="A64" s="14">
+        <v>62</v>
+      </c>
+      <c r="B64" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C64" s="15"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
+      <c r="D64" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F64" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G64" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H64" s="16"/>
       <c r="I64" s="15"/>
       <c r="J64" s="14"/>
@@ -3419,13 +3766,25 @@
       <c r="N64" s="14"/>
     </row>
     <row r="65" spans="1:14" ht="15.75">
-      <c r="A65" s="14"/>
-      <c r="B65" s="14"/>
+      <c r="A65" s="14">
+        <v>63</v>
+      </c>
+      <c r="B65" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C65" s="15"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
+      <c r="D65" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F65" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G65" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H65" s="16"/>
       <c r="I65" s="15"/>
       <c r="J65" s="14"/>
@@ -3435,13 +3794,25 @@
       <c r="N65" s="7"/>
     </row>
     <row r="66" spans="1:14" ht="15.75">
-      <c r="A66" s="14"/>
-      <c r="B66" s="14"/>
+      <c r="A66" s="14">
+        <v>64</v>
+      </c>
+      <c r="B66" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C66" s="15"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
+      <c r="D66" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="F66" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G66" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H66" s="16"/>
       <c r="I66" s="15"/>
       <c r="J66" s="14"/>
@@ -3451,13 +3822,25 @@
       <c r="N66" s="7"/>
     </row>
     <row r="67" spans="1:14" ht="15.75">
-      <c r="A67" s="14"/>
-      <c r="B67" s="14"/>
+      <c r="A67" s="14">
+        <v>65</v>
+      </c>
+      <c r="B67" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C67" s="15"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
+      <c r="D67" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="F67" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G67" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H67" s="16"/>
       <c r="I67" s="15"/>
       <c r="J67" s="14"/>
@@ -3467,13 +3850,25 @@
       <c r="N67" s="7"/>
     </row>
     <row r="68" spans="1:14" ht="15.75">
-      <c r="A68" s="14"/>
-      <c r="B68" s="14"/>
+      <c r="A68" s="14">
+        <v>66</v>
+      </c>
+      <c r="B68" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C68" s="15"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
+      <c r="D68" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F68" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G68" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H68" s="16"/>
       <c r="I68" s="15"/>
       <c r="J68" s="14"/>
@@ -3483,13 +3878,25 @@
       <c r="N68" s="7"/>
     </row>
     <row r="69" spans="1:14" ht="15.75">
-      <c r="A69" s="14"/>
-      <c r="B69" s="14"/>
+      <c r="A69" s="14">
+        <v>67</v>
+      </c>
+      <c r="B69" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C69" s="15"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
+      <c r="D69" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="F69" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G69" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H69" s="16"/>
       <c r="I69" s="15"/>
       <c r="J69" s="14"/>
@@ -3499,13 +3906,25 @@
       <c r="N69" s="7"/>
     </row>
     <row r="70" spans="1:14" ht="15.75">
-      <c r="A70" s="14"/>
-      <c r="B70" s="14"/>
+      <c r="A70" s="14">
+        <v>68</v>
+      </c>
+      <c r="B70" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C70" s="15"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
+      <c r="D70" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F70" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G70" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H70" s="16"/>
       <c r="I70" s="15"/>
       <c r="J70" s="14"/>
@@ -3515,13 +3934,25 @@
       <c r="N70" s="14"/>
     </row>
     <row r="71" spans="1:14" ht="15.75">
-      <c r="A71" s="14"/>
-      <c r="B71" s="14"/>
+      <c r="A71" s="14">
+        <v>69</v>
+      </c>
+      <c r="B71" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C71" s="15"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
+      <c r="D71" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F71" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G71" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H71" s="16"/>
       <c r="I71" s="15"/>
       <c r="J71" s="14"/>
@@ -3531,13 +3962,25 @@
       <c r="N71" s="7"/>
     </row>
     <row r="72" spans="1:14" ht="15.75">
-      <c r="A72" s="14"/>
-      <c r="B72" s="14"/>
+      <c r="A72" s="14">
+        <v>70</v>
+      </c>
+      <c r="B72" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C72" s="15"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
+      <c r="D72" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F72" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G72" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H72" s="16"/>
       <c r="I72" s="15"/>
       <c r="J72" s="14"/>
@@ -3547,13 +3990,25 @@
       <c r="N72" s="7"/>
     </row>
     <row r="73" spans="1:14" ht="15.75">
-      <c r="A73" s="14"/>
-      <c r="B73" s="14"/>
+      <c r="A73" s="14">
+        <v>71</v>
+      </c>
+      <c r="B73" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C73" s="15"/>
-      <c r="D73" s="12"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
+      <c r="D73" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F73" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G73" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H73" s="16"/>
       <c r="I73" s="15"/>
       <c r="J73" s="14"/>
@@ -3563,13 +4018,25 @@
       <c r="N73" s="7"/>
     </row>
     <row r="74" spans="1:14" ht="15.75">
-      <c r="A74" s="14"/>
-      <c r="B74" s="14"/>
+      <c r="A74" s="14">
+        <v>72</v>
+      </c>
+      <c r="B74" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C74" s="15"/>
-      <c r="D74" s="12"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
+      <c r="D74" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="F74" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G74" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H74" s="16"/>
       <c r="I74" s="15"/>
       <c r="J74" s="14"/>
@@ -3579,13 +4046,25 @@
       <c r="N74" s="7"/>
     </row>
     <row r="75" spans="1:14" ht="15.75">
-      <c r="A75" s="14"/>
-      <c r="B75" s="14"/>
+      <c r="A75" s="14">
+        <v>73</v>
+      </c>
+      <c r="B75" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C75" s="15"/>
-      <c r="D75" s="12"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
+      <c r="D75" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F75" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G75" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H75" s="16"/>
       <c r="I75" s="15"/>
       <c r="J75" s="14"/>
@@ -3595,13 +4074,25 @@
       <c r="N75" s="7"/>
     </row>
     <row r="76" spans="1:14" ht="15.75">
-      <c r="A76" s="14"/>
-      <c r="B76" s="14"/>
+      <c r="A76" s="14">
+        <v>74</v>
+      </c>
+      <c r="B76" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C76" s="15"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
+      <c r="D76" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G76" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H76" s="16"/>
       <c r="I76" s="15"/>
       <c r="J76" s="14"/>
@@ -3611,13 +4102,25 @@
       <c r="N76" s="7"/>
     </row>
     <row r="77" spans="1:14" ht="15.75">
-      <c r="A77" s="14"/>
-      <c r="B77" s="14"/>
+      <c r="A77" s="14">
+        <v>75</v>
+      </c>
+      <c r="B77" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C77" s="15"/>
-      <c r="D77" s="12"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
+      <c r="D77" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F77" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G77" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H77" s="16"/>
       <c r="I77" s="15"/>
       <c r="J77" s="14"/>
@@ -3627,13 +4130,25 @@
       <c r="N77" s="7"/>
     </row>
     <row r="78" spans="1:14" ht="15.75">
-      <c r="A78" s="14"/>
-      <c r="B78" s="14"/>
+      <c r="A78" s="14">
+        <v>76</v>
+      </c>
+      <c r="B78" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C78" s="15"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
+      <c r="D78" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F78" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G78" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H78" s="16"/>
       <c r="I78" s="15"/>
       <c r="J78" s="14"/>
@@ -3643,13 +4158,25 @@
       <c r="N78" s="7"/>
     </row>
     <row r="79" spans="1:14" ht="15.75">
-      <c r="A79" s="14"/>
-      <c r="B79" s="14"/>
+      <c r="A79" s="14">
+        <v>77</v>
+      </c>
+      <c r="B79" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C79" s="15"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
+      <c r="D79" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F79" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G79" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H79" s="16"/>
       <c r="I79" s="15"/>
       <c r="J79" s="14"/>
@@ -3659,13 +4186,25 @@
       <c r="N79" s="7"/>
     </row>
     <row r="80" spans="1:14" ht="15.75">
-      <c r="A80" s="14"/>
-      <c r="B80" s="14"/>
+      <c r="A80" s="14">
+        <v>78</v>
+      </c>
+      <c r="B80" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C80" s="15"/>
-      <c r="D80" s="12"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
+      <c r="D80" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F80" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G80" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H80" s="5"/>
       <c r="I80" s="15"/>
       <c r="J80" s="14"/>
@@ -3675,13 +4214,25 @@
       <c r="N80" s="7"/>
     </row>
     <row r="81" spans="1:14" ht="15.75">
-      <c r="A81" s="14"/>
-      <c r="B81" s="14"/>
+      <c r="A81" s="14">
+        <v>79</v>
+      </c>
+      <c r="B81" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C81" s="15"/>
-      <c r="D81" s="12"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
+      <c r="D81" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F81" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G81" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H81" s="16"/>
       <c r="I81" s="15"/>
       <c r="J81" s="14"/>
@@ -3691,13 +4242,25 @@
       <c r="N81" s="7"/>
     </row>
     <row r="82" spans="1:14" ht="15.75">
-      <c r="A82" s="14"/>
-      <c r="B82" s="14"/>
+      <c r="A82" s="14">
+        <v>80</v>
+      </c>
+      <c r="B82" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C82" s="15"/>
-      <c r="D82" s="12"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
+      <c r="D82" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F82" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G82" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H82" s="16"/>
       <c r="I82" s="15"/>
       <c r="J82" s="14"/>
@@ -3707,13 +4270,25 @@
       <c r="N82" s="7"/>
     </row>
     <row r="83" spans="1:14" ht="15.75">
-      <c r="A83" s="14"/>
-      <c r="B83" s="14"/>
+      <c r="A83" s="14">
+        <v>81</v>
+      </c>
+      <c r="B83" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C83" s="15"/>
-      <c r="D83" s="12"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
+      <c r="D83" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="F83" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G83" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H83" s="16"/>
       <c r="I83" s="15"/>
       <c r="J83" s="14"/>
@@ -3723,13 +4298,25 @@
       <c r="N83" s="7"/>
     </row>
     <row r="84" spans="1:14" ht="15.75">
-      <c r="A84" s="14"/>
-      <c r="B84" s="14"/>
+      <c r="A84" s="14">
+        <v>82</v>
+      </c>
+      <c r="B84" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C84" s="22"/>
-      <c r="D84" s="23"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
+      <c r="D84" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="E84" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="F84" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G84" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H84" s="16"/>
       <c r="I84" s="15"/>
       <c r="J84" s="14"/>
@@ -3739,13 +4326,25 @@
       <c r="N84" s="7"/>
     </row>
     <row r="85" spans="1:14" ht="15.75">
-      <c r="A85" s="14"/>
-      <c r="B85" s="14"/>
+      <c r="A85" s="14">
+        <v>83</v>
+      </c>
+      <c r="B85" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C85" s="15"/>
-      <c r="D85" s="12"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
+      <c r="D85" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="F85" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G85" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H85" s="16"/>
       <c r="I85" s="15"/>
       <c r="J85" s="14"/>
@@ -3755,13 +4354,25 @@
       <c r="N85" s="14"/>
     </row>
     <row r="86" spans="1:14" ht="15.75">
-      <c r="A86" s="14"/>
-      <c r="B86" s="14"/>
+      <c r="A86" s="14">
+        <v>84</v>
+      </c>
+      <c r="B86" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C86" s="15"/>
-      <c r="D86" s="12"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
+      <c r="D86" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F86" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G86" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H86" s="16"/>
       <c r="I86" s="15"/>
       <c r="J86" s="14"/>
@@ -3771,13 +4382,25 @@
       <c r="N86" s="14"/>
     </row>
     <row r="87" spans="1:14" ht="15.75">
-      <c r="A87" s="14"/>
-      <c r="B87" s="14"/>
+      <c r="A87" s="14">
+        <v>85</v>
+      </c>
+      <c r="B87" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C87" s="15"/>
-      <c r="D87" s="12"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
+      <c r="D87" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="F87" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G87" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H87" s="16"/>
       <c r="I87" s="15"/>
       <c r="J87" s="14"/>
@@ -3787,13 +4410,25 @@
       <c r="N87" s="7"/>
     </row>
     <row r="88" spans="1:14" ht="15.75">
-      <c r="A88" s="14"/>
-      <c r="B88" s="14"/>
+      <c r="A88" s="14">
+        <v>86</v>
+      </c>
+      <c r="B88" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C88" s="15"/>
-      <c r="D88" s="12"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
+      <c r="D88" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F88" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G88" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H88" s="16"/>
       <c r="I88" s="15"/>
       <c r="J88" s="14"/>
@@ -3803,13 +4438,25 @@
       <c r="N88" s="14"/>
     </row>
     <row r="89" spans="1:14" ht="15.75">
-      <c r="A89" s="14"/>
-      <c r="B89" s="14"/>
+      <c r="A89" s="14">
+        <v>87</v>
+      </c>
+      <c r="B89" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C89" s="15"/>
-      <c r="D89" s="12"/>
-      <c r="E89" s="13"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="14"/>
+      <c r="D89" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="F89" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G89" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H89" s="16"/>
       <c r="I89" s="15"/>
       <c r="J89" s="14"/>
@@ -3819,13 +4466,25 @@
       <c r="N89" s="14"/>
     </row>
     <row r="90" spans="1:14" ht="15.75">
-      <c r="A90" s="14"/>
-      <c r="B90" s="14"/>
+      <c r="A90" s="14">
+        <v>88</v>
+      </c>
+      <c r="B90" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C90" s="15"/>
-      <c r="D90" s="12"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
+      <c r="D90" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="F90" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G90" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H90" s="16"/>
       <c r="I90" s="15"/>
       <c r="J90" s="14"/>
@@ -3835,13 +4494,25 @@
       <c r="N90" s="7"/>
     </row>
     <row r="91" spans="1:14" ht="15.75">
-      <c r="A91" s="14"/>
-      <c r="B91" s="14"/>
+      <c r="A91" s="14">
+        <v>89</v>
+      </c>
+      <c r="B91" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C91" s="15"/>
-      <c r="D91" s="12"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="14"/>
+      <c r="D91" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F91" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G91" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H91" s="16"/>
       <c r="I91" s="15"/>
       <c r="J91" s="14"/>
@@ -3851,13 +4522,25 @@
       <c r="N91" s="7"/>
     </row>
     <row r="92" spans="1:14" ht="15.75">
-      <c r="A92" s="14"/>
-      <c r="B92" s="14"/>
+      <c r="A92" s="14">
+        <v>90</v>
+      </c>
+      <c r="B92" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C92" s="15"/>
-      <c r="D92" s="12"/>
-      <c r="E92" s="13"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="14"/>
+      <c r="D92" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F92" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G92" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H92" s="16"/>
       <c r="I92" s="15"/>
       <c r="J92" s="14"/>
@@ -3867,13 +4550,25 @@
       <c r="N92" s="14"/>
     </row>
     <row r="93" spans="1:14" ht="15.75">
-      <c r="A93" s="14"/>
-      <c r="B93" s="14"/>
+      <c r="A93" s="14">
+        <v>91</v>
+      </c>
+      <c r="B93" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C93" s="15"/>
-      <c r="D93" s="12"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="14"/>
-      <c r="G93" s="14"/>
+      <c r="D93" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F93" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G93" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H93" s="16"/>
       <c r="I93" s="15"/>
       <c r="J93" s="14"/>
@@ -3883,13 +4578,25 @@
       <c r="N93" s="7"/>
     </row>
     <row r="94" spans="1:14" ht="15.75">
-      <c r="A94" s="14"/>
-      <c r="B94" s="14"/>
+      <c r="A94" s="14">
+        <v>92</v>
+      </c>
+      <c r="B94" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C94" s="15"/>
-      <c r="D94" s="12"/>
-      <c r="E94" s="13"/>
-      <c r="F94" s="14"/>
-      <c r="G94" s="14"/>
+      <c r="D94" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="F94" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G94" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H94" s="16"/>
       <c r="I94" s="15"/>
       <c r="J94" s="14"/>
@@ -3899,13 +4606,25 @@
       <c r="N94" s="7"/>
     </row>
     <row r="95" spans="1:14" ht="15.75">
-      <c r="A95" s="14"/>
-      <c r="B95" s="14"/>
+      <c r="A95" s="14">
+        <v>93</v>
+      </c>
+      <c r="B95" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C95" s="15"/>
-      <c r="D95" s="12"/>
-      <c r="E95" s="13"/>
-      <c r="F95" s="14"/>
-      <c r="G95" s="14"/>
+      <c r="D95" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F95" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G95" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H95" s="16"/>
       <c r="I95" s="15"/>
       <c r="J95" s="14"/>
@@ -3915,13 +4634,25 @@
       <c r="N95" s="7"/>
     </row>
     <row r="96" spans="1:14" ht="15.75">
-      <c r="A96" s="14"/>
-      <c r="B96" s="14"/>
+      <c r="A96" s="14">
+        <v>94</v>
+      </c>
+      <c r="B96" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C96" s="15"/>
-      <c r="D96" s="12"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="14"/>
-      <c r="G96" s="14"/>
+      <c r="D96" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F96" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G96" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H96" s="16"/>
       <c r="I96" s="15"/>
       <c r="J96" s="14"/>
@@ -3931,13 +4662,25 @@
       <c r="N96" s="14"/>
     </row>
     <row r="97" spans="1:14" ht="15.75">
-      <c r="A97" s="14"/>
-      <c r="B97" s="14"/>
+      <c r="A97" s="14">
+        <v>95</v>
+      </c>
+      <c r="B97" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C97" s="15"/>
-      <c r="D97" s="12"/>
-      <c r="E97" s="13"/>
-      <c r="F97" s="14"/>
-      <c r="G97" s="14"/>
+      <c r="D97" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="F97" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G97" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H97" s="16"/>
       <c r="I97" s="15"/>
       <c r="J97" s="14"/>
@@ -3947,13 +4690,25 @@
       <c r="N97" s="7"/>
     </row>
     <row r="98" spans="1:14" ht="15.75">
-      <c r="A98" s="14"/>
-      <c r="B98" s="14"/>
+      <c r="A98" s="14">
+        <v>96</v>
+      </c>
+      <c r="B98" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C98" s="15"/>
-      <c r="D98" s="12"/>
-      <c r="E98" s="13"/>
-      <c r="F98" s="14"/>
-      <c r="G98" s="14"/>
+      <c r="D98" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="F98" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G98" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H98" s="16"/>
       <c r="I98" s="15"/>
       <c r="J98" s="14"/>
@@ -3963,13 +4718,25 @@
       <c r="N98" s="14"/>
     </row>
     <row r="99" spans="1:14" ht="15.75">
-      <c r="A99" s="14"/>
-      <c r="B99" s="14"/>
+      <c r="A99" s="14">
+        <v>97</v>
+      </c>
+      <c r="B99" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C99" s="15"/>
-      <c r="D99" s="12"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="14"/>
-      <c r="G99" s="14"/>
+      <c r="D99" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F99" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G99" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H99" s="16"/>
       <c r="I99" s="15"/>
       <c r="J99" s="14"/>
@@ -3979,13 +4746,25 @@
       <c r="N99" s="7"/>
     </row>
     <row r="100" spans="1:14" ht="15.75">
-      <c r="A100" s="14"/>
-      <c r="B100" s="14"/>
+      <c r="A100" s="14">
+        <v>98</v>
+      </c>
+      <c r="B100" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C100" s="15"/>
-      <c r="D100" s="12"/>
-      <c r="E100" s="13"/>
-      <c r="F100" s="14"/>
-      <c r="G100" s="14"/>
+      <c r="D100" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="F100" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G100" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H100" s="16"/>
       <c r="I100" s="15"/>
       <c r="J100" s="14"/>
@@ -3995,13 +4774,25 @@
       <c r="N100" s="7"/>
     </row>
     <row r="101" spans="1:14" ht="15.75">
-      <c r="A101" s="14"/>
-      <c r="B101" s="14"/>
+      <c r="A101" s="14">
+        <v>99</v>
+      </c>
+      <c r="B101" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C101" s="15"/>
-      <c r="D101" s="12"/>
-      <c r="E101" s="13"/>
-      <c r="F101" s="14"/>
-      <c r="G101" s="14"/>
+      <c r="D101" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="F101" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G101" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H101" s="16"/>
       <c r="I101" s="15"/>
       <c r="J101" s="14"/>
@@ -4011,13 +4802,21 @@
       <c r="N101" s="7"/>
     </row>
     <row r="102" spans="1:14" ht="15.75">
-      <c r="A102" s="14"/>
-      <c r="B102" s="14"/>
+      <c r="A102" s="14">
+        <v>100</v>
+      </c>
+      <c r="B102" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C102" s="15"/>
       <c r="D102" s="12"/>
       <c r="E102" s="13"/>
-      <c r="F102" s="14"/>
-      <c r="G102" s="14"/>
+      <c r="F102" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G102" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H102" s="16"/>
       <c r="I102" s="15"/>
       <c r="J102" s="14"/>
@@ -4027,13 +4826,21 @@
       <c r="N102" s="14"/>
     </row>
     <row r="103" spans="1:14" ht="15.75">
-      <c r="A103" s="14"/>
-      <c r="B103" s="14"/>
+      <c r="A103" s="14">
+        <v>101</v>
+      </c>
+      <c r="B103" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C103" s="15"/>
       <c r="D103" s="12"/>
       <c r="E103" s="13"/>
-      <c r="F103" s="14"/>
-      <c r="G103" s="14"/>
+      <c r="F103" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G103" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H103" s="16"/>
       <c r="I103" s="15"/>
       <c r="J103" s="14"/>
@@ -4043,13 +4850,21 @@
       <c r="N103" s="7"/>
     </row>
     <row r="104" spans="1:14" ht="15.75">
-      <c r="A104" s="14"/>
-      <c r="B104" s="14"/>
+      <c r="A104" s="14">
+        <v>102</v>
+      </c>
+      <c r="B104" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C104" s="15"/>
       <c r="D104" s="12"/>
       <c r="E104" s="13"/>
-      <c r="F104" s="14"/>
-      <c r="G104" s="14"/>
+      <c r="F104" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G104" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H104" s="16"/>
       <c r="I104" s="15"/>
       <c r="J104" s="14"/>
@@ -4059,13 +4874,21 @@
       <c r="N104" s="14"/>
     </row>
     <row r="105" spans="1:14" ht="15.75">
-      <c r="A105" s="14"/>
-      <c r="B105" s="14"/>
+      <c r="A105" s="14">
+        <v>103</v>
+      </c>
+      <c r="B105" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C105" s="15"/>
       <c r="D105" s="12"/>
       <c r="E105" s="13"/>
-      <c r="F105" s="14"/>
-      <c r="G105" s="14"/>
+      <c r="F105" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G105" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H105" s="16"/>
       <c r="I105" s="15"/>
       <c r="J105" s="14"/>
@@ -4075,13 +4898,21 @@
       <c r="N105" s="7"/>
     </row>
     <row r="106" spans="1:14" ht="15.75">
-      <c r="A106" s="14"/>
-      <c r="B106" s="14"/>
+      <c r="A106" s="14">
+        <v>104</v>
+      </c>
+      <c r="B106" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C106" s="15"/>
       <c r="D106" s="12"/>
       <c r="E106" s="13"/>
-      <c r="F106" s="14"/>
-      <c r="G106" s="14"/>
+      <c r="F106" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G106" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H106" s="16"/>
       <c r="I106" s="15"/>
       <c r="J106" s="14"/>
@@ -4091,13 +4922,21 @@
       <c r="N106" s="14"/>
     </row>
     <row r="107" spans="1:14" ht="15.75">
-      <c r="A107" s="14"/>
-      <c r="B107" s="14"/>
+      <c r="A107" s="14">
+        <v>105</v>
+      </c>
+      <c r="B107" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C107" s="15"/>
       <c r="D107" s="12"/>
       <c r="E107" s="13"/>
-      <c r="F107" s="14"/>
-      <c r="G107" s="14"/>
+      <c r="F107" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G107" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H107" s="16"/>
       <c r="I107" s="15"/>
       <c r="J107" s="14"/>
@@ -4107,13 +4946,21 @@
       <c r="N107" s="7"/>
     </row>
     <row r="108" spans="1:14" ht="15.75">
-      <c r="A108" s="14"/>
-      <c r="B108" s="14"/>
+      <c r="A108" s="14">
+        <v>106</v>
+      </c>
+      <c r="B108" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C108" s="15"/>
       <c r="D108" s="12"/>
       <c r="E108" s="13"/>
-      <c r="F108" s="14"/>
-      <c r="G108" s="14"/>
+      <c r="F108" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G108" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H108" s="16"/>
       <c r="I108" s="15"/>
       <c r="J108" s="14"/>
@@ -4123,13 +4970,21 @@
       <c r="N108" s="7"/>
     </row>
     <row r="109" spans="1:14" ht="15.75">
-      <c r="A109" s="14"/>
-      <c r="B109" s="14"/>
+      <c r="A109" s="14">
+        <v>107</v>
+      </c>
+      <c r="B109" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C109" s="22"/>
       <c r="D109" s="12"/>
       <c r="E109" s="13"/>
-      <c r="F109" s="14"/>
-      <c r="G109" s="14"/>
+      <c r="F109" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G109" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H109" s="16"/>
       <c r="I109" s="15"/>
       <c r="J109" s="14"/>
@@ -4139,13 +4994,21 @@
       <c r="N109" s="7"/>
     </row>
     <row r="110" spans="1:14" ht="15.75">
-      <c r="A110" s="14"/>
-      <c r="B110" s="14"/>
+      <c r="A110" s="14">
+        <v>108</v>
+      </c>
+      <c r="B110" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C110" s="15"/>
       <c r="D110" s="12"/>
       <c r="E110" s="13"/>
-      <c r="F110" s="14"/>
-      <c r="G110" s="14"/>
+      <c r="F110" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G110" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H110" s="5"/>
       <c r="I110" s="15"/>
       <c r="J110" s="14"/>
@@ -4155,13 +5018,21 @@
       <c r="N110" s="7"/>
     </row>
     <row r="111" spans="1:14" ht="15.75">
-      <c r="A111" s="14"/>
-      <c r="B111" s="14"/>
+      <c r="A111" s="14">
+        <v>109</v>
+      </c>
+      <c r="B111" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C111" s="15"/>
       <c r="D111" s="12"/>
       <c r="E111" s="13"/>
-      <c r="F111" s="14"/>
-      <c r="G111" s="14"/>
+      <c r="F111" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G111" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H111" s="16"/>
       <c r="I111" s="15"/>
       <c r="J111" s="14"/>
@@ -4171,13 +5042,21 @@
       <c r="N111" s="7"/>
     </row>
     <row r="112" spans="1:14" ht="15.75">
-      <c r="A112" s="14"/>
-      <c r="B112" s="14"/>
+      <c r="A112" s="14">
+        <v>110</v>
+      </c>
+      <c r="B112" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C112" s="15"/>
       <c r="D112" s="12"/>
       <c r="E112" s="13"/>
-      <c r="F112" s="14"/>
-      <c r="G112" s="14"/>
+      <c r="F112" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G112" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H112" s="16"/>
       <c r="I112" s="15"/>
       <c r="J112" s="14"/>
@@ -4187,13 +5066,21 @@
       <c r="N112" s="7"/>
     </row>
     <row r="113" spans="1:14" ht="15.75">
-      <c r="A113" s="14"/>
-      <c r="B113" s="14"/>
+      <c r="A113" s="14">
+        <v>111</v>
+      </c>
+      <c r="B113" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C113" s="15"/>
       <c r="D113" s="12"/>
       <c r="E113" s="13"/>
-      <c r="F113" s="14"/>
-      <c r="G113" s="14"/>
+      <c r="F113" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G113" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H113" s="16"/>
       <c r="I113" s="15"/>
       <c r="J113" s="14"/>
@@ -4203,13 +5090,21 @@
       <c r="N113" s="14"/>
     </row>
     <row r="114" spans="1:14" ht="15.75">
-      <c r="A114" s="14"/>
-      <c r="B114" s="14"/>
+      <c r="A114" s="14">
+        <v>112</v>
+      </c>
+      <c r="B114" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C114" s="15"/>
       <c r="D114" s="12"/>
       <c r="E114" s="13"/>
-      <c r="F114" s="14"/>
-      <c r="G114" s="14"/>
+      <c r="F114" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G114" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H114" s="16"/>
       <c r="I114" s="15"/>
       <c r="J114" s="14"/>
@@ -4219,13 +5114,21 @@
       <c r="N114" s="7"/>
     </row>
     <row r="115" spans="1:14" ht="15.75">
-      <c r="A115" s="14"/>
-      <c r="B115" s="14"/>
+      <c r="A115" s="14">
+        <v>113</v>
+      </c>
+      <c r="B115" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C115" s="15"/>
       <c r="D115" s="12"/>
       <c r="E115" s="13"/>
-      <c r="F115" s="14"/>
-      <c r="G115" s="14"/>
+      <c r="F115" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G115" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H115" s="16"/>
       <c r="I115" s="15"/>
       <c r="J115" s="14"/>
@@ -4235,13 +5138,21 @@
       <c r="N115" s="14"/>
     </row>
     <row r="116" spans="1:14" ht="15.75">
-      <c r="A116" s="14"/>
-      <c r="B116" s="14"/>
+      <c r="A116" s="14">
+        <v>114</v>
+      </c>
+      <c r="B116" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C116" s="15"/>
       <c r="D116" s="12"/>
       <c r="E116" s="13"/>
-      <c r="F116" s="14"/>
-      <c r="G116" s="14"/>
+      <c r="F116" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G116" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H116" s="16"/>
       <c r="I116" s="15"/>
       <c r="J116" s="14"/>
@@ -4251,13 +5162,21 @@
       <c r="N116" s="7"/>
     </row>
     <row r="117" spans="1:14" ht="15.75">
-      <c r="A117" s="14"/>
-      <c r="B117" s="14"/>
+      <c r="A117" s="14">
+        <v>115</v>
+      </c>
+      <c r="B117" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C117" s="15"/>
       <c r="D117" s="12"/>
       <c r="E117" s="13"/>
-      <c r="F117" s="14"/>
-      <c r="G117" s="14"/>
+      <c r="F117" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G117" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H117" s="16"/>
       <c r="I117" s="15"/>
       <c r="J117" s="14"/>
@@ -4267,13 +5186,21 @@
       <c r="N117" s="7"/>
     </row>
     <row r="118" spans="1:14" ht="15.75">
-      <c r="A118" s="14"/>
-      <c r="B118" s="14"/>
+      <c r="A118" s="14">
+        <v>116</v>
+      </c>
+      <c r="B118" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C118" s="15"/>
       <c r="D118" s="12"/>
       <c r="E118" s="13"/>
-      <c r="F118" s="14"/>
-      <c r="G118" s="14"/>
+      <c r="F118" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G118" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H118" s="16"/>
       <c r="I118" s="15"/>
       <c r="J118" s="14"/>
@@ -4283,13 +5210,21 @@
       <c r="N118" s="7"/>
     </row>
     <row r="119" spans="1:14" ht="15.75">
-      <c r="A119" s="14"/>
-      <c r="B119" s="14"/>
+      <c r="A119" s="14">
+        <v>117</v>
+      </c>
+      <c r="B119" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C119" s="15"/>
       <c r="D119" s="12"/>
       <c r="E119" s="13"/>
-      <c r="F119" s="14"/>
-      <c r="G119" s="14"/>
+      <c r="F119" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G119" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H119" s="16"/>
       <c r="I119" s="15"/>
       <c r="J119" s="14"/>
@@ -4299,13 +5234,21 @@
       <c r="N119" s="7"/>
     </row>
     <row r="120" spans="1:14" ht="15.75">
-      <c r="A120" s="14"/>
-      <c r="B120" s="14"/>
+      <c r="A120" s="14">
+        <v>118</v>
+      </c>
+      <c r="B120" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C120" s="15"/>
       <c r="D120" s="12"/>
       <c r="E120" s="13"/>
-      <c r="F120" s="14"/>
-      <c r="G120" s="14"/>
+      <c r="F120" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G120" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H120" s="16"/>
       <c r="I120" s="15"/>
       <c r="J120" s="14"/>
@@ -4315,13 +5258,21 @@
       <c r="N120" s="7"/>
     </row>
     <row r="121" spans="1:14" ht="15.75">
-      <c r="A121" s="14"/>
-      <c r="B121" s="14"/>
+      <c r="A121" s="14">
+        <v>119</v>
+      </c>
+      <c r="B121" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C121" s="15"/>
       <c r="D121" s="12"/>
       <c r="E121" s="13"/>
-      <c r="F121" s="14"/>
-      <c r="G121" s="14"/>
+      <c r="F121" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G121" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H121" s="16"/>
       <c r="I121" s="15"/>
       <c r="J121" s="14"/>
@@ -4331,13 +5282,21 @@
       <c r="N121" s="7"/>
     </row>
     <row r="122" spans="1:14" ht="15.75">
-      <c r="A122" s="14"/>
-      <c r="B122" s="14"/>
+      <c r="A122" s="14">
+        <v>120</v>
+      </c>
+      <c r="B122" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C122" s="15"/>
       <c r="D122" s="12"/>
       <c r="E122" s="13"/>
-      <c r="F122" s="14"/>
-      <c r="G122" s="14"/>
+      <c r="F122" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G122" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H122" s="16"/>
       <c r="I122" s="15"/>
       <c r="J122" s="14"/>
@@ -4347,13 +5306,21 @@
       <c r="N122" s="14"/>
     </row>
     <row r="123" spans="1:14" ht="15.75">
-      <c r="A123" s="14"/>
-      <c r="B123" s="14"/>
+      <c r="A123" s="14">
+        <v>121</v>
+      </c>
+      <c r="B123" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C123" s="15"/>
       <c r="D123" s="12"/>
       <c r="E123" s="13"/>
-      <c r="F123" s="14"/>
-      <c r="G123" s="14"/>
+      <c r="F123" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G123" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H123" s="16"/>
       <c r="I123" s="15"/>
       <c r="J123" s="14"/>
@@ -4363,13 +5330,21 @@
       <c r="N123" s="14"/>
     </row>
     <row r="124" spans="1:14" ht="15.75">
-      <c r="A124" s="14"/>
-      <c r="B124" s="14"/>
+      <c r="A124" s="14">
+        <v>122</v>
+      </c>
+      <c r="B124" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C124" s="15"/>
       <c r="D124" s="12"/>
       <c r="E124" s="13"/>
-      <c r="F124" s="14"/>
-      <c r="G124" s="14"/>
+      <c r="F124" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G124" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H124" s="16"/>
       <c r="I124" s="15"/>
       <c r="J124" s="14"/>
@@ -4379,13 +5354,21 @@
       <c r="N124" s="7"/>
     </row>
     <row r="125" spans="1:14" ht="15.75">
-      <c r="A125" s="14"/>
-      <c r="B125" s="14"/>
+      <c r="A125" s="14">
+        <v>123</v>
+      </c>
+      <c r="B125" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C125" s="15"/>
       <c r="D125" s="12"/>
       <c r="E125" s="13"/>
-      <c r="F125" s="14"/>
-      <c r="G125" s="14"/>
+      <c r="F125" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G125" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H125" s="16"/>
       <c r="I125" s="15"/>
       <c r="J125" s="14"/>
@@ -4395,13 +5378,21 @@
       <c r="N125" s="14"/>
     </row>
     <row r="126" spans="1:14" ht="15.75">
-      <c r="A126" s="14"/>
-      <c r="B126" s="14"/>
+      <c r="A126" s="14">
+        <v>124</v>
+      </c>
+      <c r="B126" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C126" s="15"/>
       <c r="D126" s="12"/>
       <c r="E126" s="13"/>
-      <c r="F126" s="14"/>
-      <c r="G126" s="14"/>
+      <c r="F126" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G126" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H126" s="16"/>
       <c r="I126" s="15"/>
       <c r="J126" s="14"/>
@@ -4411,13 +5402,21 @@
       <c r="N126" s="14"/>
     </row>
     <row r="127" spans="1:14" ht="15.75">
-      <c r="A127" s="14"/>
-      <c r="B127" s="14"/>
+      <c r="A127" s="14">
+        <v>125</v>
+      </c>
+      <c r="B127" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C127" s="15"/>
       <c r="D127" s="12"/>
       <c r="E127" s="13"/>
-      <c r="F127" s="14"/>
-      <c r="G127" s="14"/>
+      <c r="F127" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G127" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H127" s="16"/>
       <c r="I127" s="15"/>
       <c r="J127" s="14"/>
@@ -4427,13 +5426,21 @@
       <c r="N127" s="7"/>
     </row>
     <row r="128" spans="1:14" ht="15.75">
-      <c r="A128" s="14"/>
-      <c r="B128" s="14"/>
+      <c r="A128" s="14">
+        <v>126</v>
+      </c>
+      <c r="B128" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C128" s="15"/>
       <c r="D128" s="12"/>
       <c r="E128" s="13"/>
-      <c r="F128" s="14"/>
-      <c r="G128" s="14"/>
+      <c r="F128" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G128" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H128" s="16"/>
       <c r="I128" s="15"/>
       <c r="J128" s="14"/>
@@ -4443,13 +5450,21 @@
       <c r="N128" s="7"/>
     </row>
     <row r="129" spans="1:14" ht="15.75">
-      <c r="A129" s="14"/>
-      <c r="B129" s="14"/>
+      <c r="A129" s="14">
+        <v>127</v>
+      </c>
+      <c r="B129" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C129" s="15"/>
       <c r="D129" s="12"/>
       <c r="E129" s="13"/>
-      <c r="F129" s="14"/>
-      <c r="G129" s="14"/>
+      <c r="F129" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G129" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H129" s="16"/>
       <c r="I129" s="15"/>
       <c r="J129" s="14"/>
@@ -4459,13 +5474,21 @@
       <c r="N129" s="14"/>
     </row>
     <row r="130" spans="1:14" ht="15.75">
-      <c r="A130" s="14"/>
-      <c r="B130" s="14"/>
+      <c r="A130" s="14">
+        <v>128</v>
+      </c>
+      <c r="B130" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C130" s="15"/>
       <c r="D130" s="12"/>
       <c r="E130" s="13"/>
-      <c r="F130" s="14"/>
-      <c r="G130" s="14"/>
+      <c r="F130" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G130" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H130" s="16"/>
       <c r="I130" s="15"/>
       <c r="J130" s="14"/>
@@ -4475,13 +5498,21 @@
       <c r="N130" s="7"/>
     </row>
     <row r="131" spans="1:14" ht="15.75">
-      <c r="A131" s="14"/>
-      <c r="B131" s="14"/>
+      <c r="A131" s="14">
+        <v>129</v>
+      </c>
+      <c r="B131" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C131" s="15"/>
       <c r="D131" s="12"/>
       <c r="E131" s="13"/>
-      <c r="F131" s="14"/>
-      <c r="G131" s="14"/>
+      <c r="F131" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G131" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H131" s="16"/>
       <c r="I131" s="15"/>
       <c r="J131" s="14"/>
@@ -4491,13 +5522,21 @@
       <c r="N131" s="14"/>
     </row>
     <row r="132" spans="1:14" ht="15.75">
-      <c r="A132" s="14"/>
-      <c r="B132" s="14"/>
+      <c r="A132" s="14">
+        <v>130</v>
+      </c>
+      <c r="B132" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C132" s="15"/>
       <c r="D132" s="12"/>
       <c r="E132" s="13"/>
-      <c r="F132" s="14"/>
-      <c r="G132" s="14"/>
+      <c r="F132" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G132" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H132" s="16"/>
       <c r="I132" s="15"/>
       <c r="J132" s="14"/>
@@ -4507,13 +5546,21 @@
       <c r="N132" s="14"/>
     </row>
     <row r="133" spans="1:14" ht="15.75">
-      <c r="A133" s="14"/>
-      <c r="B133" s="14"/>
+      <c r="A133" s="14">
+        <v>131</v>
+      </c>
+      <c r="B133" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C133" s="15"/>
       <c r="D133" s="12"/>
       <c r="E133" s="13"/>
-      <c r="F133" s="14"/>
-      <c r="G133" s="14"/>
+      <c r="F133" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G133" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H133" s="16"/>
       <c r="I133" s="15"/>
       <c r="J133" s="14"/>
@@ -4523,13 +5570,21 @@
       <c r="N133" s="14"/>
     </row>
     <row r="134" spans="1:14" ht="15.75">
-      <c r="A134" s="14"/>
-      <c r="B134" s="14"/>
+      <c r="A134" s="14">
+        <v>132</v>
+      </c>
+      <c r="B134" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C134" s="15"/>
       <c r="D134" s="12"/>
       <c r="E134" s="13"/>
-      <c r="F134" s="14"/>
-      <c r="G134" s="14"/>
+      <c r="F134" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G134" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H134" s="16"/>
       <c r="I134" s="15"/>
       <c r="J134" s="14"/>
@@ -4539,13 +5594,21 @@
       <c r="N134" s="7"/>
     </row>
     <row r="135" spans="1:14" ht="15.75">
-      <c r="A135" s="14"/>
-      <c r="B135" s="14"/>
+      <c r="A135" s="14">
+        <v>133</v>
+      </c>
+      <c r="B135" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C135" s="15"/>
       <c r="D135" s="12"/>
       <c r="E135" s="13"/>
-      <c r="F135" s="14"/>
-      <c r="G135" s="14"/>
+      <c r="F135" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G135" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H135" s="16"/>
       <c r="I135" s="15"/>
       <c r="J135" s="14"/>
@@ -4555,13 +5618,21 @@
       <c r="N135" s="7"/>
     </row>
     <row r="136" spans="1:14" ht="15.75">
-      <c r="A136" s="14"/>
-      <c r="B136" s="14"/>
+      <c r="A136" s="14">
+        <v>134</v>
+      </c>
+      <c r="B136" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C136" s="15"/>
       <c r="D136" s="12"/>
       <c r="E136" s="13"/>
-      <c r="F136" s="14"/>
-      <c r="G136" s="14"/>
+      <c r="F136" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G136" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H136" s="16"/>
       <c r="I136" s="15"/>
       <c r="J136" s="14"/>
@@ -4571,13 +5642,21 @@
       <c r="N136" s="7"/>
     </row>
     <row r="137" spans="1:14" ht="15.75">
-      <c r="A137" s="14"/>
-      <c r="B137" s="14"/>
+      <c r="A137" s="14">
+        <v>135</v>
+      </c>
+      <c r="B137" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C137" s="15"/>
       <c r="D137" s="12"/>
       <c r="E137" s="13"/>
-      <c r="F137" s="14"/>
-      <c r="G137" s="14"/>
+      <c r="F137" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G137" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H137" s="16"/>
       <c r="I137" s="15"/>
       <c r="J137" s="14"/>
@@ -4587,13 +5666,21 @@
       <c r="N137" s="7"/>
     </row>
     <row r="138" spans="1:14" ht="15.75">
-      <c r="A138" s="14"/>
-      <c r="B138" s="14"/>
+      <c r="A138" s="14">
+        <v>136</v>
+      </c>
+      <c r="B138" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C138" s="15"/>
       <c r="D138" s="12"/>
       <c r="E138" s="13"/>
-      <c r="F138" s="14"/>
-      <c r="G138" s="14"/>
+      <c r="F138" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G138" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H138" s="16"/>
       <c r="I138" s="15"/>
       <c r="J138" s="14"/>
@@ -4603,13 +5690,21 @@
       <c r="N138" s="14"/>
     </row>
     <row r="139" spans="1:14" ht="15.75">
-      <c r="A139" s="14"/>
-      <c r="B139" s="14"/>
+      <c r="A139" s="14">
+        <v>137</v>
+      </c>
+      <c r="B139" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C139" s="15"/>
       <c r="D139" s="12"/>
       <c r="E139" s="13"/>
-      <c r="F139" s="14"/>
-      <c r="G139" s="14"/>
+      <c r="F139" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G139" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H139" s="16"/>
       <c r="I139" s="15"/>
       <c r="J139" s="14"/>
@@ -4619,13 +5714,21 @@
       <c r="N139" s="7"/>
     </row>
     <row r="140" spans="1:14" ht="15.75">
-      <c r="A140" s="14"/>
-      <c r="B140" s="14"/>
+      <c r="A140" s="14">
+        <v>138</v>
+      </c>
+      <c r="B140" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C140" s="15"/>
       <c r="D140" s="12"/>
       <c r="E140" s="13"/>
-      <c r="F140" s="14"/>
-      <c r="G140" s="14"/>
+      <c r="F140" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G140" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H140" s="16"/>
       <c r="I140" s="15"/>
       <c r="J140" s="14"/>
@@ -4635,13 +5738,21 @@
       <c r="N140" s="7"/>
     </row>
     <row r="141" spans="1:14" ht="15.75">
-      <c r="A141" s="14"/>
-      <c r="B141" s="14"/>
+      <c r="A141" s="14">
+        <v>139</v>
+      </c>
+      <c r="B141" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C141" s="22"/>
       <c r="D141" s="23"/>
       <c r="E141" s="28"/>
-      <c r="F141" s="14"/>
-      <c r="G141" s="14"/>
+      <c r="F141" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G141" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H141" s="16"/>
       <c r="I141" s="15"/>
       <c r="J141" s="14"/>
@@ -4651,13 +5762,21 @@
       <c r="N141" s="7"/>
     </row>
     <row r="142" spans="1:14" ht="15.75">
-      <c r="A142" s="14"/>
-      <c r="B142" s="14"/>
+      <c r="A142" s="14">
+        <v>140</v>
+      </c>
+      <c r="B142" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C142" s="15"/>
       <c r="D142" s="12"/>
       <c r="E142" s="13"/>
-      <c r="F142" s="14"/>
-      <c r="G142" s="14"/>
+      <c r="F142" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G142" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H142" s="16"/>
       <c r="I142" s="15"/>
       <c r="J142" s="14"/>
@@ -4667,13 +5786,21 @@
       <c r="N142" s="7"/>
     </row>
     <row r="143" spans="1:14" ht="15.75">
-      <c r="A143" s="14"/>
-      <c r="B143" s="14"/>
+      <c r="A143" s="14">
+        <v>141</v>
+      </c>
+      <c r="B143" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C143" s="15"/>
       <c r="D143" s="12"/>
       <c r="E143" s="13"/>
-      <c r="F143" s="14"/>
-      <c r="G143" s="14"/>
+      <c r="F143" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G143" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H143" s="16"/>
       <c r="I143" s="15"/>
       <c r="J143" s="14"/>
@@ -4683,13 +5810,21 @@
       <c r="N143" s="14"/>
     </row>
     <row r="144" spans="1:14" ht="15.75">
-      <c r="A144" s="14"/>
-      <c r="B144" s="14"/>
+      <c r="A144" s="14">
+        <v>142</v>
+      </c>
+      <c r="B144" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C144" s="15"/>
       <c r="D144" s="12"/>
       <c r="E144" s="13"/>
-      <c r="F144" s="14"/>
-      <c r="G144" s="14"/>
+      <c r="F144" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G144" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H144" s="16"/>
       <c r="I144" s="15"/>
       <c r="J144" s="14"/>
@@ -4699,13 +5834,21 @@
       <c r="N144" s="7"/>
     </row>
     <row r="145" spans="1:14" ht="15.75">
-      <c r="A145" s="14"/>
-      <c r="B145" s="14"/>
+      <c r="A145" s="14">
+        <v>143</v>
+      </c>
+      <c r="B145" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C145" s="15"/>
       <c r="D145" s="12"/>
       <c r="E145" s="13"/>
-      <c r="F145" s="14"/>
-      <c r="G145" s="14"/>
+      <c r="F145" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G145" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H145" s="16"/>
       <c r="I145" s="15"/>
       <c r="J145" s="14"/>
@@ -4715,13 +5858,21 @@
       <c r="N145" s="7"/>
     </row>
     <row r="146" spans="1:14" ht="15.75">
-      <c r="A146" s="14"/>
-      <c r="B146" s="14"/>
+      <c r="A146" s="14">
+        <v>144</v>
+      </c>
+      <c r="B146" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C146" s="15"/>
       <c r="D146" s="12"/>
       <c r="E146" s="13"/>
-      <c r="F146" s="14"/>
-      <c r="G146" s="14"/>
+      <c r="F146" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G146" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H146" s="16"/>
       <c r="I146" s="15"/>
       <c r="J146" s="14"/>
@@ -4731,13 +5882,21 @@
       <c r="N146" s="14"/>
     </row>
     <row r="147" spans="1:14" ht="15.75">
-      <c r="A147" s="14"/>
-      <c r="B147" s="14"/>
+      <c r="A147" s="14">
+        <v>145</v>
+      </c>
+      <c r="B147" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C147" s="15"/>
       <c r="D147" s="12"/>
       <c r="E147" s="13"/>
-      <c r="F147" s="14"/>
-      <c r="G147" s="14"/>
+      <c r="F147" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G147" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H147" s="16"/>
       <c r="I147" s="15"/>
       <c r="J147" s="14"/>
@@ -4747,13 +5906,21 @@
       <c r="N147" s="14"/>
     </row>
     <row r="148" spans="1:14" ht="15.75">
-      <c r="A148" s="14"/>
-      <c r="B148" s="14"/>
+      <c r="A148" s="14">
+        <v>146</v>
+      </c>
+      <c r="B148" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C148" s="15"/>
       <c r="D148" s="12"/>
       <c r="E148" s="13"/>
-      <c r="F148" s="14"/>
-      <c r="G148" s="14"/>
+      <c r="F148" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G148" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H148" s="16"/>
       <c r="I148" s="15"/>
       <c r="J148" s="14"/>
@@ -4763,13 +5930,21 @@
       <c r="N148" s="7"/>
     </row>
     <row r="149" spans="1:14" ht="15.75">
-      <c r="A149" s="14"/>
-      <c r="B149" s="14"/>
+      <c r="A149" s="14">
+        <v>147</v>
+      </c>
+      <c r="B149" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C149" s="15"/>
       <c r="D149" s="12"/>
       <c r="E149" s="13"/>
-      <c r="F149" s="14"/>
-      <c r="G149" s="14"/>
+      <c r="F149" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G149" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H149" s="16"/>
       <c r="I149" s="15"/>
       <c r="J149" s="14"/>
@@ -4779,13 +5954,21 @@
       <c r="N149" s="7"/>
     </row>
     <row r="150" spans="1:14" ht="15.75">
-      <c r="A150" s="14"/>
-      <c r="B150" s="14"/>
+      <c r="A150" s="14">
+        <v>148</v>
+      </c>
+      <c r="B150" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C150" s="15"/>
       <c r="D150" s="12"/>
       <c r="E150" s="13"/>
-      <c r="F150" s="14"/>
-      <c r="G150" s="14"/>
+      <c r="F150" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G150" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H150" s="16"/>
       <c r="I150" s="15"/>
       <c r="J150" s="14"/>
@@ -4795,13 +5978,21 @@
       <c r="N150" s="7"/>
     </row>
     <row r="151" spans="1:14" ht="15.75">
-      <c r="A151" s="14"/>
-      <c r="B151" s="14"/>
+      <c r="A151" s="14">
+        <v>149</v>
+      </c>
+      <c r="B151" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C151" s="15"/>
       <c r="D151" s="12"/>
       <c r="E151" s="13"/>
-      <c r="F151" s="14"/>
-      <c r="G151" s="14"/>
+      <c r="F151" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G151" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H151" s="16"/>
       <c r="I151" s="15"/>
       <c r="J151" s="14"/>
@@ -4811,13 +6002,21 @@
       <c r="N151" s="14"/>
     </row>
     <row r="152" spans="1:14" ht="15.75">
-      <c r="A152" s="14"/>
-      <c r="B152" s="14"/>
+      <c r="A152" s="14">
+        <v>150</v>
+      </c>
+      <c r="B152" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C152" s="15"/>
       <c r="D152" s="12"/>
       <c r="E152" s="13"/>
-      <c r="F152" s="14"/>
-      <c r="G152" s="14"/>
+      <c r="F152" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G152" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H152" s="16"/>
       <c r="I152" s="15"/>
       <c r="J152" s="14"/>
@@ -4827,13 +6026,21 @@
       <c r="N152" s="14"/>
     </row>
     <row r="153" spans="1:14" ht="15.75">
-      <c r="A153" s="14"/>
-      <c r="B153" s="14"/>
+      <c r="A153" s="14">
+        <v>151</v>
+      </c>
+      <c r="B153" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C153" s="15"/>
       <c r="D153" s="12"/>
       <c r="E153" s="13"/>
-      <c r="F153" s="14"/>
-      <c r="G153" s="14"/>
+      <c r="F153" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G153" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H153" s="16"/>
       <c r="I153" s="15"/>
       <c r="J153" s="14"/>
@@ -4843,13 +6050,21 @@
       <c r="N153" s="14"/>
     </row>
     <row r="154" spans="1:14" ht="15.75">
-      <c r="A154" s="14"/>
-      <c r="B154" s="14"/>
+      <c r="A154" s="14">
+        <v>152</v>
+      </c>
+      <c r="B154" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C154" s="15"/>
       <c r="D154" s="12"/>
       <c r="E154" s="13"/>
-      <c r="F154" s="14"/>
-      <c r="G154" s="14"/>
+      <c r="F154" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G154" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H154" s="16"/>
       <c r="I154" s="15"/>
       <c r="J154" s="14"/>
@@ -4859,13 +6074,21 @@
       <c r="N154" s="7"/>
     </row>
     <row r="155" spans="1:14" ht="15.75">
-      <c r="A155" s="14"/>
-      <c r="B155" s="14"/>
+      <c r="A155" s="14">
+        <v>153</v>
+      </c>
+      <c r="B155" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C155" s="15"/>
       <c r="D155" s="12"/>
       <c r="E155" s="13"/>
-      <c r="F155" s="14"/>
-      <c r="G155" s="14"/>
+      <c r="F155" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G155" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H155" s="16"/>
       <c r="I155" s="15"/>
       <c r="J155" s="14"/>
@@ -4875,13 +6098,21 @@
       <c r="N155" s="7"/>
     </row>
     <row r="156" spans="1:14" ht="15.75">
-      <c r="A156" s="14"/>
-      <c r="B156" s="14"/>
+      <c r="A156" s="14">
+        <v>154</v>
+      </c>
+      <c r="B156" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C156" s="15"/>
       <c r="D156" s="12"/>
       <c r="E156" s="13"/>
-      <c r="F156" s="14"/>
-      <c r="G156" s="14"/>
+      <c r="F156" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G156" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H156" s="16"/>
       <c r="I156" s="15"/>
       <c r="J156" s="14"/>
@@ -4891,13 +6122,21 @@
       <c r="N156" s="7"/>
     </row>
     <row r="157" spans="1:14" ht="15.75">
-      <c r="A157" s="14"/>
-      <c r="B157" s="14"/>
+      <c r="A157" s="14">
+        <v>155</v>
+      </c>
+      <c r="B157" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C157" s="15"/>
       <c r="D157" s="12"/>
       <c r="E157" s="13"/>
-      <c r="F157" s="14"/>
-      <c r="G157" s="14"/>
+      <c r="F157" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G157" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H157" s="16"/>
       <c r="I157" s="15"/>
       <c r="J157" s="14"/>
@@ -4907,13 +6146,21 @@
       <c r="N157" s="14"/>
     </row>
     <row r="158" spans="1:14" ht="15.75">
-      <c r="A158" s="14"/>
-      <c r="B158" s="14"/>
+      <c r="A158" s="14">
+        <v>156</v>
+      </c>
+      <c r="B158" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C158" s="15"/>
       <c r="D158" s="12"/>
       <c r="E158" s="13"/>
-      <c r="F158" s="14"/>
-      <c r="G158" s="14"/>
+      <c r="F158" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G158" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H158" s="16"/>
       <c r="I158" s="15"/>
       <c r="J158" s="14"/>
@@ -4923,13 +6170,21 @@
       <c r="N158" s="14"/>
     </row>
     <row r="159" spans="1:14" ht="15.75">
-      <c r="A159" s="14"/>
-      <c r="B159" s="14"/>
+      <c r="A159" s="14">
+        <v>157</v>
+      </c>
+      <c r="B159" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C159" s="15"/>
       <c r="D159" s="12"/>
       <c r="E159" s="13"/>
-      <c r="F159" s="14"/>
-      <c r="G159" s="14"/>
+      <c r="F159" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G159" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H159" s="16"/>
       <c r="I159" s="15"/>
       <c r="J159" s="14"/>
@@ -4939,13 +6194,21 @@
       <c r="N159" s="7"/>
     </row>
     <row r="160" spans="1:14" ht="15.75">
-      <c r="A160" s="14"/>
-      <c r="B160" s="14"/>
+      <c r="A160" s="14">
+        <v>158</v>
+      </c>
+      <c r="B160" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C160" s="15"/>
       <c r="D160" s="12"/>
       <c r="E160" s="13"/>
-      <c r="F160" s="14"/>
-      <c r="G160" s="14"/>
+      <c r="F160" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G160" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H160" s="16"/>
       <c r="I160" s="15"/>
       <c r="J160" s="14"/>
@@ -4955,13 +6218,21 @@
       <c r="N160" s="14"/>
     </row>
     <row r="161" spans="1:14" ht="15.75">
-      <c r="A161" s="14"/>
-      <c r="B161" s="14"/>
+      <c r="A161" s="14">
+        <v>159</v>
+      </c>
+      <c r="B161" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C161" s="15"/>
       <c r="D161" s="12"/>
       <c r="E161" s="13"/>
-      <c r="F161" s="14"/>
-      <c r="G161" s="14"/>
+      <c r="F161" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G161" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H161" s="16"/>
       <c r="I161" s="15"/>
       <c r="J161" s="14"/>
@@ -4971,13 +6242,21 @@
       <c r="N161" s="7"/>
     </row>
     <row r="162" spans="1:14" ht="15.75">
-      <c r="A162" s="14"/>
-      <c r="B162" s="14"/>
+      <c r="A162" s="14">
+        <v>160</v>
+      </c>
+      <c r="B162" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C162" s="15"/>
       <c r="D162" s="12"/>
       <c r="E162" s="13"/>
-      <c r="F162" s="14"/>
-      <c r="G162" s="14"/>
+      <c r="F162" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G162" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H162" s="16"/>
       <c r="I162" s="15"/>
       <c r="J162" s="14"/>
@@ -4987,13 +6266,21 @@
       <c r="N162" s="7"/>
     </row>
     <row r="163" spans="1:14" ht="15.75">
-      <c r="A163" s="14"/>
-      <c r="B163" s="14"/>
+      <c r="A163" s="14">
+        <v>161</v>
+      </c>
+      <c r="B163" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C163" s="15"/>
       <c r="D163" s="12"/>
       <c r="E163" s="13"/>
-      <c r="F163" s="14"/>
-      <c r="G163" s="14"/>
+      <c r="F163" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G163" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H163" s="16"/>
       <c r="I163" s="15"/>
       <c r="J163" s="14"/>
@@ -5003,13 +6290,21 @@
       <c r="N163" s="7"/>
     </row>
     <row r="164" spans="1:14" ht="15.75">
-      <c r="A164" s="14"/>
-      <c r="B164" s="14"/>
+      <c r="A164" s="14">
+        <v>162</v>
+      </c>
+      <c r="B164" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C164" s="15"/>
       <c r="D164" s="12"/>
       <c r="E164" s="13"/>
-      <c r="F164" s="14"/>
-      <c r="G164" s="14"/>
+      <c r="F164" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G164" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H164" s="16"/>
       <c r="I164" s="15"/>
       <c r="J164" s="14"/>
@@ -5019,13 +6314,21 @@
       <c r="N164" s="7"/>
     </row>
     <row r="165" spans="1:14" ht="15.75">
-      <c r="A165" s="14"/>
-      <c r="B165" s="14"/>
+      <c r="A165" s="14">
+        <v>163</v>
+      </c>
+      <c r="B165" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C165" s="22"/>
       <c r="D165" s="23"/>
       <c r="E165" s="28"/>
-      <c r="F165" s="14"/>
-      <c r="G165" s="14"/>
+      <c r="F165" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G165" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H165" s="16"/>
       <c r="I165" s="15"/>
       <c r="J165" s="14"/>
@@ -5035,13 +6338,21 @@
       <c r="N165" s="7"/>
     </row>
     <row r="166" spans="1:14" ht="15.75">
-      <c r="A166" s="14"/>
-      <c r="B166" s="14"/>
+      <c r="A166" s="14">
+        <v>164</v>
+      </c>
+      <c r="B166" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C166" s="15"/>
       <c r="D166" s="12"/>
       <c r="E166" s="13"/>
-      <c r="F166" s="14"/>
-      <c r="G166" s="14"/>
+      <c r="F166" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G166" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H166" s="16"/>
       <c r="I166" s="15"/>
       <c r="J166" s="14"/>
@@ -5051,13 +6362,21 @@
       <c r="N166" s="7"/>
     </row>
     <row r="167" spans="1:14" ht="15.75">
-      <c r="A167" s="14"/>
-      <c r="B167" s="14"/>
+      <c r="A167" s="14">
+        <v>165</v>
+      </c>
+      <c r="B167" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C167" s="15"/>
       <c r="D167" s="12"/>
       <c r="E167" s="13"/>
-      <c r="F167" s="14"/>
-      <c r="G167" s="14"/>
+      <c r="F167" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G167" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H167" s="16"/>
       <c r="I167" s="15"/>
       <c r="J167" s="14"/>
@@ -5067,13 +6386,21 @@
       <c r="N167" s="7"/>
     </row>
     <row r="168" spans="1:14" ht="15.75">
-      <c r="A168" s="14"/>
-      <c r="B168" s="14"/>
+      <c r="A168" s="14">
+        <v>166</v>
+      </c>
+      <c r="B168" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C168" s="15"/>
       <c r="D168" s="12"/>
       <c r="E168" s="13"/>
-      <c r="F168" s="14"/>
-      <c r="G168" s="14"/>
+      <c r="F168" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G168" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H168" s="16"/>
       <c r="I168" s="15"/>
       <c r="J168" s="14"/>
@@ -5083,13 +6410,21 @@
       <c r="N168" s="7"/>
     </row>
     <row r="169" spans="1:14" ht="15.75">
-      <c r="A169" s="14"/>
-      <c r="B169" s="14"/>
+      <c r="A169" s="14">
+        <v>167</v>
+      </c>
+      <c r="B169" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C169" s="15"/>
       <c r="D169" s="12"/>
       <c r="E169" s="13"/>
-      <c r="F169" s="14"/>
-      <c r="G169" s="14"/>
+      <c r="F169" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G169" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H169" s="16"/>
       <c r="I169" s="15"/>
       <c r="J169" s="14"/>
@@ -5099,13 +6434,21 @@
       <c r="N169" s="7"/>
     </row>
     <row r="170" spans="1:14" ht="15.75">
-      <c r="A170" s="14"/>
-      <c r="B170" s="14"/>
+      <c r="A170" s="14">
+        <v>168</v>
+      </c>
+      <c r="B170" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C170" s="15"/>
       <c r="D170" s="12"/>
       <c r="E170" s="13"/>
-      <c r="F170" s="14"/>
-      <c r="G170" s="14"/>
+      <c r="F170" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G170" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H170" s="16"/>
       <c r="I170" s="15"/>
       <c r="J170" s="14"/>
@@ -5115,13 +6458,21 @@
       <c r="N170" s="7"/>
     </row>
     <row r="171" spans="1:14" ht="15.75">
-      <c r="A171" s="14"/>
-      <c r="B171" s="14"/>
+      <c r="A171" s="14">
+        <v>169</v>
+      </c>
+      <c r="B171" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C171" s="15"/>
       <c r="D171" s="12"/>
       <c r="E171" s="13"/>
-      <c r="F171" s="14"/>
-      <c r="G171" s="14"/>
+      <c r="F171" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G171" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H171" s="16"/>
       <c r="I171" s="15"/>
       <c r="J171" s="14"/>
@@ -5131,13 +6482,21 @@
       <c r="N171" s="7"/>
     </row>
     <row r="172" spans="1:14" ht="15.75">
-      <c r="A172" s="14"/>
-      <c r="B172" s="14"/>
+      <c r="A172" s="14">
+        <v>170</v>
+      </c>
+      <c r="B172" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C172" s="15"/>
       <c r="D172" s="12"/>
       <c r="E172" s="13"/>
-      <c r="F172" s="14"/>
-      <c r="G172" s="14"/>
+      <c r="F172" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G172" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H172" s="16"/>
       <c r="I172" s="15"/>
       <c r="J172" s="14"/>
@@ -5147,13 +6506,21 @@
       <c r="N172" s="7"/>
     </row>
     <row r="173" spans="1:14" ht="15.75">
-      <c r="A173" s="14"/>
-      <c r="B173" s="14"/>
+      <c r="A173" s="14">
+        <v>171</v>
+      </c>
+      <c r="B173" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C173" s="15"/>
       <c r="D173" s="12"/>
       <c r="E173" s="13"/>
-      <c r="F173" s="14"/>
-      <c r="G173" s="14"/>
+      <c r="F173" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G173" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H173" s="16"/>
       <c r="I173" s="15"/>
       <c r="J173" s="14"/>
@@ -5163,13 +6530,21 @@
       <c r="N173" s="7"/>
     </row>
     <row r="174" spans="1:14" ht="15.75">
-      <c r="A174" s="14"/>
-      <c r="B174" s="14"/>
+      <c r="A174" s="14">
+        <v>172</v>
+      </c>
+      <c r="B174" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C174" s="15"/>
       <c r="D174" s="12"/>
       <c r="E174" s="13"/>
-      <c r="F174" s="14"/>
-      <c r="G174" s="14"/>
+      <c r="F174" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G174" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H174" s="16"/>
       <c r="I174" s="15"/>
       <c r="J174" s="14"/>
@@ -5179,13 +6554,21 @@
       <c r="N174" s="7"/>
     </row>
     <row r="175" spans="1:14" ht="15.75">
-      <c r="A175" s="14"/>
-      <c r="B175" s="14"/>
+      <c r="A175" s="14">
+        <v>173</v>
+      </c>
+      <c r="B175" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C175" s="15"/>
       <c r="D175" s="12"/>
       <c r="E175" s="13"/>
-      <c r="F175" s="14"/>
-      <c r="G175" s="14"/>
+      <c r="F175" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G175" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H175" s="16"/>
       <c r="I175" s="15"/>
       <c r="J175" s="14"/>
@@ -5195,13 +6578,21 @@
       <c r="N175" s="7"/>
     </row>
     <row r="176" spans="1:14" ht="15.75">
-      <c r="A176" s="14"/>
-      <c r="B176" s="14"/>
+      <c r="A176" s="14">
+        <v>174</v>
+      </c>
+      <c r="B176" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C176" s="15"/>
       <c r="D176" s="12"/>
       <c r="E176" s="13"/>
-      <c r="F176" s="14"/>
-      <c r="G176" s="14"/>
+      <c r="F176" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G176" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H176" s="16"/>
       <c r="I176" s="15"/>
       <c r="J176" s="14"/>
@@ -5211,13 +6602,21 @@
       <c r="N176" s="7"/>
     </row>
     <row r="177" spans="1:14" ht="15.75">
-      <c r="A177" s="14"/>
-      <c r="B177" s="14"/>
+      <c r="A177" s="14">
+        <v>175</v>
+      </c>
+      <c r="B177" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C177" s="15"/>
       <c r="D177" s="12"/>
       <c r="E177" s="13"/>
-      <c r="F177" s="14"/>
-      <c r="G177" s="14"/>
+      <c r="F177" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G177" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H177" s="16"/>
       <c r="I177" s="15"/>
       <c r="J177" s="14"/>
@@ -5227,13 +6626,21 @@
       <c r="N177" s="7"/>
     </row>
     <row r="178" spans="1:14" ht="15.75">
-      <c r="A178" s="14"/>
-      <c r="B178" s="14"/>
+      <c r="A178" s="14">
+        <v>176</v>
+      </c>
+      <c r="B178" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C178" s="15"/>
       <c r="D178" s="12"/>
       <c r="E178" s="13"/>
-      <c r="F178" s="14"/>
-      <c r="G178" s="14"/>
+      <c r="F178" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G178" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H178" s="16"/>
       <c r="I178" s="15"/>
       <c r="J178" s="14"/>
@@ -5243,13 +6650,21 @@
       <c r="N178" s="14"/>
     </row>
     <row r="179" spans="1:14" ht="15.75">
-      <c r="A179" s="14"/>
-      <c r="B179" s="14"/>
+      <c r="A179" s="14">
+        <v>177</v>
+      </c>
+      <c r="B179" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C179" s="15"/>
       <c r="D179" s="12"/>
       <c r="E179" s="13"/>
-      <c r="F179" s="14"/>
-      <c r="G179" s="14"/>
+      <c r="F179" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G179" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H179" s="16"/>
       <c r="I179" s="15"/>
       <c r="J179" s="14"/>
@@ -5259,13 +6674,21 @@
       <c r="N179" s="14"/>
     </row>
     <row r="180" spans="1:14" ht="15.75">
-      <c r="A180" s="14"/>
-      <c r="B180" s="14"/>
+      <c r="A180" s="14">
+        <v>178</v>
+      </c>
+      <c r="B180" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C180" s="15"/>
       <c r="D180" s="12"/>
       <c r="E180" s="13"/>
-      <c r="F180" s="14"/>
-      <c r="G180" s="14"/>
+      <c r="F180" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G180" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H180" s="16"/>
       <c r="I180" s="15"/>
       <c r="J180" s="14"/>
@@ -5275,13 +6698,21 @@
       <c r="N180" s="7"/>
     </row>
     <row r="181" spans="1:14" ht="15.75">
-      <c r="A181" s="14"/>
-      <c r="B181" s="14"/>
+      <c r="A181" s="14">
+        <v>179</v>
+      </c>
+      <c r="B181" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C181" s="15"/>
       <c r="D181" s="12"/>
       <c r="E181" s="13"/>
-      <c r="F181" s="14"/>
-      <c r="G181" s="14"/>
+      <c r="F181" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G181" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H181" s="16"/>
       <c r="I181" s="15"/>
       <c r="J181" s="14"/>
@@ -5291,13 +6722,21 @@
       <c r="N181" s="7"/>
     </row>
     <row r="182" spans="1:14" ht="15.75">
-      <c r="A182" s="14"/>
-      <c r="B182" s="14"/>
+      <c r="A182" s="14">
+        <v>180</v>
+      </c>
+      <c r="B182" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C182" s="15"/>
       <c r="D182" s="12"/>
       <c r="E182" s="13"/>
-      <c r="F182" s="14"/>
-      <c r="G182" s="14"/>
+      <c r="F182" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G182" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H182" s="16"/>
       <c r="I182" s="15"/>
       <c r="J182" s="14"/>
@@ -5307,13 +6746,21 @@
       <c r="N182" s="7"/>
     </row>
     <row r="183" spans="1:14" ht="15.75">
-      <c r="A183" s="14"/>
-      <c r="B183" s="14"/>
+      <c r="A183" s="14">
+        <v>181</v>
+      </c>
+      <c r="B183" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C183" s="15"/>
       <c r="D183" s="12"/>
       <c r="E183" s="13"/>
-      <c r="F183" s="14"/>
-      <c r="G183" s="14"/>
+      <c r="F183" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G183" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H183" s="16"/>
       <c r="I183" s="15"/>
       <c r="J183" s="14"/>
@@ -5323,13 +6770,21 @@
       <c r="N183" s="7"/>
     </row>
     <row r="184" spans="1:14" ht="15.75">
-      <c r="A184" s="14"/>
-      <c r="B184" s="14"/>
+      <c r="A184" s="14">
+        <v>182</v>
+      </c>
+      <c r="B184" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C184" s="15"/>
       <c r="D184" s="12"/>
       <c r="E184" s="13"/>
-      <c r="F184" s="14"/>
-      <c r="G184" s="14"/>
+      <c r="F184" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G184" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H184" s="16"/>
       <c r="I184" s="15"/>
       <c r="J184" s="14"/>
@@ -5339,13 +6794,21 @@
       <c r="N184" s="7"/>
     </row>
     <row r="185" spans="1:14" ht="15.75">
-      <c r="A185" s="14"/>
-      <c r="B185" s="14"/>
+      <c r="A185" s="14">
+        <v>183</v>
+      </c>
+      <c r="B185" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C185" s="15"/>
       <c r="D185" s="12"/>
       <c r="E185" s="13"/>
-      <c r="F185" s="14"/>
-      <c r="G185" s="14"/>
+      <c r="F185" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G185" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H185" s="16"/>
       <c r="I185" s="15"/>
       <c r="J185" s="14"/>
@@ -5355,13 +6818,21 @@
       <c r="N185" s="7"/>
     </row>
     <row r="186" spans="1:14" ht="15.75">
-      <c r="A186" s="14"/>
-      <c r="B186" s="14"/>
+      <c r="A186" s="14">
+        <v>184</v>
+      </c>
+      <c r="B186" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C186" s="15"/>
       <c r="D186" s="12"/>
       <c r="E186" s="13"/>
-      <c r="F186" s="14"/>
-      <c r="G186" s="14"/>
+      <c r="F186" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G186" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H186" s="16"/>
       <c r="I186" s="15"/>
       <c r="J186" s="14"/>
@@ -5371,13 +6842,21 @@
       <c r="N186" s="7"/>
     </row>
     <row r="187" spans="1:14" ht="15.75">
-      <c r="A187" s="14"/>
-      <c r="B187" s="14"/>
+      <c r="A187" s="14">
+        <v>185</v>
+      </c>
+      <c r="B187" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C187" s="15"/>
       <c r="D187" s="12"/>
       <c r="E187" s="13"/>
-      <c r="F187" s="14"/>
-      <c r="G187" s="14"/>
+      <c r="F187" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G187" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H187" s="16"/>
       <c r="I187" s="15"/>
       <c r="J187" s="14"/>
@@ -5387,13 +6866,21 @@
       <c r="N187" s="7"/>
     </row>
     <row r="188" spans="1:14" ht="15.75">
-      <c r="A188" s="14"/>
-      <c r="B188" s="14"/>
+      <c r="A188" s="14">
+        <v>186</v>
+      </c>
+      <c r="B188" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C188" s="15"/>
       <c r="D188" s="12"/>
       <c r="E188" s="13"/>
-      <c r="F188" s="14"/>
-      <c r="G188" s="14"/>
+      <c r="F188" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G188" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H188" s="16"/>
       <c r="I188" s="15"/>
       <c r="J188" s="14"/>
@@ -5403,13 +6890,21 @@
       <c r="N188" s="7"/>
     </row>
     <row r="189" spans="1:14" ht="15.75">
-      <c r="A189" s="14"/>
-      <c r="B189" s="14"/>
+      <c r="A189" s="14">
+        <v>187</v>
+      </c>
+      <c r="B189" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C189" s="15"/>
       <c r="D189" s="12"/>
       <c r="E189" s="13"/>
-      <c r="F189" s="14"/>
-      <c r="G189" s="14"/>
+      <c r="F189" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G189" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H189" s="16"/>
       <c r="I189" s="15"/>
       <c r="J189" s="14"/>
@@ -5419,13 +6914,21 @@
       <c r="N189" s="7"/>
     </row>
     <row r="190" spans="1:14" ht="15.75">
-      <c r="A190" s="14"/>
-      <c r="B190" s="14"/>
+      <c r="A190" s="14">
+        <v>188</v>
+      </c>
+      <c r="B190" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C190" s="15"/>
       <c r="D190" s="12"/>
       <c r="E190" s="13"/>
-      <c r="F190" s="14"/>
-      <c r="G190" s="14"/>
+      <c r="F190" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G190" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H190" s="16"/>
       <c r="I190" s="15"/>
       <c r="J190" s="14"/>
@@ -5435,13 +6938,21 @@
       <c r="N190" s="7"/>
     </row>
     <row r="191" spans="1:14" ht="15.75">
-      <c r="A191" s="14"/>
-      <c r="B191" s="14"/>
+      <c r="A191" s="14">
+        <v>189</v>
+      </c>
+      <c r="B191" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C191" s="15"/>
       <c r="D191" s="12"/>
       <c r="E191" s="13"/>
-      <c r="F191" s="14"/>
-      <c r="G191" s="14"/>
+      <c r="F191" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G191" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H191" s="16"/>
       <c r="I191" s="15"/>
       <c r="J191" s="14"/>
@@ -5451,13 +6962,21 @@
       <c r="N191" s="7"/>
     </row>
     <row r="192" spans="1:14" ht="15.75">
-      <c r="A192" s="14"/>
-      <c r="B192" s="14"/>
+      <c r="A192" s="14">
+        <v>190</v>
+      </c>
+      <c r="B192" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C192" s="15"/>
       <c r="D192" s="12"/>
       <c r="E192" s="13"/>
-      <c r="F192" s="14"/>
-      <c r="G192" s="14"/>
+      <c r="F192" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G192" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H192" s="16"/>
       <c r="I192" s="15"/>
       <c r="J192" s="14"/>
@@ -5467,13 +6986,21 @@
       <c r="N192" s="7"/>
     </row>
     <row r="193" spans="1:14" ht="15.75">
-      <c r="A193" s="14"/>
-      <c r="B193" s="14"/>
+      <c r="A193" s="14">
+        <v>191</v>
+      </c>
+      <c r="B193" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C193" s="15"/>
       <c r="D193" s="12"/>
       <c r="E193" s="13"/>
-      <c r="F193" s="14"/>
-      <c r="G193" s="14"/>
+      <c r="F193" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G193" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H193" s="16"/>
       <c r="I193" s="15"/>
       <c r="J193" s="14"/>
@@ -5483,13 +7010,21 @@
       <c r="N193" s="7"/>
     </row>
     <row r="194" spans="1:14" ht="15.75">
-      <c r="A194" s="14"/>
-      <c r="B194" s="14"/>
+      <c r="A194" s="14">
+        <v>192</v>
+      </c>
+      <c r="B194" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C194" s="15"/>
       <c r="D194" s="12"/>
       <c r="E194" s="13"/>
-      <c r="F194" s="14"/>
-      <c r="G194" s="14"/>
+      <c r="F194" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G194" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H194" s="16"/>
       <c r="I194" s="15"/>
       <c r="J194" s="14"/>
@@ -5499,13 +7034,21 @@
       <c r="N194" s="7"/>
     </row>
     <row r="195" spans="1:14" ht="15.75">
-      <c r="A195" s="14"/>
-      <c r="B195" s="14"/>
+      <c r="A195" s="14">
+        <v>193</v>
+      </c>
+      <c r="B195" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C195" s="15"/>
       <c r="D195" s="12"/>
       <c r="E195" s="13"/>
-      <c r="F195" s="14"/>
-      <c r="G195" s="14"/>
+      <c r="F195" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G195" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H195" s="16"/>
       <c r="I195" s="15"/>
       <c r="J195" s="14"/>
@@ -5515,13 +7058,21 @@
       <c r="N195" s="7"/>
     </row>
     <row r="196" spans="1:14" ht="15.75">
-      <c r="A196" s="14"/>
-      <c r="B196" s="14"/>
+      <c r="A196" s="14">
+        <v>194</v>
+      </c>
+      <c r="B196" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C196" s="15"/>
       <c r="D196" s="12"/>
       <c r="E196" s="13"/>
-      <c r="F196" s="14"/>
-      <c r="G196" s="14"/>
+      <c r="F196" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G196" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H196" s="16"/>
       <c r="I196" s="15"/>
       <c r="J196" s="14"/>
@@ -5531,13 +7082,21 @@
       <c r="N196" s="7"/>
     </row>
     <row r="197" spans="1:14" ht="15.75">
-      <c r="A197" s="14"/>
-      <c r="B197" s="14"/>
+      <c r="A197" s="14">
+        <v>195</v>
+      </c>
+      <c r="B197" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C197" s="15"/>
       <c r="D197" s="12"/>
       <c r="E197" s="13"/>
-      <c r="F197" s="14"/>
-      <c r="G197" s="14"/>
+      <c r="F197" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G197" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H197" s="16"/>
       <c r="I197" s="15"/>
       <c r="J197" s="14"/>
@@ -5547,13 +7106,21 @@
       <c r="N197" s="7"/>
     </row>
     <row r="198" spans="1:14" ht="15.75">
-      <c r="A198" s="14"/>
-      <c r="B198" s="14"/>
+      <c r="A198" s="14">
+        <v>196</v>
+      </c>
+      <c r="B198" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C198" s="15"/>
       <c r="D198" s="12"/>
       <c r="E198" s="13"/>
-      <c r="F198" s="14"/>
-      <c r="G198" s="14"/>
+      <c r="F198" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G198" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H198" s="16"/>
       <c r="I198" s="15"/>
       <c r="J198" s="14"/>
@@ -5563,13 +7130,21 @@
       <c r="N198" s="7"/>
     </row>
     <row r="199" spans="1:14" ht="15.75">
-      <c r="A199" s="14"/>
-      <c r="B199" s="14"/>
+      <c r="A199" s="14">
+        <v>197</v>
+      </c>
+      <c r="B199" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C199" s="15"/>
       <c r="D199" s="12"/>
       <c r="E199" s="13"/>
-      <c r="F199" s="14"/>
-      <c r="G199" s="14"/>
+      <c r="F199" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G199" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H199" s="16"/>
       <c r="I199" s="15"/>
       <c r="J199" s="14"/>
@@ -5579,13 +7154,21 @@
       <c r="N199" s="7"/>
     </row>
     <row r="200" spans="1:14" ht="15.75">
-      <c r="A200" s="14"/>
-      <c r="B200" s="14"/>
+      <c r="A200" s="14">
+        <v>198</v>
+      </c>
+      <c r="B200" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C200" s="15"/>
       <c r="D200" s="12"/>
       <c r="E200" s="13"/>
-      <c r="F200" s="14"/>
-      <c r="G200" s="14"/>
+      <c r="F200" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G200" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H200" s="16"/>
       <c r="I200" s="15"/>
       <c r="J200" s="14"/>
@@ -5595,13 +7178,21 @@
       <c r="N200" s="7"/>
     </row>
     <row r="201" spans="1:14" ht="15.75">
-      <c r="A201" s="14"/>
-      <c r="B201" s="14"/>
+      <c r="A201" s="14">
+        <v>199</v>
+      </c>
+      <c r="B201" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C201" s="15"/>
       <c r="D201" s="12"/>
       <c r="E201" s="13"/>
-      <c r="F201" s="14"/>
-      <c r="G201" s="14"/>
+      <c r="F201" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G201" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H201" s="32"/>
       <c r="I201" s="15"/>
       <c r="J201" s="14"/>
@@ -5611,13 +7202,21 @@
       <c r="N201" s="7"/>
     </row>
     <row r="202" spans="1:14" ht="15.75">
-      <c r="A202" s="14"/>
-      <c r="B202" s="14"/>
+      <c r="A202" s="14">
+        <v>200</v>
+      </c>
+      <c r="B202" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C202" s="15"/>
       <c r="D202" s="12"/>
       <c r="E202" s="13"/>
-      <c r="F202" s="14"/>
-      <c r="G202" s="14"/>
+      <c r="F202" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G202" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H202" s="16"/>
       <c r="I202" s="15"/>
       <c r="J202" s="14"/>
@@ -5627,13 +7226,21 @@
       <c r="N202" s="7"/>
     </row>
     <row r="203" spans="1:14" ht="15.75">
-      <c r="A203" s="14"/>
-      <c r="B203" s="14"/>
+      <c r="A203" s="14">
+        <v>201</v>
+      </c>
+      <c r="B203" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C203" s="15"/>
       <c r="D203" s="12"/>
       <c r="E203" s="13"/>
-      <c r="F203" s="14"/>
-      <c r="G203" s="14"/>
+      <c r="F203" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G203" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H203" s="16"/>
       <c r="I203" s="15"/>
       <c r="J203" s="14"/>
@@ -5643,13 +7250,21 @@
       <c r="N203" s="7"/>
     </row>
     <row r="204" spans="1:14" ht="15.75">
-      <c r="A204" s="14"/>
-      <c r="B204" s="14"/>
+      <c r="A204" s="14">
+        <v>202</v>
+      </c>
+      <c r="B204" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C204" s="15"/>
       <c r="D204" s="12"/>
       <c r="E204" s="13"/>
-      <c r="F204" s="14"/>
-      <c r="G204" s="14"/>
+      <c r="F204" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G204" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H204" s="16"/>
       <c r="I204" s="15"/>
       <c r="J204" s="14"/>
@@ -5659,13 +7274,21 @@
       <c r="N204" s="7"/>
     </row>
     <row r="205" spans="1:14" ht="15.75">
-      <c r="A205" s="14"/>
-      <c r="B205" s="14"/>
+      <c r="A205" s="14">
+        <v>203</v>
+      </c>
+      <c r="B205" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C205" s="15"/>
       <c r="D205" s="12"/>
       <c r="E205" s="13"/>
-      <c r="F205" s="14"/>
-      <c r="G205" s="14"/>
+      <c r="F205" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G205" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H205" s="16"/>
       <c r="I205" s="15"/>
       <c r="J205" s="14"/>
@@ -5675,13 +7298,21 @@
       <c r="N205" s="7"/>
     </row>
     <row r="206" spans="1:14" ht="15.75">
-      <c r="A206" s="14"/>
-      <c r="B206" s="14"/>
+      <c r="A206" s="14">
+        <v>204</v>
+      </c>
+      <c r="B206" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C206" s="15"/>
       <c r="D206" s="12"/>
       <c r="E206" s="13"/>
-      <c r="F206" s="14"/>
-      <c r="G206" s="14"/>
+      <c r="F206" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G206" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H206" s="16"/>
       <c r="I206" s="15"/>
       <c r="J206" s="14"/>
@@ -5691,13 +7322,21 @@
       <c r="N206" s="7"/>
     </row>
     <row r="207" spans="1:14" ht="15.75">
-      <c r="A207" s="14"/>
-      <c r="B207" s="14"/>
+      <c r="A207" s="14">
+        <v>205</v>
+      </c>
+      <c r="B207" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C207" s="15"/>
       <c r="D207" s="12"/>
       <c r="E207" s="13"/>
-      <c r="F207" s="14"/>
-      <c r="G207" s="14"/>
+      <c r="F207" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G207" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H207" s="16"/>
       <c r="I207" s="15"/>
       <c r="J207" s="14"/>
@@ -5707,13 +7346,21 @@
       <c r="N207" s="7"/>
     </row>
     <row r="208" spans="1:14" ht="15.75">
-      <c r="A208" s="14"/>
-      <c r="B208" s="14"/>
+      <c r="A208" s="14">
+        <v>206</v>
+      </c>
+      <c r="B208" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C208" s="15"/>
       <c r="D208" s="12"/>
       <c r="E208" s="13"/>
-      <c r="F208" s="14"/>
-      <c r="G208" s="14"/>
+      <c r="F208" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G208" s="41" t="s">
+        <v>134</v>
+      </c>
       <c r="H208" s="16"/>
       <c r="I208" s="15"/>
       <c r="J208" s="14"/>
@@ -5723,12 +7370,18 @@
       <c r="N208" s="7"/>
     </row>
     <row r="209" spans="1:14" ht="15.75">
-      <c r="A209" s="14"/>
-      <c r="B209" s="14"/>
+      <c r="A209" s="14">
+        <v>207</v>
+      </c>
+      <c r="B209" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C209" s="15"/>
       <c r="D209" s="12"/>
       <c r="E209" s="13"/>
-      <c r="F209" s="14"/>
+      <c r="F209" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G209" s="14"/>
       <c r="H209" s="16"/>
       <c r="I209" s="15"/>
@@ -5739,12 +7392,18 @@
       <c r="N209" s="7"/>
     </row>
     <row r="210" spans="1:14" ht="15.75">
-      <c r="A210" s="14"/>
-      <c r="B210" s="14"/>
+      <c r="A210" s="14">
+        <v>208</v>
+      </c>
+      <c r="B210" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C210" s="15"/>
       <c r="D210" s="12"/>
       <c r="E210" s="13"/>
-      <c r="F210" s="14"/>
+      <c r="F210" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G210" s="14"/>
       <c r="H210" s="16"/>
       <c r="I210" s="15"/>
@@ -5755,12 +7414,18 @@
       <c r="N210" s="7"/>
     </row>
     <row r="211" spans="1:14" ht="15.75">
-      <c r="A211" s="14"/>
-      <c r="B211" s="14"/>
+      <c r="A211" s="14">
+        <v>209</v>
+      </c>
+      <c r="B211" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C211" s="15"/>
       <c r="D211" s="12"/>
       <c r="E211" s="13"/>
-      <c r="F211" s="14"/>
+      <c r="F211" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G211" s="14"/>
       <c r="H211" s="16"/>
       <c r="I211" s="15"/>
@@ -5771,12 +7436,18 @@
       <c r="N211" s="7"/>
     </row>
     <row r="212" spans="1:14" ht="15.75">
-      <c r="A212" s="14"/>
-      <c r="B212" s="14"/>
+      <c r="A212" s="14">
+        <v>210</v>
+      </c>
+      <c r="B212" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C212" s="15"/>
       <c r="D212" s="12"/>
       <c r="E212" s="13"/>
-      <c r="F212" s="14"/>
+      <c r="F212" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G212" s="14"/>
       <c r="H212" s="16"/>
       <c r="I212" s="15"/>
@@ -5787,12 +7458,18 @@
       <c r="N212" s="7"/>
     </row>
     <row r="213" spans="1:14" ht="15.75">
-      <c r="A213" s="14"/>
-      <c r="B213" s="14"/>
+      <c r="A213" s="14">
+        <v>211</v>
+      </c>
+      <c r="B213" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C213" s="15"/>
       <c r="D213" s="12"/>
       <c r="E213" s="13"/>
-      <c r="F213" s="14"/>
+      <c r="F213" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G213" s="14"/>
       <c r="H213" s="16"/>
       <c r="I213" s="15"/>
@@ -5803,12 +7480,18 @@
       <c r="N213" s="7"/>
     </row>
     <row r="214" spans="1:14" ht="15.75">
-      <c r="A214" s="14"/>
-      <c r="B214" s="14"/>
+      <c r="A214" s="14">
+        <v>212</v>
+      </c>
+      <c r="B214" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C214" s="15"/>
       <c r="D214" s="12"/>
       <c r="E214" s="13"/>
-      <c r="F214" s="14"/>
+      <c r="F214" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G214" s="14"/>
       <c r="H214" s="16"/>
       <c r="I214" s="15"/>
@@ -5819,12 +7502,18 @@
       <c r="N214" s="7"/>
     </row>
     <row r="215" spans="1:14" ht="15.75">
-      <c r="A215" s="14"/>
-      <c r="B215" s="14"/>
+      <c r="A215" s="14">
+        <v>213</v>
+      </c>
+      <c r="B215" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C215" s="15"/>
       <c r="D215" s="12"/>
       <c r="E215" s="13"/>
-      <c r="F215" s="14"/>
+      <c r="F215" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G215" s="14"/>
       <c r="H215" s="16"/>
       <c r="I215" s="15"/>
@@ -5835,12 +7524,18 @@
       <c r="N215" s="7"/>
     </row>
     <row r="216" spans="1:14" ht="15.75">
-      <c r="A216" s="14"/>
-      <c r="B216" s="14"/>
+      <c r="A216" s="14">
+        <v>214</v>
+      </c>
+      <c r="B216" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C216" s="15"/>
       <c r="D216" s="12"/>
       <c r="E216" s="13"/>
-      <c r="F216" s="14"/>
+      <c r="F216" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G216" s="14"/>
       <c r="H216" s="16"/>
       <c r="I216" s="15"/>
@@ -5851,12 +7546,18 @@
       <c r="N216" s="7"/>
     </row>
     <row r="217" spans="1:14" ht="15.75">
-      <c r="A217" s="14"/>
-      <c r="B217" s="14"/>
+      <c r="A217" s="14">
+        <v>215</v>
+      </c>
+      <c r="B217" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C217" s="22"/>
       <c r="D217" s="23"/>
       <c r="E217" s="28"/>
-      <c r="F217" s="14"/>
+      <c r="F217" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G217" s="14"/>
       <c r="H217" s="16"/>
       <c r="I217" s="15"/>
@@ -5867,12 +7568,18 @@
       <c r="N217" s="7"/>
     </row>
     <row r="218" spans="1:14" ht="15.75">
-      <c r="A218" s="14"/>
-      <c r="B218" s="14"/>
+      <c r="A218" s="14">
+        <v>216</v>
+      </c>
+      <c r="B218" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C218" s="15"/>
       <c r="D218" s="12"/>
       <c r="E218" s="13"/>
-      <c r="F218" s="14"/>
+      <c r="F218" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G218" s="14"/>
       <c r="H218" s="16"/>
       <c r="I218" s="15"/>
@@ -5883,12 +7590,18 @@
       <c r="N218" s="7"/>
     </row>
     <row r="219" spans="1:14" ht="15.75">
-      <c r="A219" s="14"/>
-      <c r="B219" s="14"/>
+      <c r="A219" s="14">
+        <v>217</v>
+      </c>
+      <c r="B219" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C219" s="15"/>
       <c r="D219" s="12"/>
       <c r="E219" s="13"/>
-      <c r="F219" s="14"/>
+      <c r="F219" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G219" s="14"/>
       <c r="H219" s="16"/>
       <c r="I219" s="15"/>
@@ -5899,12 +7612,18 @@
       <c r="N219" s="7"/>
     </row>
     <row r="220" spans="1:14" ht="15.75">
-      <c r="A220" s="14"/>
-      <c r="B220" s="14"/>
+      <c r="A220" s="14">
+        <v>218</v>
+      </c>
+      <c r="B220" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C220" s="15"/>
       <c r="D220" s="12"/>
       <c r="E220" s="13"/>
-      <c r="F220" s="14"/>
+      <c r="F220" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G220" s="14"/>
       <c r="H220" s="16"/>
       <c r="I220" s="15"/>
@@ -5915,12 +7634,18 @@
       <c r="N220" s="7"/>
     </row>
     <row r="221" spans="1:14" ht="15.75">
-      <c r="A221" s="14"/>
-      <c r="B221" s="14"/>
+      <c r="A221" s="14">
+        <v>219</v>
+      </c>
+      <c r="B221" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C221" s="15"/>
       <c r="D221" s="12"/>
       <c r="E221" s="13"/>
-      <c r="F221" s="14"/>
+      <c r="F221" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G221" s="14"/>
       <c r="H221" s="16"/>
       <c r="I221" s="15"/>
@@ -5931,12 +7656,18 @@
       <c r="N221" s="7"/>
     </row>
     <row r="222" spans="1:14" ht="15.75">
-      <c r="A222" s="14"/>
-      <c r="B222" s="14"/>
+      <c r="A222" s="14">
+        <v>220</v>
+      </c>
+      <c r="B222" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C222" s="15"/>
       <c r="D222" s="12"/>
       <c r="E222" s="13"/>
-      <c r="F222" s="14"/>
+      <c r="F222" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G222" s="14"/>
       <c r="H222" s="16"/>
       <c r="I222" s="15"/>
@@ -5947,12 +7678,18 @@
       <c r="N222" s="7"/>
     </row>
     <row r="223" spans="1:14" ht="15.75">
-      <c r="A223" s="14"/>
-      <c r="B223" s="14"/>
+      <c r="A223" s="14">
+        <v>221</v>
+      </c>
+      <c r="B223" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C223" s="15"/>
       <c r="D223" s="12"/>
       <c r="E223" s="13"/>
-      <c r="F223" s="14"/>
+      <c r="F223" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G223" s="14"/>
       <c r="H223" s="16"/>
       <c r="I223" s="15"/>
@@ -5963,12 +7700,18 @@
       <c r="N223" s="7"/>
     </row>
     <row r="224" spans="1:14" ht="15.75">
-      <c r="A224" s="14"/>
-      <c r="B224" s="14"/>
+      <c r="A224" s="14">
+        <v>222</v>
+      </c>
+      <c r="B224" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C224" s="15"/>
       <c r="D224" s="12"/>
       <c r="E224" s="13"/>
-      <c r="F224" s="14"/>
+      <c r="F224" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G224" s="14"/>
       <c r="H224" s="16"/>
       <c r="I224" s="15"/>
@@ -5979,12 +7722,18 @@
       <c r="N224" s="7"/>
     </row>
     <row r="225" spans="1:14" ht="15.75">
-      <c r="A225" s="14"/>
-      <c r="B225" s="14"/>
+      <c r="A225" s="14">
+        <v>223</v>
+      </c>
+      <c r="B225" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C225" s="15"/>
       <c r="D225" s="12"/>
       <c r="E225" s="13"/>
-      <c r="F225" s="14"/>
+      <c r="F225" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G225" s="14"/>
       <c r="H225" s="16"/>
       <c r="I225" s="15"/>
@@ -5995,12 +7744,18 @@
       <c r="N225" s="7"/>
     </row>
     <row r="226" spans="1:14" ht="15.75">
-      <c r="A226" s="14"/>
-      <c r="B226" s="14"/>
+      <c r="A226" s="14">
+        <v>224</v>
+      </c>
+      <c r="B226" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C226" s="15"/>
       <c r="D226" s="12"/>
       <c r="E226" s="13"/>
-      <c r="F226" s="14"/>
+      <c r="F226" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G226" s="14"/>
       <c r="H226" s="16"/>
       <c r="I226" s="15"/>
@@ -6011,12 +7766,18 @@
       <c r="N226" s="7"/>
     </row>
     <row r="227" spans="1:14" ht="15.75">
-      <c r="A227" s="14"/>
-      <c r="B227" s="14"/>
+      <c r="A227" s="14">
+        <v>225</v>
+      </c>
+      <c r="B227" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C227" s="15"/>
       <c r="D227" s="12"/>
       <c r="E227" s="13"/>
-      <c r="F227" s="14"/>
+      <c r="F227" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G227" s="14"/>
       <c r="H227" s="16"/>
       <c r="I227" s="15"/>
@@ -6027,12 +7788,18 @@
       <c r="N227" s="7"/>
     </row>
     <row r="228" spans="1:14" ht="15.75">
-      <c r="A228" s="14"/>
-      <c r="B228" s="14"/>
+      <c r="A228" s="14">
+        <v>226</v>
+      </c>
+      <c r="B228" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C228" s="15"/>
       <c r="D228" s="12"/>
       <c r="E228" s="13"/>
-      <c r="F228" s="14"/>
+      <c r="F228" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G228" s="14"/>
       <c r="H228" s="16"/>
       <c r="I228" s="15"/>
@@ -6043,12 +7810,18 @@
       <c r="N228" s="7"/>
     </row>
     <row r="229" spans="1:14" ht="15.75">
-      <c r="A229" s="14"/>
-      <c r="B229" s="14"/>
+      <c r="A229" s="14">
+        <v>227</v>
+      </c>
+      <c r="B229" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C229" s="15"/>
       <c r="D229" s="12"/>
       <c r="E229" s="13"/>
-      <c r="F229" s="14"/>
+      <c r="F229" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G229" s="14"/>
       <c r="H229" s="16"/>
       <c r="I229" s="15"/>
@@ -6059,12 +7832,18 @@
       <c r="N229" s="7"/>
     </row>
     <row r="230" spans="1:14" ht="15.75">
-      <c r="A230" s="14"/>
-      <c r="B230" s="14"/>
+      <c r="A230" s="14">
+        <v>228</v>
+      </c>
+      <c r="B230" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C230" s="15"/>
       <c r="D230" s="12"/>
       <c r="E230" s="13"/>
-      <c r="F230" s="14"/>
+      <c r="F230" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G230" s="14"/>
       <c r="H230" s="16"/>
       <c r="I230" s="15"/>
@@ -6075,12 +7854,18 @@
       <c r="N230" s="7"/>
     </row>
     <row r="231" spans="1:14" ht="15.75">
-      <c r="A231" s="14"/>
-      <c r="B231" s="14"/>
+      <c r="A231" s="14">
+        <v>229</v>
+      </c>
+      <c r="B231" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C231" s="15"/>
       <c r="D231" s="12"/>
       <c r="E231" s="28"/>
-      <c r="F231" s="14"/>
+      <c r="F231" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G231" s="14"/>
       <c r="H231" s="16"/>
       <c r="I231" s="15"/>
@@ -6091,12 +7876,18 @@
       <c r="N231" s="7"/>
     </row>
     <row r="232" spans="1:14" ht="15.75">
-      <c r="A232" s="14"/>
-      <c r="B232" s="14"/>
+      <c r="A232" s="14">
+        <v>230</v>
+      </c>
+      <c r="B232" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C232" s="15"/>
       <c r="D232" s="12"/>
       <c r="E232" s="13"/>
-      <c r="F232" s="14"/>
+      <c r="F232" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G232" s="14"/>
       <c r="H232" s="16"/>
       <c r="I232" s="15"/>
@@ -6107,12 +7898,18 @@
       <c r="N232" s="7"/>
     </row>
     <row r="233" spans="1:14" ht="15.75">
-      <c r="A233" s="14"/>
-      <c r="B233" s="14"/>
+      <c r="A233" s="14">
+        <v>231</v>
+      </c>
+      <c r="B233" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C233" s="15"/>
       <c r="D233" s="12"/>
       <c r="E233" s="13"/>
-      <c r="F233" s="14"/>
+      <c r="F233" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G233" s="14"/>
       <c r="H233" s="16"/>
       <c r="I233" s="15"/>
@@ -6123,12 +7920,18 @@
       <c r="N233" s="7"/>
     </row>
     <row r="234" spans="1:14" ht="15.75">
-      <c r="A234" s="14"/>
-      <c r="B234" s="14"/>
+      <c r="A234" s="14">
+        <v>232</v>
+      </c>
+      <c r="B234" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C234" s="15"/>
       <c r="D234" s="12"/>
       <c r="E234" s="13"/>
-      <c r="F234" s="14"/>
+      <c r="F234" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G234" s="14"/>
       <c r="H234" s="16"/>
       <c r="I234" s="15"/>
@@ -6139,12 +7942,18 @@
       <c r="N234" s="7"/>
     </row>
     <row r="235" spans="1:14" ht="15.75">
-      <c r="A235" s="14"/>
-      <c r="B235" s="14"/>
+      <c r="A235" s="14">
+        <v>233</v>
+      </c>
+      <c r="B235" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C235" s="15"/>
       <c r="D235" s="12"/>
       <c r="E235" s="13"/>
-      <c r="F235" s="14"/>
+      <c r="F235" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G235" s="14"/>
       <c r="H235" s="16"/>
       <c r="I235" s="15"/>
@@ -6155,12 +7964,18 @@
       <c r="N235" s="7"/>
     </row>
     <row r="236" spans="1:14" ht="15.75">
-      <c r="A236" s="14"/>
-      <c r="B236" s="14"/>
+      <c r="A236" s="14">
+        <v>234</v>
+      </c>
+      <c r="B236" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C236" s="15"/>
       <c r="D236" s="12"/>
       <c r="E236" s="13"/>
-      <c r="F236" s="14"/>
+      <c r="F236" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G236" s="14"/>
       <c r="H236" s="16"/>
       <c r="I236" s="15"/>
@@ -6171,12 +7986,18 @@
       <c r="N236" s="7"/>
     </row>
     <row r="237" spans="1:14" ht="15.75">
-      <c r="A237" s="14"/>
-      <c r="B237" s="14"/>
+      <c r="A237" s="14">
+        <v>235</v>
+      </c>
+      <c r="B237" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C237" s="15"/>
       <c r="D237" s="12"/>
       <c r="E237" s="13"/>
-      <c r="F237" s="14"/>
+      <c r="F237" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G237" s="14"/>
       <c r="H237" s="16"/>
       <c r="I237" s="15"/>
@@ -6187,12 +8008,18 @@
       <c r="N237" s="7"/>
     </row>
     <row r="238" spans="1:14" ht="15.75">
-      <c r="A238" s="14"/>
-      <c r="B238" s="14"/>
+      <c r="A238" s="14">
+        <v>236</v>
+      </c>
+      <c r="B238" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C238" s="15"/>
       <c r="D238" s="12"/>
       <c r="E238" s="13"/>
-      <c r="F238" s="14"/>
+      <c r="F238" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G238" s="14"/>
       <c r="H238" s="16"/>
       <c r="I238" s="15"/>
@@ -6203,12 +8030,18 @@
       <c r="N238" s="7"/>
     </row>
     <row r="239" spans="1:14" ht="15.75">
-      <c r="A239" s="14"/>
-      <c r="B239" s="14"/>
+      <c r="A239" s="14">
+        <v>237</v>
+      </c>
+      <c r="B239" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C239" s="15"/>
       <c r="D239" s="12"/>
       <c r="E239" s="13"/>
-      <c r="F239" s="14"/>
+      <c r="F239" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G239" s="14"/>
       <c r="H239" s="16"/>
       <c r="I239" s="15"/>
@@ -6219,12 +8052,18 @@
       <c r="N239" s="7"/>
     </row>
     <row r="240" spans="1:14" ht="15.75">
-      <c r="A240" s="14"/>
-      <c r="B240" s="14"/>
+      <c r="A240" s="14">
+        <v>238</v>
+      </c>
+      <c r="B240" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C240" s="15"/>
       <c r="D240" s="12"/>
       <c r="E240" s="13"/>
-      <c r="F240" s="14"/>
+      <c r="F240" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G240" s="14"/>
       <c r="H240" s="16"/>
       <c r="I240" s="15"/>
@@ -6235,12 +8074,18 @@
       <c r="N240" s="7"/>
     </row>
     <row r="241" spans="1:14" ht="15.75">
-      <c r="A241" s="14"/>
-      <c r="B241" s="14"/>
+      <c r="A241" s="14">
+        <v>239</v>
+      </c>
+      <c r="B241" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C241" s="15"/>
       <c r="D241" s="12"/>
       <c r="E241" s="13"/>
-      <c r="F241" s="14"/>
+      <c r="F241" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G241" s="14"/>
       <c r="H241" s="16"/>
       <c r="I241" s="15"/>
@@ -6251,12 +8096,18 @@
       <c r="N241" s="7"/>
     </row>
     <row r="242" spans="1:14" ht="15.75">
-      <c r="A242" s="14"/>
-      <c r="B242" s="14"/>
+      <c r="A242" s="14">
+        <v>240</v>
+      </c>
+      <c r="B242" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C242" s="15"/>
       <c r="D242" s="12"/>
       <c r="E242" s="13"/>
-      <c r="F242" s="14"/>
+      <c r="F242" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G242" s="14"/>
       <c r="H242" s="16"/>
       <c r="I242" s="15"/>
@@ -6267,12 +8118,18 @@
       <c r="N242" s="7"/>
     </row>
     <row r="243" spans="1:14" ht="15.75">
-      <c r="A243" s="14"/>
-      <c r="B243" s="14"/>
+      <c r="A243" s="14">
+        <v>241</v>
+      </c>
+      <c r="B243" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C243" s="15"/>
       <c r="D243" s="12"/>
       <c r="E243" s="13"/>
-      <c r="F243" s="14"/>
+      <c r="F243" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G243" s="14"/>
       <c r="H243" s="16"/>
       <c r="I243" s="15"/>
@@ -6283,12 +8140,18 @@
       <c r="N243" s="7"/>
     </row>
     <row r="244" spans="1:14" ht="15.75">
-      <c r="A244" s="14"/>
-      <c r="B244" s="14"/>
+      <c r="A244" s="14">
+        <v>242</v>
+      </c>
+      <c r="B244" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C244" s="15"/>
       <c r="D244" s="12"/>
       <c r="E244" s="13"/>
-      <c r="F244" s="14"/>
+      <c r="F244" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G244" s="14"/>
       <c r="H244" s="16"/>
       <c r="I244" s="15"/>
@@ -6299,12 +8162,18 @@
       <c r="N244" s="7"/>
     </row>
     <row r="245" spans="1:14" ht="15.75">
-      <c r="A245" s="14"/>
-      <c r="B245" s="14"/>
+      <c r="A245" s="14">
+        <v>243</v>
+      </c>
+      <c r="B245" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C245" s="15"/>
       <c r="D245" s="12"/>
       <c r="E245" s="13"/>
-      <c r="F245" s="14"/>
+      <c r="F245" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G245" s="14"/>
       <c r="H245" s="16"/>
       <c r="I245" s="15"/>
@@ -6315,12 +8184,18 @@
       <c r="N245" s="7"/>
     </row>
     <row r="246" spans="1:14" ht="15.75">
-      <c r="A246" s="14"/>
-      <c r="B246" s="14"/>
+      <c r="A246" s="14">
+        <v>244</v>
+      </c>
+      <c r="B246" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C246" s="15"/>
       <c r="D246" s="12"/>
       <c r="E246" s="13"/>
-      <c r="F246" s="14"/>
+      <c r="F246" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G246" s="14"/>
       <c r="H246" s="16"/>
       <c r="I246" s="15"/>
@@ -6331,12 +8206,18 @@
       <c r="N246" s="7"/>
     </row>
     <row r="247" spans="1:14" ht="15.75">
-      <c r="A247" s="14"/>
-      <c r="B247" s="14"/>
+      <c r="A247" s="14">
+        <v>245</v>
+      </c>
+      <c r="B247" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C247" s="15"/>
       <c r="D247" s="12"/>
       <c r="E247" s="13"/>
-      <c r="F247" s="14"/>
+      <c r="F247" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G247" s="14"/>
       <c r="H247" s="16"/>
       <c r="I247" s="15"/>
@@ -6347,12 +8228,18 @@
       <c r="N247" s="7"/>
     </row>
     <row r="248" spans="1:14" ht="15.75">
-      <c r="A248" s="14"/>
-      <c r="B248" s="14"/>
+      <c r="A248" s="14">
+        <v>246</v>
+      </c>
+      <c r="B248" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C248" s="15"/>
       <c r="D248" s="12"/>
       <c r="E248" s="13"/>
-      <c r="F248" s="14"/>
+      <c r="F248" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G248" s="14"/>
       <c r="H248" s="16"/>
       <c r="I248" s="15"/>
@@ -6363,12 +8250,18 @@
       <c r="N248" s="7"/>
     </row>
     <row r="249" spans="1:14" ht="15.75">
-      <c r="A249" s="14"/>
-      <c r="B249" s="14"/>
+      <c r="A249" s="14">
+        <v>247</v>
+      </c>
+      <c r="B249" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C249" s="15"/>
       <c r="D249" s="12"/>
       <c r="E249" s="13"/>
-      <c r="F249" s="14"/>
+      <c r="F249" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G249" s="14"/>
       <c r="H249" s="16"/>
       <c r="I249" s="15"/>
@@ -6379,12 +8272,18 @@
       <c r="N249" s="7"/>
     </row>
     <row r="250" spans="1:14" ht="15.75">
-      <c r="A250" s="14"/>
-      <c r="B250" s="14"/>
+      <c r="A250" s="14">
+        <v>248</v>
+      </c>
+      <c r="B250" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C250" s="15"/>
       <c r="D250" s="12"/>
       <c r="E250" s="13"/>
-      <c r="F250" s="14"/>
+      <c r="F250" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G250" s="14"/>
       <c r="H250" s="16"/>
       <c r="I250" s="15"/>
@@ -6395,12 +8294,18 @@
       <c r="N250" s="7"/>
     </row>
     <row r="251" spans="1:14" ht="15.75">
-      <c r="A251" s="14"/>
-      <c r="B251" s="14"/>
+      <c r="A251" s="14">
+        <v>249</v>
+      </c>
+      <c r="B251" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C251" s="15"/>
       <c r="D251" s="12"/>
       <c r="E251" s="13"/>
-      <c r="F251" s="14"/>
+      <c r="F251" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G251" s="14"/>
       <c r="H251" s="16"/>
       <c r="I251" s="15"/>
@@ -6411,12 +8316,18 @@
       <c r="N251" s="7"/>
     </row>
     <row r="252" spans="1:14" ht="15.75">
-      <c r="A252" s="14"/>
-      <c r="B252" s="14"/>
+      <c r="A252" s="14">
+        <v>250</v>
+      </c>
+      <c r="B252" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C252" s="15"/>
       <c r="D252" s="12"/>
       <c r="E252" s="13"/>
-      <c r="F252" s="14"/>
+      <c r="F252" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G252" s="14"/>
       <c r="H252" s="16"/>
       <c r="I252" s="15"/>
@@ -6427,12 +8338,18 @@
       <c r="N252" s="7"/>
     </row>
     <row r="253" spans="1:14" ht="15.75">
-      <c r="A253" s="14"/>
-      <c r="B253" s="14"/>
+      <c r="A253" s="14">
+        <v>251</v>
+      </c>
+      <c r="B253" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C253" s="15"/>
       <c r="D253" s="12"/>
       <c r="E253" s="13"/>
-      <c r="F253" s="14"/>
+      <c r="F253" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G253" s="14"/>
       <c r="H253" s="16"/>
       <c r="I253" s="15"/>
@@ -6443,12 +8360,18 @@
       <c r="N253" s="7"/>
     </row>
     <row r="254" spans="1:14" ht="15.75">
-      <c r="A254" s="14"/>
-      <c r="B254" s="14"/>
+      <c r="A254" s="14">
+        <v>252</v>
+      </c>
+      <c r="B254" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C254" s="15"/>
       <c r="D254" s="12"/>
       <c r="E254" s="13"/>
-      <c r="F254" s="14"/>
+      <c r="F254" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G254" s="14"/>
       <c r="H254" s="16"/>
       <c r="I254" s="15"/>
@@ -6459,12 +8382,18 @@
       <c r="N254" s="7"/>
     </row>
     <row r="255" spans="1:14" ht="15.75">
-      <c r="A255" s="14"/>
-      <c r="B255" s="14"/>
+      <c r="A255" s="14">
+        <v>253</v>
+      </c>
+      <c r="B255" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C255" s="15"/>
       <c r="D255" s="12"/>
       <c r="E255" s="13"/>
-      <c r="F255" s="14"/>
+      <c r="F255" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G255" s="14"/>
       <c r="H255" s="16"/>
       <c r="I255" s="15"/>
@@ -6475,12 +8404,18 @@
       <c r="N255" s="7"/>
     </row>
     <row r="256" spans="1:14" ht="15.75">
-      <c r="A256" s="14"/>
-      <c r="B256" s="14"/>
+      <c r="A256" s="14">
+        <v>254</v>
+      </c>
+      <c r="B256" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C256" s="15"/>
       <c r="D256" s="12"/>
       <c r="E256" s="13"/>
-      <c r="F256" s="14"/>
+      <c r="F256" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G256" s="14"/>
       <c r="H256" s="16"/>
       <c r="I256" s="15"/>
@@ -6491,12 +8426,18 @@
       <c r="N256" s="7"/>
     </row>
     <row r="257" spans="1:16" ht="15.75">
-      <c r="A257" s="14"/>
-      <c r="B257" s="14"/>
+      <c r="A257" s="14">
+        <v>255</v>
+      </c>
+      <c r="B257" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C257" s="15"/>
       <c r="D257" s="12"/>
       <c r="E257" s="13"/>
-      <c r="F257" s="14"/>
+      <c r="F257" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G257" s="14"/>
       <c r="H257" s="16"/>
       <c r="I257" s="15"/>
@@ -6507,12 +8448,18 @@
       <c r="N257" s="7"/>
     </row>
     <row r="258" spans="1:16" ht="15.75">
-      <c r="A258" s="14"/>
-      <c r="B258" s="14"/>
+      <c r="A258" s="14">
+        <v>256</v>
+      </c>
+      <c r="B258" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C258" s="15"/>
       <c r="D258" s="12"/>
       <c r="E258" s="13"/>
-      <c r="F258" s="14"/>
+      <c r="F258" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G258" s="14"/>
       <c r="H258" s="16"/>
       <c r="I258" s="15"/>
@@ -6523,12 +8470,18 @@
       <c r="N258" s="7"/>
     </row>
     <row r="259" spans="1:16" ht="15.75">
-      <c r="A259" s="14"/>
-      <c r="B259" s="14"/>
+      <c r="A259" s="14">
+        <v>257</v>
+      </c>
+      <c r="B259" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C259" s="15"/>
       <c r="D259" s="12"/>
       <c r="E259" s="13"/>
-      <c r="F259" s="14"/>
+      <c r="F259" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G259" s="14"/>
       <c r="H259" s="16"/>
       <c r="I259" s="15"/>
@@ -6539,12 +8492,18 @@
       <c r="N259" s="7"/>
     </row>
     <row r="260" spans="1:16" ht="15.75">
-      <c r="A260" s="14"/>
-      <c r="B260" s="14"/>
+      <c r="A260" s="14">
+        <v>258</v>
+      </c>
+      <c r="B260" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C260" s="15"/>
       <c r="D260" s="12"/>
       <c r="E260" s="13"/>
-      <c r="F260" s="14"/>
+      <c r="F260" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G260" s="14"/>
       <c r="H260" s="16"/>
       <c r="I260" s="15"/>
@@ -6555,12 +8514,18 @@
       <c r="N260" s="7"/>
     </row>
     <row r="261" spans="1:16" ht="15.75">
-      <c r="A261" s="14"/>
-      <c r="B261" s="14"/>
+      <c r="A261" s="14">
+        <v>259</v>
+      </c>
+      <c r="B261" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C261" s="15"/>
       <c r="D261" s="12"/>
       <c r="E261" s="13"/>
-      <c r="F261" s="14"/>
+      <c r="F261" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G261" s="14"/>
       <c r="H261" s="16"/>
       <c r="I261" s="15"/>
@@ -6572,12 +8537,18 @@
       <c r="P261" s="35"/>
     </row>
     <row r="262" spans="1:16" ht="15.75">
-      <c r="A262" s="14"/>
-      <c r="B262" s="14"/>
+      <c r="A262" s="14">
+        <v>260</v>
+      </c>
+      <c r="B262" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C262" s="15"/>
       <c r="D262" s="12"/>
       <c r="E262" s="13"/>
-      <c r="F262" s="14"/>
+      <c r="F262" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G262" s="14"/>
       <c r="H262" s="16"/>
       <c r="I262" s="15"/>
@@ -6588,12 +8559,18 @@
       <c r="N262" s="7"/>
     </row>
     <row r="263" spans="1:16" ht="15.75">
-      <c r="A263" s="14"/>
-      <c r="B263" s="14"/>
+      <c r="A263" s="14">
+        <v>261</v>
+      </c>
+      <c r="B263" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C263" s="15"/>
       <c r="D263" s="12"/>
       <c r="E263" s="13"/>
-      <c r="F263" s="14"/>
+      <c r="F263" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G263" s="14"/>
       <c r="H263" s="16"/>
       <c r="I263" s="15"/>
@@ -6604,12 +8581,18 @@
       <c r="N263" s="7"/>
     </row>
     <row r="264" spans="1:16" ht="15.75">
-      <c r="A264" s="14"/>
-      <c r="B264" s="14"/>
+      <c r="A264" s="14">
+        <v>262</v>
+      </c>
+      <c r="B264" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C264" s="15"/>
       <c r="D264" s="12"/>
       <c r="E264" s="13"/>
-      <c r="F264" s="14"/>
+      <c r="F264" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G264" s="14"/>
       <c r="H264" s="16"/>
       <c r="I264" s="15"/>
@@ -6620,12 +8603,18 @@
       <c r="N264" s="14"/>
     </row>
     <row r="265" spans="1:16" ht="15.75">
-      <c r="A265" s="14"/>
-      <c r="B265" s="14"/>
+      <c r="A265" s="14">
+        <v>263</v>
+      </c>
+      <c r="B265" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C265" s="15"/>
       <c r="D265" s="12"/>
       <c r="E265" s="13"/>
-      <c r="F265" s="14"/>
+      <c r="F265" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G265" s="14"/>
       <c r="H265" s="16"/>
       <c r="I265" s="15"/>
@@ -6636,12 +8625,18 @@
       <c r="N265" s="14"/>
     </row>
     <row r="266" spans="1:16" ht="15.75">
-      <c r="A266" s="14"/>
-      <c r="B266" s="14"/>
+      <c r="A266" s="14">
+        <v>264</v>
+      </c>
+      <c r="B266" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C266" s="15"/>
       <c r="D266" s="12"/>
       <c r="E266" s="13"/>
-      <c r="F266" s="14"/>
+      <c r="F266" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G266" s="14"/>
       <c r="H266" s="16"/>
       <c r="I266" s="15"/>
@@ -6652,12 +8647,18 @@
       <c r="N266" s="7"/>
     </row>
     <row r="267" spans="1:16" ht="15.75">
-      <c r="A267" s="14"/>
-      <c r="B267" s="14"/>
+      <c r="A267" s="14">
+        <v>265</v>
+      </c>
+      <c r="B267" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C267" s="15"/>
       <c r="D267" s="12"/>
       <c r="E267" s="13"/>
-      <c r="F267" s="14"/>
+      <c r="F267" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G267" s="14"/>
       <c r="H267" s="16"/>
       <c r="I267" s="15"/>
@@ -6668,12 +8669,18 @@
       <c r="N267" s="7"/>
     </row>
     <row r="268" spans="1:16" ht="15.75">
-      <c r="A268" s="14"/>
-      <c r="B268" s="14"/>
+      <c r="A268" s="14">
+        <v>266</v>
+      </c>
+      <c r="B268" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C268" s="15"/>
       <c r="D268" s="12"/>
       <c r="E268" s="13"/>
-      <c r="F268" s="14"/>
+      <c r="F268" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G268" s="14"/>
       <c r="H268" s="16"/>
       <c r="I268" s="15"/>
@@ -6684,12 +8691,18 @@
       <c r="N268" s="7"/>
     </row>
     <row r="269" spans="1:16" ht="15.75">
-      <c r="A269" s="14"/>
-      <c r="B269" s="14"/>
+      <c r="A269" s="14">
+        <v>267</v>
+      </c>
+      <c r="B269" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C269" s="15"/>
       <c r="D269" s="12"/>
       <c r="E269" s="13"/>
-      <c r="F269" s="14"/>
+      <c r="F269" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G269" s="14"/>
       <c r="H269" s="16"/>
       <c r="I269" s="15"/>
@@ -6700,12 +8713,18 @@
       <c r="N269" s="7"/>
     </row>
     <row r="270" spans="1:16" ht="15.75">
-      <c r="A270" s="14"/>
-      <c r="B270" s="14"/>
+      <c r="A270" s="14">
+        <v>268</v>
+      </c>
+      <c r="B270" s="36" t="s">
+        <v>18</v>
+      </c>
       <c r="C270" s="15"/>
       <c r="D270" s="12"/>
       <c r="E270" s="13"/>
-      <c r="F270" s="14"/>
+      <c r="F270" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="G270" s="14"/>
       <c r="H270" s="16"/>
       <c r="I270" s="15"/>
@@ -6719,7 +8738,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
@@ -6772,7 +8791,7 @@
       </c>
       <c r="B2" s="4">
         <f>COUNTIF('All Record'!$F$2:$F$1048576,"Female")</f>
-        <v>31</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="21">
@@ -6781,7 +8800,7 @@
       </c>
       <c r="B3" s="4">
         <f>COUNTIF('All Record'!$F$2:$F$1048576,"Male")</f>
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="21">
@@ -6790,7 +8809,7 @@
       </c>
       <c r="B4" s="4">
         <f>B2+B3</f>
-        <v>53</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/Sindhi Muslim/Classes/GBPS SJCHS Student Data 2024-2025.xlsx
+++ b/Sindhi Muslim/Classes/GBPS SJCHS Student Data 2024-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21F35D1-949E-4382-B138-0BACB321B5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A457D7C-D9B7-444D-9B90-9D7EA9830693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Class - I" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Record'!$A$2:$N$270</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Record'!$A$2:$N$271</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="375">
   <si>
     <t>STUDENT PROFILE 2024-2025</t>
   </si>
@@ -662,6 +662,504 @@
   </si>
   <si>
     <t>Muhammad Sultan</t>
+  </si>
+  <si>
+    <t>Ayesha</t>
+  </si>
+  <si>
+    <t>Class-9</t>
+  </si>
+  <si>
+    <t>0312-2618279</t>
+  </si>
+  <si>
+    <t>Afsheen Panwar</t>
+  </si>
+  <si>
+    <t>Ubaidullah Panwar</t>
+  </si>
+  <si>
+    <t>45504-7152033-1</t>
+  </si>
+  <si>
+    <t>0313-3592916</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>Muhammad Khan Brohi</t>
+  </si>
+  <si>
+    <t>42501-3772761-1</t>
+  </si>
+  <si>
+    <t>0323-8257746</t>
+  </si>
+  <si>
+    <t>Bibi Khair un Nisa</t>
+  </si>
+  <si>
+    <t>Syed Qutub Ali Shah</t>
+  </si>
+  <si>
+    <t>61101-5662788-7</t>
+  </si>
+  <si>
+    <t>0345-6127462</t>
+  </si>
+  <si>
+    <t>Farasha</t>
+  </si>
+  <si>
+    <t>Javed Ali Janwari</t>
+  </si>
+  <si>
+    <t>43203-1361254-1</t>
+  </si>
+  <si>
+    <t>0315-5513891</t>
+  </si>
+  <si>
+    <t>Haleema</t>
+  </si>
+  <si>
+    <t>Qalandar Bux</t>
+  </si>
+  <si>
+    <t>0315-3608569</t>
+  </si>
+  <si>
+    <t>Kashaf</t>
+  </si>
+  <si>
+    <t>Ali Asghar</t>
+  </si>
+  <si>
+    <t>0300-2779283</t>
+  </si>
+  <si>
+    <t>Mukhtiar Ali</t>
+  </si>
+  <si>
+    <t>43203-1686457-3</t>
+  </si>
+  <si>
+    <t>Maheen Zulfiqar</t>
+  </si>
+  <si>
+    <t>43102-6468973-3</t>
+  </si>
+  <si>
+    <t>Nosheen Panwar</t>
+  </si>
+  <si>
+    <t>Qandeel Zehra</t>
+  </si>
+  <si>
+    <t>Waheed Ali Bhatti</t>
+  </si>
+  <si>
+    <t>0300-3092169</t>
+  </si>
+  <si>
+    <t>Sanam</t>
+  </si>
+  <si>
+    <t>42301-3732301-1</t>
+  </si>
+  <si>
+    <t>0307-2951807</t>
+  </si>
+  <si>
+    <t>Sidra</t>
+  </si>
+  <si>
+    <t>Fida Hussain Solangi</t>
+  </si>
+  <si>
+    <t>0300-2479218</t>
+  </si>
+  <si>
+    <t>Saima</t>
+  </si>
+  <si>
+    <t>42401-6077541-3</t>
+  </si>
+  <si>
+    <t>0370-8250457</t>
+  </si>
+  <si>
+    <t>Salwa</t>
+  </si>
+  <si>
+    <t>42301-1022934-9</t>
+  </si>
+  <si>
+    <t>0312-8691559</t>
+  </si>
+  <si>
+    <t>Tayyaba</t>
+  </si>
+  <si>
+    <t>43302-1123756-9</t>
+  </si>
+  <si>
+    <t>0301-3227511</t>
+  </si>
+  <si>
+    <t>Tuba</t>
+  </si>
+  <si>
+    <t>Yasir Ahmed</t>
+  </si>
+  <si>
+    <t>0319-9299817</t>
+  </si>
+  <si>
+    <t>Zainab</t>
+  </si>
+  <si>
+    <t>Sultan</t>
+  </si>
+  <si>
+    <t>42501-1529307-3</t>
+  </si>
+  <si>
+    <t>0320-2582360</t>
+  </si>
+  <si>
+    <t>Asim</t>
+  </si>
+  <si>
+    <t>Muhammad Hanif</t>
+  </si>
+  <si>
+    <t>0306-2105988</t>
+  </si>
+  <si>
+    <t>Haseeb Ullah</t>
+  </si>
+  <si>
+    <t>Hafeezullah Abro</t>
+  </si>
+  <si>
+    <t>45203-2072186-5</t>
+  </si>
+  <si>
+    <t>0309-7562201</t>
+  </si>
+  <si>
+    <t>Moiz</t>
+  </si>
+  <si>
+    <t>Munawar Ali Bhatti</t>
+  </si>
+  <si>
+    <t>0300-2625466</t>
+  </si>
+  <si>
+    <t>Meesum Abbas Bhatti</t>
+  </si>
+  <si>
+    <t>41306-8696434-5</t>
+  </si>
+  <si>
+    <t>Muhammad Mustaqeem</t>
+  </si>
+  <si>
+    <t>Shamshad Ali</t>
+  </si>
+  <si>
+    <t>42501-9615316-1</t>
+  </si>
+  <si>
+    <t>0303-2607266</t>
+  </si>
+  <si>
+    <t>Mian Muhammad Shayan</t>
+  </si>
+  <si>
+    <t>Jawad Ahmed</t>
+  </si>
+  <si>
+    <t>0337-8292190</t>
+  </si>
+  <si>
+    <t>Mudassir</t>
+  </si>
+  <si>
+    <t>Gulzar Ahmed</t>
+  </si>
+  <si>
+    <t>0307-2271772</t>
+  </si>
+  <si>
+    <t>Manzar Hussain</t>
+  </si>
+  <si>
+    <t>Ghulam Murtaza Hakro</t>
+  </si>
+  <si>
+    <t>43303-7690113-3</t>
+  </si>
+  <si>
+    <t>0324-2203306</t>
+  </si>
+  <si>
+    <t>Noorullah Soomro</t>
+  </si>
+  <si>
+    <t>Abdul Jabbar</t>
+  </si>
+  <si>
+    <t>42501-8527716-5</t>
+  </si>
+  <si>
+    <t>0333-8250222</t>
+  </si>
+  <si>
+    <t>Nawab Khan</t>
+  </si>
+  <si>
+    <t>Shaban</t>
+  </si>
+  <si>
+    <t>Allah Dino</t>
+  </si>
+  <si>
+    <t>42504-5208620-1</t>
+  </si>
+  <si>
+    <t>0304-3528288</t>
+  </si>
+  <si>
+    <t>Shafique Ahmed</t>
+  </si>
+  <si>
+    <t>Rafique Ahmed</t>
+  </si>
+  <si>
+    <t>42000-8965653-1</t>
+  </si>
+  <si>
+    <t>0316-0126957</t>
+  </si>
+  <si>
+    <t>Saif Ur Rehman</t>
+  </si>
+  <si>
+    <t>Taha</t>
+  </si>
+  <si>
+    <t>Israr Ahmed</t>
+  </si>
+  <si>
+    <t>0313-3964544</t>
+  </si>
+  <si>
+    <t>Aijaz Ali</t>
+  </si>
+  <si>
+    <t>41203-5798781-5</t>
+  </si>
+  <si>
+    <t>0309-2877853</t>
+  </si>
+  <si>
+    <t>Zaheer Ali</t>
+  </si>
+  <si>
+    <t>Shah Muhammad</t>
+  </si>
+  <si>
+    <t>Muhammad Sufyan</t>
+  </si>
+  <si>
+    <t>Imran Khan</t>
+  </si>
+  <si>
+    <t>45402-0970980-5</t>
+  </si>
+  <si>
+    <t>0300-2499097</t>
+  </si>
+  <si>
+    <t>Madina</t>
+  </si>
+  <si>
+    <t>Yasir Arafat</t>
+  </si>
+  <si>
+    <t>0300-8238705</t>
+  </si>
+  <si>
+    <t>Abdul Samad</t>
+  </si>
+  <si>
+    <t>Rehmatullah</t>
+  </si>
+  <si>
+    <t>Class-6</t>
+  </si>
+  <si>
+    <t>Danish</t>
+  </si>
+  <si>
+    <t>Muhammad Sameer</t>
+  </si>
+  <si>
+    <t>Abdul Wasay</t>
+  </si>
+  <si>
+    <t>Faisal Ahmed</t>
+  </si>
+  <si>
+    <t>Muhammad Muzammil</t>
+  </si>
+  <si>
+    <t>Muhammad Yaseen</t>
+  </si>
+  <si>
+    <t>Muhammad Younis</t>
+  </si>
+  <si>
+    <t>Irshad Ali</t>
+  </si>
+  <si>
+    <t>Haji Malah</t>
+  </si>
+  <si>
+    <t>Uzair Ahmed</t>
+  </si>
+  <si>
+    <t>Muhammad Tayab</t>
+  </si>
+  <si>
+    <t>Javed Ali</t>
+  </si>
+  <si>
+    <t>Abid Ali</t>
+  </si>
+  <si>
+    <t>Joun Ali</t>
+  </si>
+  <si>
+    <t>Mukhtiar Ahmed</t>
+  </si>
+  <si>
+    <t>Wajid Ali</t>
+  </si>
+  <si>
+    <t>Sana</t>
+  </si>
+  <si>
+    <t>Kaneez Fatima</t>
+  </si>
+  <si>
+    <t>Rizwan</t>
+  </si>
+  <si>
+    <t>Noor-E-Muqaddas</t>
+  </si>
+  <si>
+    <t>Muhammad Idrees</t>
+  </si>
+  <si>
+    <t>Zainab Khatoon</t>
+  </si>
+  <si>
+    <t>Sohrab Khan</t>
+  </si>
+  <si>
+    <t>Noor Fatima</t>
+  </si>
+  <si>
+    <t>Ghulam Yaseen</t>
+  </si>
+  <si>
+    <t>Shaista</t>
+  </si>
+  <si>
+    <t>Naseer Ahmed</t>
+  </si>
+  <si>
+    <t>Naina Naz</t>
+  </si>
+  <si>
+    <t>Shabnam</t>
+  </si>
+  <si>
+    <t>Abdul Hameed</t>
+  </si>
+  <si>
+    <t>Fatima Batool</t>
+  </si>
+  <si>
+    <t>Faiza</t>
+  </si>
+  <si>
+    <t>Muhammad Ghafoor</t>
+  </si>
+  <si>
+    <t>Rubina</t>
+  </si>
+  <si>
+    <t>Rafia</t>
+  </si>
+  <si>
+    <t>Aman Badshah</t>
+  </si>
+  <si>
+    <t>Batool</t>
+  </si>
+  <si>
+    <t>Sawera</t>
+  </si>
+  <si>
+    <t>Abdul Raheem</t>
+  </si>
+  <si>
+    <t>Zara Bano</t>
+  </si>
+  <si>
+    <t>Maham</t>
+  </si>
+  <si>
+    <t>Irfan Zahoor</t>
+  </si>
+  <si>
+    <t>Nabi Bakhsh</t>
+  </si>
+  <si>
+    <t>Mahnoor Fatima</t>
+  </si>
+  <si>
+    <t>Zehra Batool</t>
+  </si>
+  <si>
+    <t>Amna</t>
+  </si>
+  <si>
+    <t>Muskan</t>
+  </si>
+  <si>
+    <t>43105-1119761-1</t>
+  </si>
+  <si>
+    <t>0314-2105908</t>
+  </si>
+  <si>
+    <t>42501-0818042-7</t>
+  </si>
+  <si>
+    <t>0315-8790855</t>
+  </si>
+  <si>
+    <t>45301-9811038-3</t>
+  </si>
+  <si>
+    <t>24301-0852650-7</t>
   </si>
 </sst>
 </file>
@@ -671,12 +1169,26 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -930,69 +1442,76 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1581,7 +2100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P270"/>
+  <dimension ref="A1:P271"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="17" customWidth="1"/>
@@ -1602,22 +2121,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
     </row>
     <row r="2" spans="1:14" s="11" customFormat="1" ht="15.75">
       <c r="A2" s="8" t="s">
@@ -1697,7 +2216,7 @@
       <c r="K3" s="5">
         <v>44441</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="41" t="s">
         <v>122</v>
       </c>
       <c r="M3" s="7"/>
@@ -1739,7 +2258,7 @@
       <c r="K4" s="5">
         <v>44814</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="41" t="s">
         <v>123</v>
       </c>
       <c r="M4" s="7"/>
@@ -1781,7 +2300,7 @@
       <c r="K5" s="5">
         <v>44356</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="41" t="s">
         <v>125</v>
       </c>
       <c r="M5" s="7"/>
@@ -1823,7 +2342,7 @@
       <c r="K6" s="5">
         <v>43381</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="41" t="s">
         <v>126</v>
       </c>
       <c r="M6" s="7"/>
@@ -1865,7 +2384,7 @@
       <c r="K7" s="5">
         <v>44903</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="41" t="s">
         <v>130</v>
       </c>
       <c r="M7" s="7"/>
@@ -1907,7 +2426,7 @@
       <c r="K8" s="5">
         <v>44356</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="41" t="s">
         <v>125</v>
       </c>
       <c r="M8" s="7"/>
@@ -1943,7 +2462,7 @@
         <v>119</v>
       </c>
       <c r="K9" s="5"/>
-      <c r="L9" s="7"/>
+      <c r="L9" s="41"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7" t="s">
         <v>127</v>
@@ -1977,7 +2496,7 @@
         <v>119</v>
       </c>
       <c r="K10" s="5"/>
-      <c r="L10" s="7"/>
+      <c r="L10" s="41"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7" t="s">
         <v>127</v>
@@ -2011,7 +2530,7 @@
         <v>119</v>
       </c>
       <c r="K11" s="5"/>
-      <c r="L11" s="7"/>
+      <c r="L11" s="41"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7" t="s">
         <v>127</v>
@@ -2045,7 +2564,7 @@
         <v>119</v>
       </c>
       <c r="K12" s="5"/>
-      <c r="L12" s="7"/>
+      <c r="L12" s="41"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7" t="s">
         <v>127</v>
@@ -2079,7 +2598,7 @@
         <v>119</v>
       </c>
       <c r="K13" s="5"/>
-      <c r="L13" s="7"/>
+      <c r="L13" s="41"/>
       <c r="M13" s="7"/>
       <c r="N13" s="7" t="s">
         <v>127</v>
@@ -2113,7 +2632,7 @@
         <v>119</v>
       </c>
       <c r="K14" s="5"/>
-      <c r="L14" s="7"/>
+      <c r="L14" s="41"/>
       <c r="M14" s="7"/>
       <c r="N14" s="7" t="s">
         <v>127</v>
@@ -2147,7 +2666,7 @@
         <v>119</v>
       </c>
       <c r="K15" s="5"/>
-      <c r="L15" s="7"/>
+      <c r="L15" s="41"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7" t="s">
         <v>127</v>
@@ -2181,7 +2700,7 @@
         <v>119</v>
       </c>
       <c r="K16" s="5"/>
-      <c r="L16" s="7"/>
+      <c r="L16" s="41"/>
       <c r="M16" s="7"/>
       <c r="N16" s="7" t="s">
         <v>127</v>
@@ -2215,7 +2734,7 @@
         <v>119</v>
       </c>
       <c r="K17" s="5"/>
-      <c r="L17" s="7"/>
+      <c r="L17" s="41"/>
       <c r="M17" s="7"/>
       <c r="N17" s="7" t="s">
         <v>127</v>
@@ -2249,7 +2768,7 @@
         <v>119</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="7"/>
+      <c r="L18" s="41"/>
       <c r="M18" s="7"/>
       <c r="N18" s="7" t="s">
         <v>127</v>
@@ -2283,7 +2802,7 @@
         <v>119</v>
       </c>
       <c r="K19" s="5"/>
-      <c r="L19" s="7"/>
+      <c r="L19" s="41"/>
       <c r="M19" s="7"/>
       <c r="N19" s="7" t="s">
         <v>127</v>
@@ -2317,7 +2836,7 @@
         <v>119</v>
       </c>
       <c r="K20" s="5"/>
-      <c r="L20" s="7"/>
+      <c r="L20" s="41"/>
       <c r="M20" s="7"/>
       <c r="N20" s="7" t="s">
         <v>127</v>
@@ -2351,7 +2870,7 @@
         <v>119</v>
       </c>
       <c r="K21" s="5"/>
-      <c r="L21" s="7"/>
+      <c r="L21" s="41"/>
       <c r="M21" s="7"/>
       <c r="N21" s="7" t="s">
         <v>127</v>
@@ -2385,7 +2904,7 @@
         <v>119</v>
       </c>
       <c r="K22" s="5"/>
-      <c r="L22" s="7"/>
+      <c r="L22" s="41"/>
       <c r="M22" s="7"/>
       <c r="N22" s="7" t="s">
         <v>127</v>
@@ -2419,7 +2938,7 @@
         <v>119</v>
       </c>
       <c r="K23" s="5"/>
-      <c r="L23" s="7"/>
+      <c r="L23" s="41"/>
       <c r="M23" s="7"/>
       <c r="N23" s="7" t="s">
         <v>127</v>
@@ -2453,7 +2972,7 @@
         <v>119</v>
       </c>
       <c r="K24" s="5"/>
-      <c r="L24" s="7"/>
+      <c r="L24" s="41"/>
       <c r="M24" s="7"/>
       <c r="N24" s="7" t="s">
         <v>127</v>
@@ -2487,7 +3006,7 @@
         <v>119</v>
       </c>
       <c r="K25" s="5"/>
-      <c r="L25" s="7"/>
+      <c r="L25" s="41"/>
       <c r="M25" s="7"/>
       <c r="N25" s="7" t="s">
         <v>127</v>
@@ -2521,7 +3040,7 @@
         <v>119</v>
       </c>
       <c r="K26" s="5"/>
-      <c r="L26" s="7"/>
+      <c r="L26" s="41"/>
       <c r="M26" s="7"/>
       <c r="N26" s="7" t="s">
         <v>127</v>
@@ -2555,7 +3074,7 @@
         <v>119</v>
       </c>
       <c r="K27" s="5"/>
-      <c r="L27" s="7"/>
+      <c r="L27" s="41"/>
       <c r="M27" s="7"/>
       <c r="N27" s="7" t="s">
         <v>127</v>
@@ -2589,7 +3108,7 @@
         <v>119</v>
       </c>
       <c r="K28" s="5"/>
-      <c r="L28" s="7"/>
+      <c r="L28" s="41"/>
       <c r="M28" s="7"/>
       <c r="N28" s="7" t="s">
         <v>127</v>
@@ -2623,7 +3142,7 @@
         <v>119</v>
       </c>
       <c r="K29" s="5"/>
-      <c r="L29" s="7"/>
+      <c r="L29" s="41"/>
       <c r="M29" s="7"/>
       <c r="N29" s="7" t="s">
         <v>127</v>
@@ -2657,7 +3176,7 @@
         <v>119</v>
       </c>
       <c r="K30" s="5"/>
-      <c r="L30" s="7"/>
+      <c r="L30" s="41"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7" t="s">
         <v>127</v>
@@ -2691,7 +3210,7 @@
         <v>119</v>
       </c>
       <c r="K31" s="5"/>
-      <c r="L31" s="7"/>
+      <c r="L31" s="41"/>
       <c r="M31" s="7"/>
       <c r="N31" s="7" t="s">
         <v>127</v>
@@ -2725,7 +3244,7 @@
         <v>119</v>
       </c>
       <c r="K32" s="5"/>
-      <c r="L32" s="7"/>
+      <c r="L32" s="41"/>
       <c r="M32" s="7"/>
       <c r="N32" s="7" t="s">
         <v>127</v>
@@ -2759,7 +3278,7 @@
         <v>119</v>
       </c>
       <c r="K33" s="5"/>
-      <c r="L33" s="7"/>
+      <c r="L33" s="41"/>
       <c r="M33" s="14"/>
       <c r="N33" s="7" t="s">
         <v>127</v>
@@ -2793,7 +3312,7 @@
         <v>119</v>
       </c>
       <c r="K34" s="5"/>
-      <c r="L34" s="7"/>
+      <c r="L34" s="41"/>
       <c r="M34" s="7"/>
       <c r="N34" s="7" t="s">
         <v>127</v>
@@ -2827,7 +3346,7 @@
         <v>119</v>
       </c>
       <c r="K35" s="5"/>
-      <c r="L35" s="7"/>
+      <c r="L35" s="41"/>
       <c r="M35" s="7"/>
       <c r="N35" s="7" t="s">
         <v>127</v>
@@ -2861,7 +3380,7 @@
         <v>119</v>
       </c>
       <c r="K36" s="5"/>
-      <c r="L36" s="7"/>
+      <c r="L36" s="41"/>
       <c r="M36" s="7"/>
       <c r="N36" s="7" t="s">
         <v>127</v>
@@ -2895,7 +3414,7 @@
         <v>119</v>
       </c>
       <c r="K37" s="5"/>
-      <c r="L37" s="7"/>
+      <c r="L37" s="41"/>
       <c r="M37" s="7"/>
       <c r="N37" s="7" t="s">
         <v>127</v>
@@ -2929,7 +3448,7 @@
         <v>119</v>
       </c>
       <c r="K38" s="5"/>
-      <c r="L38" s="7"/>
+      <c r="L38" s="41"/>
       <c r="M38" s="7"/>
       <c r="N38" s="7" t="s">
         <v>127</v>
@@ -2963,7 +3482,7 @@
         <v>119</v>
       </c>
       <c r="K39" s="5"/>
-      <c r="L39" s="7"/>
+      <c r="L39" s="41"/>
       <c r="M39" s="7"/>
       <c r="N39" s="7" t="s">
         <v>127</v>
@@ -2997,7 +3516,7 @@
         <v>119</v>
       </c>
       <c r="K40" s="5"/>
-      <c r="L40" s="7"/>
+      <c r="L40" s="41"/>
       <c r="M40" s="7"/>
       <c r="N40" s="7" t="s">
         <v>127</v>
@@ -3031,7 +3550,7 @@
         <v>119</v>
       </c>
       <c r="K41" s="5"/>
-      <c r="L41" s="7"/>
+      <c r="L41" s="41"/>
       <c r="M41" s="20"/>
       <c r="N41" s="7" t="s">
         <v>127</v>
@@ -3065,7 +3584,7 @@
         <v>119</v>
       </c>
       <c r="K42" s="5"/>
-      <c r="L42" s="7"/>
+      <c r="L42" s="41"/>
       <c r="M42" s="7"/>
       <c r="N42" s="7" t="s">
         <v>127</v>
@@ -3099,7 +3618,7 @@
         <v>119</v>
       </c>
       <c r="K43" s="5"/>
-      <c r="L43" s="7"/>
+      <c r="L43" s="41"/>
       <c r="M43" s="7"/>
       <c r="N43" s="7" t="s">
         <v>127</v>
@@ -3133,7 +3652,7 @@
         <v>119</v>
       </c>
       <c r="K44" s="5"/>
-      <c r="L44" s="7"/>
+      <c r="L44" s="41"/>
       <c r="M44" s="7"/>
       <c r="N44" s="7" t="s">
         <v>127</v>
@@ -3167,7 +3686,7 @@
         <v>119</v>
       </c>
       <c r="K45" s="5"/>
-      <c r="L45" s="7"/>
+      <c r="L45" s="41"/>
       <c r="M45" s="7"/>
       <c r="N45" s="7" t="s">
         <v>127</v>
@@ -3201,7 +3720,7 @@
         <v>119</v>
       </c>
       <c r="K46" s="5"/>
-      <c r="L46" s="7"/>
+      <c r="L46" s="41"/>
       <c r="M46" s="7"/>
       <c r="N46" s="7" t="s">
         <v>127</v>
@@ -3235,7 +3754,7 @@
         <v>119</v>
       </c>
       <c r="K47" s="5"/>
-      <c r="L47" s="7"/>
+      <c r="L47" s="41"/>
       <c r="M47" s="7"/>
       <c r="N47" s="7" t="s">
         <v>127</v>
@@ -3269,7 +3788,7 @@
         <v>119</v>
       </c>
       <c r="K48" s="5"/>
-      <c r="L48" s="7"/>
+      <c r="L48" s="41"/>
       <c r="M48" s="7"/>
       <c r="N48" s="7" t="s">
         <v>127</v>
@@ -3303,7 +3822,7 @@
         <v>119</v>
       </c>
       <c r="K49" s="5"/>
-      <c r="L49" s="7"/>
+      <c r="L49" s="41"/>
       <c r="M49" s="7"/>
       <c r="N49" s="7" t="s">
         <v>127</v>
@@ -3337,7 +3856,7 @@
         <v>119</v>
       </c>
       <c r="K50" s="5"/>
-      <c r="L50" s="7"/>
+      <c r="L50" s="41"/>
       <c r="M50" s="7"/>
       <c r="N50" s="7" t="s">
         <v>127</v>
@@ -3371,7 +3890,7 @@
         <v>119</v>
       </c>
       <c r="K51" s="5"/>
-      <c r="L51" s="7"/>
+      <c r="L51" s="41"/>
       <c r="M51" s="7"/>
       <c r="N51" s="7" t="s">
         <v>127</v>
@@ -3405,7 +3924,7 @@
         <v>119</v>
       </c>
       <c r="K52" s="5"/>
-      <c r="L52" s="7"/>
+      <c r="L52" s="41"/>
       <c r="M52" s="7"/>
       <c r="N52" s="7" t="s">
         <v>127</v>
@@ -3439,7 +3958,7 @@
         <v>119</v>
       </c>
       <c r="K53" s="16"/>
-      <c r="L53" s="7"/>
+      <c r="L53" s="41"/>
       <c r="M53" s="14"/>
       <c r="N53" s="7" t="s">
         <v>127</v>
@@ -3473,7 +3992,7 @@
         <v>119</v>
       </c>
       <c r="K54" s="16"/>
-      <c r="L54" s="7"/>
+      <c r="L54" s="41"/>
       <c r="M54" s="14"/>
       <c r="N54" s="7" t="s">
         <v>127</v>
@@ -3507,7 +4026,7 @@
         <v>119</v>
       </c>
       <c r="K55" s="5"/>
-      <c r="L55" s="7"/>
+      <c r="L55" s="41"/>
       <c r="M55" s="14"/>
       <c r="N55" s="7" t="s">
         <v>127</v>
@@ -3527,17 +4046,21 @@
       <c r="E56" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="F56" s="41" t="s">
+      <c r="F56" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G56" s="41" t="s">
+      <c r="G56" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H56" s="16"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="14"/>
+      <c r="I56" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J56" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K56" s="16"/>
-      <c r="L56" s="7"/>
+      <c r="L56" s="41"/>
       <c r="M56" s="29"/>
       <c r="N56" s="7"/>
     </row>
@@ -3555,21 +4078,25 @@
       <c r="E57" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="F57" s="41" t="s">
+      <c r="F57" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G57" s="41" t="s">
+      <c r="G57" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H57" s="16"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="14"/>
+      <c r="I57" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J57" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K57" s="16"/>
-      <c r="L57" s="7"/>
+      <c r="L57" s="41"/>
       <c r="M57" s="14"/>
       <c r="N57" s="7"/>
     </row>
-    <row r="58" spans="1:14" ht="15.75">
+    <row r="58" spans="1:14">
       <c r="A58" s="14">
         <v>56</v>
       </c>
@@ -3583,17 +4110,21 @@
       <c r="E58" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="F58" s="41" t="s">
+      <c r="F58" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G58" s="41" t="s">
+      <c r="G58" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H58" s="16"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="14"/>
+      <c r="I58" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J58" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K58" s="16"/>
-      <c r="L58" s="7"/>
+      <c r="L58" s="41"/>
       <c r="M58" s="14"/>
       <c r="N58" s="14"/>
     </row>
@@ -3611,21 +4142,25 @@
       <c r="E59" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="F59" s="41" t="s">
+      <c r="F59" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G59" s="41" t="s">
+      <c r="G59" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H59" s="16"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="14"/>
+      <c r="I59" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J59" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K59" s="16"/>
-      <c r="L59" s="7"/>
+      <c r="L59" s="41"/>
       <c r="M59" s="14"/>
       <c r="N59" s="7"/>
     </row>
-    <row r="60" spans="1:14" ht="15.75">
+    <row r="60" spans="1:14">
       <c r="A60" s="14">
         <v>58</v>
       </c>
@@ -3639,17 +4174,21 @@
       <c r="E60" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="F60" s="41" t="s">
+      <c r="F60" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G60" s="41" t="s">
+      <c r="G60" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H60" s="16"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="14"/>
+      <c r="I60" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J60" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K60" s="16"/>
-      <c r="L60" s="7"/>
+      <c r="L60" s="41"/>
       <c r="M60" s="14"/>
       <c r="N60" s="14"/>
     </row>
@@ -3667,17 +4206,21 @@
       <c r="E61" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="F61" s="41" t="s">
+      <c r="F61" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G61" s="41" t="s">
+      <c r="G61" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H61" s="5"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="14"/>
+      <c r="I61" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J61" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K61" s="16"/>
-      <c r="L61" s="7"/>
+      <c r="L61" s="41"/>
       <c r="M61" s="14"/>
       <c r="N61" s="7"/>
     </row>
@@ -3695,21 +4238,25 @@
       <c r="E62" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F62" s="41" t="s">
+      <c r="F62" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G62" s="41" t="s">
+      <c r="G62" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H62" s="16"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="14"/>
+      <c r="I62" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J62" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K62" s="16"/>
-      <c r="L62" s="7"/>
+      <c r="L62" s="41"/>
       <c r="M62" s="14"/>
       <c r="N62" s="7"/>
     </row>
-    <row r="63" spans="1:14" ht="15.75">
+    <row r="63" spans="1:14">
       <c r="A63" s="14">
         <v>61</v>
       </c>
@@ -3723,21 +4270,25 @@
       <c r="E63" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F63" s="41" t="s">
+      <c r="F63" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G63" s="41" t="s">
+      <c r="G63" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H63" s="16"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="14"/>
+      <c r="I63" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J63" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K63" s="16"/>
-      <c r="L63" s="7"/>
+      <c r="L63" s="41"/>
       <c r="M63" s="14"/>
       <c r="N63" s="14"/>
     </row>
-    <row r="64" spans="1:14" ht="15.75">
+    <row r="64" spans="1:14">
       <c r="A64" s="14">
         <v>62</v>
       </c>
@@ -3751,17 +4302,21 @@
       <c r="E64" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="F64" s="41" t="s">
+      <c r="F64" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G64" s="41" t="s">
+      <c r="G64" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H64" s="16"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="14"/>
+      <c r="I64" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J64" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K64" s="16"/>
-      <c r="L64" s="7"/>
+      <c r="L64" s="41"/>
       <c r="M64" s="14"/>
       <c r="N64" s="14"/>
     </row>
@@ -3779,17 +4334,21 @@
       <c r="E65" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="F65" s="41" t="s">
+      <c r="F65" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G65" s="41" t="s">
+      <c r="G65" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H65" s="16"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="14"/>
+      <c r="I65" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J65" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K65" s="16"/>
-      <c r="L65" s="7"/>
+      <c r="L65" s="41"/>
       <c r="M65" s="14"/>
       <c r="N65" s="7"/>
     </row>
@@ -3807,17 +4366,21 @@
       <c r="E66" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="F66" s="41" t="s">
+      <c r="F66" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G66" s="41" t="s">
+      <c r="G66" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H66" s="16"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="14"/>
+      <c r="I66" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J66" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K66" s="16"/>
-      <c r="L66" s="7"/>
+      <c r="L66" s="41"/>
       <c r="M66" s="14"/>
       <c r="N66" s="7"/>
     </row>
@@ -3835,17 +4398,21 @@
       <c r="E67" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="F67" s="41" t="s">
+      <c r="F67" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G67" s="41" t="s">
+      <c r="G67" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H67" s="16"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="14"/>
+      <c r="I67" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J67" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K67" s="16"/>
-      <c r="L67" s="7"/>
+      <c r="L67" s="41"/>
       <c r="M67" s="14"/>
       <c r="N67" s="7"/>
     </row>
@@ -3863,17 +4430,21 @@
       <c r="E68" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="F68" s="41" t="s">
+      <c r="F68" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G68" s="41" t="s">
+      <c r="G68" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H68" s="16"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="14"/>
+      <c r="I68" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J68" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K68" s="16"/>
-      <c r="L68" s="7"/>
+      <c r="L68" s="41"/>
       <c r="M68" s="14"/>
       <c r="N68" s="7"/>
     </row>
@@ -3891,21 +4462,25 @@
       <c r="E69" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="F69" s="41" t="s">
+      <c r="F69" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G69" s="41" t="s">
+      <c r="G69" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H69" s="16"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="14"/>
+      <c r="I69" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J69" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K69" s="16"/>
-      <c r="L69" s="7"/>
+      <c r="L69" s="41"/>
       <c r="M69" s="14"/>
       <c r="N69" s="7"/>
     </row>
-    <row r="70" spans="1:14" ht="15.75">
+    <row r="70" spans="1:14">
       <c r="A70" s="14">
         <v>68</v>
       </c>
@@ -3919,17 +4494,21 @@
       <c r="E70" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="F70" s="41" t="s">
+      <c r="F70" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G70" s="41" t="s">
+      <c r="G70" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H70" s="16"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="14"/>
+      <c r="I70" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J70" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K70" s="16"/>
-      <c r="L70" s="7"/>
+      <c r="L70" s="41"/>
       <c r="M70" s="14"/>
       <c r="N70" s="14"/>
     </row>
@@ -3947,17 +4526,21 @@
       <c r="E71" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="F71" s="41" t="s">
+      <c r="F71" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G71" s="41" t="s">
+      <c r="G71" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H71" s="16"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="14"/>
+      <c r="I71" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J71" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K71" s="16"/>
-      <c r="L71" s="7"/>
+      <c r="L71" s="41"/>
       <c r="M71" s="14"/>
       <c r="N71" s="7"/>
     </row>
@@ -3975,17 +4558,21 @@
       <c r="E72" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="F72" s="41" t="s">
+      <c r="F72" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G72" s="41" t="s">
+      <c r="G72" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H72" s="16"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="14"/>
+      <c r="I72" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J72" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K72" s="16"/>
-      <c r="L72" s="7"/>
+      <c r="L72" s="41"/>
       <c r="M72" s="14"/>
       <c r="N72" s="7"/>
     </row>
@@ -4003,17 +4590,21 @@
       <c r="E73" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="F73" s="41" t="s">
+      <c r="F73" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G73" s="41" t="s">
+      <c r="G73" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H73" s="16"/>
-      <c r="I73" s="15"/>
-      <c r="J73" s="14"/>
+      <c r="I73" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J73" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K73" s="16"/>
-      <c r="L73" s="7"/>
+      <c r="L73" s="41"/>
       <c r="M73" s="14"/>
       <c r="N73" s="7"/>
     </row>
@@ -4031,17 +4622,21 @@
       <c r="E74" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="F74" s="41" t="s">
+      <c r="F74" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G74" s="41" t="s">
+      <c r="G74" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H74" s="16"/>
-      <c r="I74" s="15"/>
-      <c r="J74" s="14"/>
+      <c r="I74" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J74" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K74" s="16"/>
-      <c r="L74" s="7"/>
+      <c r="L74" s="41"/>
       <c r="M74" s="14"/>
       <c r="N74" s="7"/>
     </row>
@@ -4059,17 +4654,21 @@
       <c r="E75" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="F75" s="41" t="s">
+      <c r="F75" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G75" s="41" t="s">
+      <c r="G75" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H75" s="16"/>
-      <c r="I75" s="15"/>
-      <c r="J75" s="14"/>
+      <c r="I75" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J75" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K75" s="16"/>
-      <c r="L75" s="7"/>
+      <c r="L75" s="41"/>
       <c r="M75" s="14"/>
       <c r="N75" s="7"/>
     </row>
@@ -4087,17 +4686,21 @@
       <c r="E76" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F76" s="41" t="s">
+      <c r="F76" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G76" s="41" t="s">
+      <c r="G76" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H76" s="16"/>
-      <c r="I76" s="15"/>
-      <c r="J76" s="14"/>
+      <c r="I76" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J76" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K76" s="16"/>
-      <c r="L76" s="7"/>
+      <c r="L76" s="41"/>
       <c r="M76" s="14"/>
       <c r="N76" s="7"/>
     </row>
@@ -4115,17 +4718,21 @@
       <c r="E77" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="F77" s="41" t="s">
+      <c r="F77" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G77" s="41" t="s">
+      <c r="G77" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H77" s="16"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="14"/>
+      <c r="I77" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J77" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K77" s="16"/>
-      <c r="L77" s="7"/>
+      <c r="L77" s="41"/>
       <c r="M77" s="14"/>
       <c r="N77" s="7"/>
     </row>
@@ -4143,17 +4750,21 @@
       <c r="E78" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="F78" s="41" t="s">
+      <c r="F78" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G78" s="41" t="s">
+      <c r="G78" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H78" s="16"/>
-      <c r="I78" s="15"/>
-      <c r="J78" s="14"/>
+      <c r="I78" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J78" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K78" s="16"/>
-      <c r="L78" s="7"/>
+      <c r="L78" s="41"/>
       <c r="M78" s="14"/>
       <c r="N78" s="7"/>
     </row>
@@ -4171,17 +4782,21 @@
       <c r="E79" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="F79" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G79" s="41" t="s">
+      <c r="F79" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G79" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H79" s="16"/>
-      <c r="I79" s="15"/>
-      <c r="J79" s="14"/>
+      <c r="I79" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J79" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K79" s="16"/>
-      <c r="L79" s="7"/>
+      <c r="L79" s="41"/>
       <c r="M79" s="14"/>
       <c r="N79" s="7"/>
     </row>
@@ -4199,17 +4814,21 @@
       <c r="E80" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F80" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G80" s="41" t="s">
+      <c r="F80" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G80" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H80" s="5"/>
-      <c r="I80" s="15"/>
-      <c r="J80" s="14"/>
+      <c r="I80" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J80" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K80" s="16"/>
-      <c r="L80" s="7"/>
+      <c r="L80" s="41"/>
       <c r="M80" s="7"/>
       <c r="N80" s="7"/>
     </row>
@@ -4227,17 +4846,21 @@
       <c r="E81" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="F81" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G81" s="41" t="s">
+      <c r="F81" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G81" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H81" s="16"/>
-      <c r="I81" s="15"/>
-      <c r="J81" s="14"/>
+      <c r="I81" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J81" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K81" s="16"/>
-      <c r="L81" s="7"/>
+      <c r="L81" s="41"/>
       <c r="M81" s="30"/>
       <c r="N81" s="7"/>
     </row>
@@ -4255,17 +4878,21 @@
       <c r="E82" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="F82" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G82" s="41" t="s">
+      <c r="F82" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G82" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H82" s="16"/>
-      <c r="I82" s="15"/>
-      <c r="J82" s="14"/>
+      <c r="I82" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J82" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K82" s="16"/>
-      <c r="L82" s="7"/>
+      <c r="L82" s="41"/>
       <c r="M82" s="14"/>
       <c r="N82" s="7"/>
     </row>
@@ -4283,17 +4910,21 @@
       <c r="E83" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="F83" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G83" s="41" t="s">
+      <c r="F83" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G83" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H83" s="16"/>
-      <c r="I83" s="15"/>
-      <c r="J83" s="14"/>
+      <c r="I83" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J83" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K83" s="16"/>
-      <c r="L83" s="7"/>
+      <c r="L83" s="41"/>
       <c r="M83" s="14"/>
       <c r="N83" s="7"/>
     </row>
@@ -4311,21 +4942,25 @@
       <c r="E84" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F84" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G84" s="41" t="s">
+      <c r="F84" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G84" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H84" s="16"/>
-      <c r="I84" s="15"/>
-      <c r="J84" s="14"/>
+      <c r="I84" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J84" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K84" s="16"/>
-      <c r="L84" s="7"/>
+      <c r="L84" s="41"/>
       <c r="M84" s="30"/>
       <c r="N84" s="7"/>
     </row>
-    <row r="85" spans="1:14" ht="15.75">
+    <row r="85" spans="1:14">
       <c r="A85" s="14">
         <v>83</v>
       </c>
@@ -4339,21 +4974,25 @@
       <c r="E85" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="F85" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G85" s="41" t="s">
+      <c r="F85" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G85" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H85" s="16"/>
-      <c r="I85" s="15"/>
-      <c r="J85" s="14"/>
+      <c r="I85" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J85" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K85" s="16"/>
-      <c r="L85" s="7"/>
+      <c r="L85" s="41"/>
       <c r="M85" s="14"/>
       <c r="N85" s="14"/>
     </row>
-    <row r="86" spans="1:14" ht="15.75">
+    <row r="86" spans="1:14">
       <c r="A86" s="14">
         <v>84</v>
       </c>
@@ -4367,17 +5006,21 @@
       <c r="E86" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="F86" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G86" s="41" t="s">
+      <c r="F86" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G86" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H86" s="16"/>
-      <c r="I86" s="15"/>
-      <c r="J86" s="14"/>
+      <c r="I86" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J86" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K86" s="16"/>
-      <c r="L86" s="7"/>
+      <c r="L86" s="41"/>
       <c r="M86" s="14"/>
       <c r="N86" s="14"/>
     </row>
@@ -4395,21 +5038,25 @@
       <c r="E87" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="F87" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G87" s="41" t="s">
+      <c r="F87" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G87" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H87" s="16"/>
-      <c r="I87" s="15"/>
-      <c r="J87" s="14"/>
+      <c r="I87" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J87" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K87" s="5"/>
-      <c r="L87" s="7"/>
+      <c r="L87" s="41"/>
       <c r="M87" s="14"/>
       <c r="N87" s="7"/>
     </row>
-    <row r="88" spans="1:14" ht="15.75">
+    <row r="88" spans="1:14">
       <c r="A88" s="14">
         <v>86</v>
       </c>
@@ -4423,21 +5070,25 @@
       <c r="E88" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F88" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G88" s="41" t="s">
+      <c r="F88" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G88" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H88" s="16"/>
-      <c r="I88" s="15"/>
-      <c r="J88" s="14"/>
+      <c r="I88" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J88" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K88" s="16"/>
-      <c r="L88" s="7"/>
+      <c r="L88" s="41"/>
       <c r="M88" s="14"/>
       <c r="N88" s="14"/>
     </row>
-    <row r="89" spans="1:14" ht="15.75">
+    <row r="89" spans="1:14">
       <c r="A89" s="14">
         <v>87</v>
       </c>
@@ -4451,17 +5102,21 @@
       <c r="E89" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="F89" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G89" s="41" t="s">
+      <c r="F89" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G89" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H89" s="16"/>
-      <c r="I89" s="15"/>
-      <c r="J89" s="14"/>
+      <c r="I89" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J89" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K89" s="16"/>
-      <c r="L89" s="7"/>
+      <c r="L89" s="41"/>
       <c r="M89" s="14"/>
       <c r="N89" s="14"/>
     </row>
@@ -4479,17 +5134,21 @@
       <c r="E90" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="F90" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G90" s="41" t="s">
+      <c r="F90" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G90" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H90" s="16"/>
-      <c r="I90" s="15"/>
-      <c r="J90" s="14"/>
+      <c r="I90" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J90" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K90" s="16"/>
-      <c r="L90" s="7"/>
+      <c r="L90" s="41"/>
       <c r="M90" s="14"/>
       <c r="N90" s="7"/>
     </row>
@@ -4507,21 +5166,25 @@
       <c r="E91" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="F91" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G91" s="41" t="s">
+      <c r="F91" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G91" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H91" s="16"/>
-      <c r="I91" s="15"/>
-      <c r="J91" s="14"/>
+      <c r="I91" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J91" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K91" s="16"/>
-      <c r="L91" s="7"/>
+      <c r="L91" s="41"/>
       <c r="M91" s="14"/>
       <c r="N91" s="7"/>
     </row>
-    <row r="92" spans="1:14" ht="15.75">
+    <row r="92" spans="1:14">
       <c r="A92" s="14">
         <v>90</v>
       </c>
@@ -4535,17 +5198,21 @@
       <c r="E92" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F92" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G92" s="41" t="s">
+      <c r="F92" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G92" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H92" s="16"/>
-      <c r="I92" s="15"/>
-      <c r="J92" s="14"/>
+      <c r="I92" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J92" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K92" s="16"/>
-      <c r="L92" s="7"/>
+      <c r="L92" s="41"/>
       <c r="M92" s="14"/>
       <c r="N92" s="14"/>
     </row>
@@ -4563,17 +5230,21 @@
       <c r="E93" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F93" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G93" s="41" t="s">
+      <c r="F93" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G93" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H93" s="16"/>
-      <c r="I93" s="15"/>
-      <c r="J93" s="14"/>
+      <c r="I93" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J93" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K93" s="16"/>
-      <c r="L93" s="7"/>
+      <c r="L93" s="41"/>
       <c r="M93" s="14"/>
       <c r="N93" s="7"/>
     </row>
@@ -4591,17 +5262,21 @@
       <c r="E94" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="F94" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G94" s="41" t="s">
+      <c r="F94" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G94" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H94" s="16"/>
-      <c r="I94" s="15"/>
-      <c r="J94" s="14"/>
+      <c r="I94" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J94" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K94" s="16"/>
-      <c r="L94" s="7"/>
+      <c r="L94" s="41"/>
       <c r="M94" s="14"/>
       <c r="N94" s="7"/>
     </row>
@@ -4619,21 +5294,25 @@
       <c r="E95" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="F95" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G95" s="41" t="s">
+      <c r="F95" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G95" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H95" s="16"/>
-      <c r="I95" s="15"/>
-      <c r="J95" s="14"/>
+      <c r="I95" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J95" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K95" s="16"/>
-      <c r="L95" s="7"/>
+      <c r="L95" s="41"/>
       <c r="M95" s="14"/>
       <c r="N95" s="7"/>
     </row>
-    <row r="96" spans="1:14" ht="15.75">
+    <row r="96" spans="1:14">
       <c r="A96" s="14">
         <v>94</v>
       </c>
@@ -4647,17 +5326,21 @@
       <c r="E96" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="F96" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G96" s="41" t="s">
+      <c r="F96" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G96" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H96" s="16"/>
-      <c r="I96" s="15"/>
-      <c r="J96" s="14"/>
+      <c r="I96" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J96" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K96" s="16"/>
-      <c r="L96" s="7"/>
+      <c r="L96" s="41"/>
       <c r="M96" s="14"/>
       <c r="N96" s="14"/>
     </row>
@@ -4675,21 +5358,25 @@
       <c r="E97" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="F97" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G97" s="41" t="s">
+      <c r="F97" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G97" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H97" s="16"/>
-      <c r="I97" s="15"/>
-      <c r="J97" s="14"/>
+      <c r="I97" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J97" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K97" s="16"/>
-      <c r="L97" s="7"/>
+      <c r="L97" s="41"/>
       <c r="M97" s="14"/>
       <c r="N97" s="7"/>
     </row>
-    <row r="98" spans="1:14" ht="15.75">
+    <row r="98" spans="1:14">
       <c r="A98" s="14">
         <v>96</v>
       </c>
@@ -4703,17 +5390,21 @@
       <c r="E98" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="F98" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G98" s="41" t="s">
+      <c r="F98" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G98" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H98" s="16"/>
-      <c r="I98" s="15"/>
-      <c r="J98" s="14"/>
+      <c r="I98" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J98" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K98" s="16"/>
-      <c r="L98" s="7"/>
+      <c r="L98" s="41"/>
       <c r="M98" s="14"/>
       <c r="N98" s="14"/>
     </row>
@@ -4731,17 +5422,21 @@
       <c r="E99" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="F99" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G99" s="41" t="s">
+      <c r="F99" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G99" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H99" s="16"/>
-      <c r="I99" s="15"/>
-      <c r="J99" s="14"/>
+      <c r="I99" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J99" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K99" s="16"/>
-      <c r="L99" s="7"/>
+      <c r="L99" s="41"/>
       <c r="M99" s="14"/>
       <c r="N99" s="7"/>
     </row>
@@ -4759,17 +5454,21 @@
       <c r="E100" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="F100" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G100" s="41" t="s">
+      <c r="F100" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G100" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H100" s="16"/>
-      <c r="I100" s="15"/>
-      <c r="J100" s="14"/>
+      <c r="I100" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J100" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K100" s="16"/>
-      <c r="L100" s="7"/>
+      <c r="L100" s="41"/>
       <c r="M100" s="14"/>
       <c r="N100" s="7"/>
     </row>
@@ -4787,42 +5486,60 @@
       <c r="E101" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="F101" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G101" s="41" t="s">
+      <c r="F101" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G101" s="40" t="s">
         <v>134</v>
       </c>
       <c r="H101" s="16"/>
-      <c r="I101" s="15"/>
-      <c r="J101" s="14"/>
+      <c r="I101" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J101" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K101" s="16"/>
-      <c r="L101" s="7"/>
+      <c r="L101" s="41"/>
       <c r="M101" s="30"/>
       <c r="N101" s="7"/>
     </row>
-    <row r="102" spans="1:14" ht="15.75">
+    <row r="102" spans="1:14">
       <c r="A102" s="14">
         <v>100</v>
       </c>
       <c r="B102" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C102" s="15"/>
-      <c r="D102" s="12"/>
-      <c r="E102" s="13"/>
-      <c r="F102" s="41" t="s">
+      <c r="C102" s="15">
+        <v>858</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F102" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G102" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H102" s="16"/>
-      <c r="I102" s="15"/>
-      <c r="J102" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H102" s="42">
+        <v>39985</v>
+      </c>
+      <c r="I102" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J102" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K102" s="16"/>
-      <c r="L102" s="7"/>
-      <c r="M102" s="14"/>
+      <c r="L102" s="41"/>
+      <c r="M102" s="41" t="s">
+        <v>211</v>
+      </c>
       <c r="N102" s="14"/>
     </row>
     <row r="103" spans="1:14" ht="15.75">
@@ -4832,45 +5549,77 @@
       <c r="B103" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C103" s="15"/>
-      <c r="D103" s="12"/>
-      <c r="E103" s="13"/>
-      <c r="F103" s="41" t="s">
+      <c r="C103" s="15">
+        <v>872</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="F103" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G103" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H103" s="16"/>
-      <c r="I103" s="15"/>
-      <c r="J103" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H103" s="16">
+        <v>39803</v>
+      </c>
+      <c r="I103" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J103" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K103" s="16"/>
-      <c r="L103" s="7"/>
-      <c r="M103" s="14"/>
+      <c r="L103" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="M103" s="41" t="s">
+        <v>215</v>
+      </c>
       <c r="N103" s="7"/>
     </row>
-    <row r="104" spans="1:14" ht="15.75">
+    <row r="104" spans="1:14">
       <c r="A104" s="14">
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C104" s="15"/>
-      <c r="D104" s="12"/>
-      <c r="E104" s="13"/>
-      <c r="F104" s="41" t="s">
+      <c r="C104" s="15">
+        <v>876</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F104" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G104" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H104" s="16"/>
-      <c r="I104" s="15"/>
-      <c r="J104" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H104" s="16">
+        <v>40617</v>
+      </c>
+      <c r="I104" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J104" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K104" s="16"/>
-      <c r="L104" s="7"/>
-      <c r="M104" s="14"/>
+      <c r="L104" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="M104" s="41" t="s">
+        <v>219</v>
+      </c>
       <c r="N104" s="14"/>
     </row>
     <row r="105" spans="1:14" ht="15.75">
@@ -4880,45 +5629,77 @@
       <c r="B105" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C105" s="15"/>
-      <c r="D105" s="12"/>
-      <c r="E105" s="13"/>
-      <c r="F105" s="41" t="s">
+      <c r="C105" s="15">
+        <v>887</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="F105" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G105" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H105" s="16"/>
-      <c r="I105" s="15"/>
-      <c r="J105" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H105" s="16">
+        <v>40091</v>
+      </c>
+      <c r="I105" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J105" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K105" s="16"/>
-      <c r="L105" s="7"/>
-      <c r="M105" s="14"/>
+      <c r="L105" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="M105" s="41" t="s">
+        <v>223</v>
+      </c>
       <c r="N105" s="7"/>
     </row>
-    <row r="106" spans="1:14" ht="15.75">
+    <row r="106" spans="1:14">
       <c r="A106" s="14">
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C106" s="15"/>
-      <c r="D106" s="12"/>
-      <c r="E106" s="13"/>
-      <c r="F106" s="41" t="s">
+      <c r="C106" s="15">
+        <v>884</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E106" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="F106" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G106" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H106" s="16"/>
-      <c r="I106" s="15"/>
-      <c r="J106" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H106" s="16">
+        <v>38884</v>
+      </c>
+      <c r="I106" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J106" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K106" s="16"/>
-      <c r="L106" s="7"/>
-      <c r="M106" s="14"/>
+      <c r="L106" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="M106" s="41" t="s">
+        <v>227</v>
+      </c>
       <c r="N106" s="14"/>
     </row>
     <row r="107" spans="1:14" ht="15.75">
@@ -4928,21 +5709,37 @@
       <c r="B107" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C107" s="15"/>
-      <c r="D107" s="12"/>
-      <c r="E107" s="13"/>
-      <c r="F107" s="41" t="s">
+      <c r="C107" s="15">
+        <v>752</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E107" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="F107" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G107" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H107" s="16"/>
-      <c r="I107" s="15"/>
-      <c r="J107" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H107" s="16">
+        <v>39209</v>
+      </c>
+      <c r="I107" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J107" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K107" s="16"/>
-      <c r="L107" s="7"/>
-      <c r="M107" s="14"/>
+      <c r="L107" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="M107" s="41" t="s">
+        <v>230</v>
+      </c>
       <c r="N107" s="7"/>
     </row>
     <row r="108" spans="1:14" ht="15.75">
@@ -4952,21 +5749,35 @@
       <c r="B108" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C108" s="15"/>
-      <c r="D108" s="12"/>
-      <c r="E108" s="13"/>
-      <c r="F108" s="41" t="s">
+      <c r="C108" s="15">
+        <v>893</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="E108" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="F108" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G108" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H108" s="16"/>
-      <c r="I108" s="15"/>
-      <c r="J108" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H108" s="16">
+        <v>40120</v>
+      </c>
+      <c r="I108" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J108" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K108" s="16"/>
-      <c r="L108" s="7"/>
-      <c r="M108" s="14"/>
+      <c r="L108" s="41"/>
+      <c r="M108" s="41" t="s">
+        <v>233</v>
+      </c>
       <c r="N108" s="7"/>
     </row>
     <row r="109" spans="1:14" ht="15.75">
@@ -4976,20 +5787,34 @@
       <c r="B109" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C109" s="22"/>
-      <c r="D109" s="12"/>
-      <c r="E109" s="13"/>
-      <c r="F109" s="41" t="s">
+      <c r="C109" s="22">
+        <v>897</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E109" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="F109" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G109" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H109" s="16"/>
-      <c r="I109" s="15"/>
-      <c r="J109" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H109" s="16">
+        <v>40619</v>
+      </c>
+      <c r="I109" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J109" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K109" s="16"/>
-      <c r="L109" s="7"/>
+      <c r="L109" s="41" t="s">
+        <v>235</v>
+      </c>
       <c r="M109" s="31"/>
       <c r="N109" s="7"/>
     </row>
@@ -5000,21 +5825,37 @@
       <c r="B110" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C110" s="15"/>
-      <c r="D110" s="12"/>
-      <c r="E110" s="13"/>
-      <c r="F110" s="41" t="s">
+      <c r="C110" s="43">
+        <v>751</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F110" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G110" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H110" s="5"/>
-      <c r="I110" s="15"/>
-      <c r="J110" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H110" s="5">
+        <v>39860</v>
+      </c>
+      <c r="I110" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J110" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K110" s="5"/>
-      <c r="L110" s="7"/>
-      <c r="M110" s="31"/>
+      <c r="L110" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="M110" s="41" t="s">
+        <v>230</v>
+      </c>
       <c r="N110" s="7"/>
     </row>
     <row r="111" spans="1:14" ht="15.75">
@@ -5024,21 +5865,37 @@
       <c r="B111" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C111" s="15"/>
-      <c r="D111" s="12"/>
-      <c r="E111" s="13"/>
-      <c r="F111" s="41" t="s">
+      <c r="C111" s="15">
+        <v>901</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="F111" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G111" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H111" s="16"/>
-      <c r="I111" s="15"/>
-      <c r="J111" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H111" s="16">
+        <v>40625</v>
+      </c>
+      <c r="I111" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J111" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K111" s="32"/>
-      <c r="L111" s="7"/>
-      <c r="M111" s="31"/>
+      <c r="L111" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="M111" s="41" t="s">
+        <v>215</v>
+      </c>
       <c r="N111" s="7"/>
     </row>
     <row r="112" spans="1:14" ht="15.75">
@@ -5048,45 +5905,77 @@
       <c r="B112" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C112" s="15"/>
-      <c r="D112" s="12"/>
-      <c r="E112" s="13"/>
-      <c r="F112" s="41" t="s">
+      <c r="C112" s="15">
+        <v>763</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="F112" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G112" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H112" s="16"/>
-      <c r="I112" s="15"/>
-      <c r="J112" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H112" s="16">
+        <v>40858</v>
+      </c>
+      <c r="I112" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J112" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K112" s="16"/>
-      <c r="L112" s="7"/>
-      <c r="M112" s="31"/>
+      <c r="L112" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="M112" s="41" t="s">
+        <v>241</v>
+      </c>
       <c r="N112" s="7"/>
     </row>
-    <row r="113" spans="1:14" ht="15.75">
+    <row r="113" spans="1:14">
       <c r="A113" s="14">
         <v>111</v>
       </c>
       <c r="B113" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C113" s="15"/>
-      <c r="D113" s="12"/>
-      <c r="E113" s="13"/>
-      <c r="F113" s="41" t="s">
+      <c r="C113" s="15">
+        <v>749</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F113" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G113" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H113" s="16"/>
-      <c r="I113" s="15"/>
-      <c r="J113" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H113" s="16">
+        <v>38913</v>
+      </c>
+      <c r="I113" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J113" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K113" s="16"/>
-      <c r="L113" s="7"/>
-      <c r="M113" s="31"/>
+      <c r="L113" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="M113" s="41" t="s">
+        <v>244</v>
+      </c>
       <c r="N113" s="14"/>
     </row>
     <row r="114" spans="1:14" ht="15.75">
@@ -5096,45 +5985,75 @@
       <c r="B114" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C114" s="15"/>
-      <c r="D114" s="12"/>
-      <c r="E114" s="13"/>
-      <c r="F114" s="41" t="s">
+      <c r="C114" s="15">
+        <v>890</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="E114" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="F114" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G114" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H114" s="16"/>
-      <c r="I114" s="15"/>
-      <c r="J114" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H114" s="16">
+        <v>40913</v>
+      </c>
+      <c r="I114" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J114" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K114" s="16"/>
-      <c r="L114" s="7"/>
-      <c r="M114" s="7"/>
+      <c r="L114" s="41"/>
+      <c r="M114" s="41" t="s">
+        <v>247</v>
+      </c>
       <c r="N114" s="7"/>
     </row>
-    <row r="115" spans="1:14" ht="15.75">
+    <row r="115" spans="1:14">
       <c r="A115" s="14">
         <v>113</v>
       </c>
       <c r="B115" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C115" s="15"/>
-      <c r="D115" s="12"/>
-      <c r="E115" s="13"/>
-      <c r="F115" s="41" t="s">
+      <c r="C115" s="15">
+        <v>889</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F115" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G115" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H115" s="16"/>
-      <c r="I115" s="15"/>
-      <c r="J115" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H115" s="16">
+        <v>40404</v>
+      </c>
+      <c r="I115" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J115" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K115" s="16"/>
-      <c r="L115" s="7"/>
-      <c r="M115" s="31"/>
+      <c r="L115" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="M115" s="41" t="s">
+        <v>250</v>
+      </c>
       <c r="N115" s="14"/>
     </row>
     <row r="116" spans="1:14" ht="15.75">
@@ -5144,21 +6063,37 @@
       <c r="B116" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C116" s="15"/>
-      <c r="D116" s="12"/>
-      <c r="E116" s="13"/>
-      <c r="F116" s="41" t="s">
+      <c r="C116" s="15">
+        <v>898</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F116" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G116" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H116" s="16"/>
-      <c r="I116" s="15"/>
-      <c r="J116" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H116" s="16">
+        <v>40210</v>
+      </c>
+      <c r="I116" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J116" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K116" s="16"/>
-      <c r="L116" s="7"/>
-      <c r="M116" s="33"/>
+      <c r="L116" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="M116" s="41" t="s">
+        <v>253</v>
+      </c>
       <c r="N116" s="7"/>
     </row>
     <row r="117" spans="1:14" ht="15.75">
@@ -5168,21 +6103,37 @@
       <c r="B117" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="15"/>
-      <c r="D117" s="12"/>
-      <c r="E117" s="13"/>
-      <c r="F117" s="41" t="s">
+      <c r="C117" s="15">
+        <v>899</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F117" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G117" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H117" s="16"/>
-      <c r="I117" s="15"/>
-      <c r="J117" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H117" s="16">
+        <v>40919</v>
+      </c>
+      <c r="I117" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J117" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K117" s="16"/>
-      <c r="L117" s="7"/>
-      <c r="M117" s="14"/>
+      <c r="L117" s="41" t="s">
+        <v>255</v>
+      </c>
+      <c r="M117" s="41" t="s">
+        <v>256</v>
+      </c>
       <c r="N117" s="7"/>
     </row>
     <row r="118" spans="1:14" ht="15.75">
@@ -5192,21 +6143,35 @@
       <c r="B118" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C118" s="15"/>
-      <c r="D118" s="12"/>
-      <c r="E118" s="13"/>
-      <c r="F118" s="41" t="s">
+      <c r="C118" s="15">
+        <v>900</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="E118" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="F118" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G118" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H118" s="16"/>
-      <c r="I118" s="15"/>
-      <c r="J118" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H118" s="16">
+        <v>40019</v>
+      </c>
+      <c r="I118" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J118" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K118" s="16"/>
-      <c r="L118" s="7"/>
-      <c r="M118" s="14"/>
+      <c r="L118" s="41"/>
+      <c r="M118" s="41" t="s">
+        <v>259</v>
+      </c>
       <c r="N118" s="7"/>
     </row>
     <row r="119" spans="1:14" ht="15.75">
@@ -5216,21 +6181,37 @@
       <c r="B119" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C119" s="15"/>
-      <c r="D119" s="12"/>
-      <c r="E119" s="13"/>
-      <c r="F119" s="41" t="s">
+      <c r="C119" s="15">
+        <v>756</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E119" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="F119" s="40" t="s">
         <v>58</v>
       </c>
       <c r="G119" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H119" s="16"/>
-      <c r="I119" s="15"/>
-      <c r="J119" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H119" s="16">
+        <v>40179</v>
+      </c>
+      <c r="I119" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J119" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K119" s="16"/>
-      <c r="L119" s="7"/>
-      <c r="M119" s="5"/>
+      <c r="L119" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="M119" s="42" t="s">
+        <v>263</v>
+      </c>
       <c r="N119" s="7"/>
     </row>
     <row r="120" spans="1:14" ht="15.75">
@@ -5241,20 +6222,30 @@
         <v>18</v>
       </c>
       <c r="C120" s="15"/>
-      <c r="D120" s="12"/>
-      <c r="E120" s="13"/>
+      <c r="D120" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="E120" s="13" t="s">
+        <v>317</v>
+      </c>
       <c r="F120" s="41" t="s">
         <v>58</v>
       </c>
       <c r="G120" s="41" t="s">
-        <v>134</v>
+        <v>210</v>
       </c>
       <c r="H120" s="16"/>
-      <c r="I120" s="15"/>
-      <c r="J120" s="14"/>
+      <c r="I120" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J120" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K120" s="16"/>
-      <c r="L120" s="7"/>
-      <c r="M120" s="31"/>
+      <c r="L120" s="41"/>
+      <c r="M120" s="42" t="s">
+        <v>318</v>
+      </c>
       <c r="N120" s="7"/>
     </row>
     <row r="121" spans="1:14" ht="15.75">
@@ -5264,21 +6255,35 @@
       <c r="B121" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C121" s="15"/>
-      <c r="D121" s="12"/>
-      <c r="E121" s="13"/>
+      <c r="C121" s="15">
+        <v>750</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>265</v>
+      </c>
       <c r="F121" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G121" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H121" s="16"/>
-      <c r="I121" s="15"/>
-      <c r="J121" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H121" s="16">
+        <v>40035</v>
+      </c>
+      <c r="I121" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J121" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K121" s="16"/>
-      <c r="L121" s="7"/>
-      <c r="M121" s="31"/>
+      <c r="L121" s="41"/>
+      <c r="M121" s="41" t="s">
+        <v>266</v>
+      </c>
       <c r="N121" s="7"/>
     </row>
     <row r="122" spans="1:14" ht="15.75">
@@ -5288,70 +6293,116 @@
       <c r="B122" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C122" s="15"/>
-      <c r="D122" s="12"/>
-      <c r="E122" s="13"/>
+      <c r="C122" s="15">
+        <v>867</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E122" s="13" t="s">
+        <v>268</v>
+      </c>
       <c r="F122" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G122" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H122" s="16"/>
-      <c r="I122" s="15"/>
-      <c r="J122" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H122" s="16">
+        <v>40219</v>
+      </c>
+      <c r="I122" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J122" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K122" s="16"/>
-      <c r="L122" s="7"/>
-      <c r="M122" s="31"/>
-      <c r="N122" s="14"/>
-    </row>
-    <row r="123" spans="1:14" ht="15.75">
+      <c r="L122" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="M122" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="N122" s="7"/>
+    </row>
+    <row r="123" spans="1:14">
       <c r="A123" s="14">
         <v>121</v>
       </c>
       <c r="B123" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C123" s="15"/>
-      <c r="D123" s="12"/>
-      <c r="E123" s="13"/>
+      <c r="C123" s="15">
+        <v>754</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>272</v>
+      </c>
       <c r="F123" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G123" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H123" s="16"/>
-      <c r="I123" s="15"/>
-      <c r="J123" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H123" s="16">
+        <v>39919</v>
+      </c>
+      <c r="I123" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J123" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K123" s="16"/>
-      <c r="L123" s="7"/>
-      <c r="M123" s="31"/>
+      <c r="L123" s="41"/>
+      <c r="M123" s="41" t="s">
+        <v>273</v>
+      </c>
       <c r="N123" s="14"/>
     </row>
-    <row r="124" spans="1:14" ht="15.75">
+    <row r="124" spans="1:14">
       <c r="A124" s="14">
         <v>122</v>
       </c>
       <c r="B124" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C124" s="15"/>
-      <c r="D124" s="12"/>
-      <c r="E124" s="13"/>
+      <c r="C124" s="15">
+        <v>878</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>240</v>
+      </c>
       <c r="F124" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G124" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H124" s="16"/>
-      <c r="I124" s="15"/>
-      <c r="J124" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H124" s="16">
+        <v>40065</v>
+      </c>
+      <c r="I124" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J124" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K124" s="16"/>
-      <c r="L124" s="5"/>
-      <c r="M124" s="31"/>
-      <c r="N124" s="7"/>
+      <c r="L124" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="M124" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="N124" s="14"/>
     </row>
     <row r="125" spans="1:14" ht="15.75">
       <c r="A125" s="14">
@@ -5360,70 +6411,112 @@
       <c r="B125" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C125" s="15"/>
-      <c r="D125" s="12"/>
-      <c r="E125" s="13"/>
+      <c r="C125" s="15">
+        <v>847</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="E125" s="13" t="s">
+        <v>277</v>
+      </c>
       <c r="F125" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G125" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H125" s="16"/>
-      <c r="I125" s="15"/>
-      <c r="J125" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H125" s="16">
+        <v>39290</v>
+      </c>
+      <c r="I125" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J125" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K125" s="16"/>
-      <c r="L125" s="7"/>
-      <c r="M125" s="31"/>
-      <c r="N125" s="14"/>
-    </row>
-    <row r="126" spans="1:14" ht="15.75">
+      <c r="L125" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="M125" s="41" t="s">
+        <v>279</v>
+      </c>
+      <c r="N125" s="7"/>
+    </row>
+    <row r="126" spans="1:14">
       <c r="A126" s="14">
         <v>124</v>
       </c>
       <c r="B126" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C126" s="15"/>
-      <c r="D126" s="12"/>
-      <c r="E126" s="13"/>
+      <c r="C126" s="15">
+        <v>895</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="E126" s="13" t="s">
+        <v>281</v>
+      </c>
       <c r="F126" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G126" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H126" s="16"/>
-      <c r="I126" s="15"/>
-      <c r="J126" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H126" s="16">
+        <v>39963</v>
+      </c>
+      <c r="I126" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J126" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K126" s="16"/>
-      <c r="L126" s="7"/>
-      <c r="M126" s="31"/>
+      <c r="L126" s="41"/>
+      <c r="M126" s="41" t="s">
+        <v>282</v>
+      </c>
       <c r="N126" s="14"/>
     </row>
-    <row r="127" spans="1:14" ht="15.75">
+    <row r="127" spans="1:14">
       <c r="A127" s="14">
         <v>125</v>
       </c>
       <c r="B127" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C127" s="15"/>
-      <c r="D127" s="12"/>
-      <c r="E127" s="13"/>
+      <c r="C127" s="15">
+        <v>747</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E127" s="13" t="s">
+        <v>284</v>
+      </c>
       <c r="F127" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G127" s="41" t="s">
-        <v>134</v>
+        <v>210</v>
       </c>
       <c r="H127" s="16"/>
-      <c r="I127" s="15"/>
-      <c r="J127" s="14"/>
+      <c r="I127" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J127" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K127" s="16"/>
-      <c r="L127" s="7"/>
-      <c r="M127" s="5"/>
-      <c r="N127" s="7"/>
+      <c r="L127" s="41"/>
+      <c r="M127" s="41" t="s">
+        <v>285</v>
+      </c>
+      <c r="N127" s="14"/>
     </row>
     <row r="128" spans="1:14" ht="15.75">
       <c r="A128" s="14">
@@ -5432,21 +6525,37 @@
       <c r="B128" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C128" s="15"/>
-      <c r="D128" s="12"/>
-      <c r="E128" s="13"/>
+      <c r="C128" s="15">
+        <v>851</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E128" s="13" t="s">
+        <v>287</v>
+      </c>
       <c r="F128" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G128" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H128" s="16"/>
-      <c r="I128" s="15"/>
-      <c r="J128" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H128" s="16">
+        <v>39975</v>
+      </c>
+      <c r="I128" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J128" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K128" s="16"/>
-      <c r="L128" s="7"/>
-      <c r="M128" s="31"/>
+      <c r="L128" s="41" t="s">
+        <v>288</v>
+      </c>
+      <c r="M128" s="42" t="s">
+        <v>289</v>
+      </c>
       <c r="N128" s="7"/>
     </row>
     <row r="129" spans="1:14" ht="15.75">
@@ -5456,46 +6565,78 @@
       <c r="B129" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C129" s="15"/>
-      <c r="D129" s="12"/>
-      <c r="E129" s="13"/>
+      <c r="C129" s="15">
+        <v>882</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>291</v>
+      </c>
       <c r="F129" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G129" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H129" s="16"/>
-      <c r="I129" s="15"/>
-      <c r="J129" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H129" s="16">
+        <v>41189</v>
+      </c>
+      <c r="I129" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J129" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K129" s="16"/>
-      <c r="L129" s="7"/>
-      <c r="M129" s="14"/>
-      <c r="N129" s="14"/>
-    </row>
-    <row r="130" spans="1:14" ht="15.75">
+      <c r="L129" s="41" t="s">
+        <v>292</v>
+      </c>
+      <c r="M129" s="41" t="s">
+        <v>293</v>
+      </c>
+      <c r="N129" s="7"/>
+    </row>
+    <row r="130" spans="1:14">
       <c r="A130" s="14">
         <v>128</v>
       </c>
       <c r="B130" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C130" s="15"/>
-      <c r="D130" s="12"/>
-      <c r="E130" s="13"/>
+      <c r="C130" s="15">
+        <v>877</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="E130" s="13" t="s">
+        <v>217</v>
+      </c>
       <c r="F130" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G130" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H130" s="16"/>
-      <c r="I130" s="15"/>
-      <c r="J130" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H130" s="16">
+        <v>40304</v>
+      </c>
+      <c r="I130" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J130" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K130" s="16"/>
-      <c r="L130" s="7"/>
-      <c r="M130" s="31"/>
-      <c r="N130" s="7"/>
+      <c r="L130" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="M130" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="N130" s="14"/>
     </row>
     <row r="131" spans="1:14" ht="15.75">
       <c r="A131" s="14">
@@ -5504,94 +6645,156 @@
       <c r="B131" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C131" s="15"/>
-      <c r="D131" s="12"/>
-      <c r="E131" s="13"/>
+      <c r="C131" s="15">
+        <v>881</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="E131" s="13" t="s">
+        <v>296</v>
+      </c>
       <c r="F131" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G131" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H131" s="16"/>
-      <c r="I131" s="15"/>
-      <c r="J131" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H131" s="16">
+        <v>39848</v>
+      </c>
+      <c r="I131" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J131" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K131" s="16"/>
-      <c r="L131" s="7"/>
-      <c r="M131" s="31"/>
-      <c r="N131" s="14"/>
-    </row>
-    <row r="132" spans="1:14" ht="15.75">
+      <c r="L131" s="41" t="s">
+        <v>297</v>
+      </c>
+      <c r="M131" s="41" t="s">
+        <v>298</v>
+      </c>
+      <c r="N131" s="7"/>
+    </row>
+    <row r="132" spans="1:14">
       <c r="A132" s="14">
         <v>130</v>
       </c>
       <c r="B132" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C132" s="15"/>
-      <c r="D132" s="12"/>
-      <c r="E132" s="13"/>
+      <c r="C132" s="15">
+        <v>891</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="E132" s="13" t="s">
+        <v>300</v>
+      </c>
       <c r="F132" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G132" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H132" s="16"/>
-      <c r="I132" s="15"/>
-      <c r="J132" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H132" s="16">
+        <v>39636</v>
+      </c>
+      <c r="I132" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J132" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K132" s="16"/>
-      <c r="L132" s="7"/>
-      <c r="M132" s="14"/>
+      <c r="L132" s="41" t="s">
+        <v>301</v>
+      </c>
+      <c r="M132" s="41" t="s">
+        <v>302</v>
+      </c>
       <c r="N132" s="14"/>
     </row>
-    <row r="133" spans="1:14" ht="15.75">
+    <row r="133" spans="1:14">
       <c r="A133" s="14">
         <v>131</v>
       </c>
       <c r="B133" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C133" s="15"/>
-      <c r="D133" s="12"/>
-      <c r="E133" s="13"/>
+      <c r="C133" s="15">
+        <v>896</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="E133" s="13" t="s">
+        <v>53</v>
+      </c>
       <c r="F133" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G133" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H133" s="16"/>
-      <c r="I133" s="15"/>
-      <c r="J133" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H133" s="16">
+        <v>40601</v>
+      </c>
+      <c r="I133" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J133" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K133" s="16"/>
-      <c r="L133" s="7"/>
-      <c r="M133" s="20"/>
+      <c r="L133" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="M133" s="41" t="s">
+        <v>253</v>
+      </c>
       <c r="N133" s="14"/>
     </row>
-    <row r="134" spans="1:14" ht="15.75">
+    <row r="134" spans="1:14">
       <c r="A134" s="14">
         <v>132</v>
       </c>
       <c r="B134" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C134" s="15"/>
-      <c r="D134" s="12"/>
-      <c r="E134" s="13"/>
+      <c r="C134" s="15">
+        <v>765</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="E134" s="13" t="s">
+        <v>305</v>
+      </c>
       <c r="F134" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G134" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H134" s="16"/>
-      <c r="I134" s="15"/>
-      <c r="J134" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H134" s="16">
+        <v>39078</v>
+      </c>
+      <c r="I134" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J134" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K134" s="16"/>
-      <c r="L134" s="7"/>
-      <c r="M134" s="20"/>
-      <c r="N134" s="7"/>
+      <c r="L134" s="41"/>
+      <c r="M134" s="41" t="s">
+        <v>306</v>
+      </c>
+      <c r="N134" s="14"/>
     </row>
     <row r="135" spans="1:14" ht="15.75">
       <c r="A135" s="14">
@@ -5600,21 +6803,37 @@
       <c r="B135" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C135" s="15"/>
-      <c r="D135" s="12"/>
-      <c r="E135" s="13"/>
+      <c r="C135" s="15">
+        <v>894</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E135" s="13" t="s">
+        <v>307</v>
+      </c>
       <c r="F135" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G135" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H135" s="16"/>
-      <c r="I135" s="15"/>
-      <c r="J135" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H135" s="16">
+        <v>39789</v>
+      </c>
+      <c r="I135" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J135" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K135" s="16"/>
-      <c r="L135" s="7"/>
-      <c r="M135" s="31"/>
+      <c r="L135" s="41" t="s">
+        <v>308</v>
+      </c>
+      <c r="M135" s="41" t="s">
+        <v>309</v>
+      </c>
       <c r="N135" s="7"/>
     </row>
     <row r="136" spans="1:14" ht="15.75">
@@ -5624,20 +6843,32 @@
       <c r="B136" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C136" s="15"/>
-      <c r="D136" s="12"/>
-      <c r="E136" s="13"/>
+      <c r="C136" s="15">
+        <v>753</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>311</v>
+      </c>
       <c r="F136" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G136" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H136" s="16"/>
-      <c r="I136" s="15"/>
-      <c r="J136" s="14"/>
-      <c r="K136" s="5"/>
-      <c r="L136" s="7"/>
+        <v>210</v>
+      </c>
+      <c r="H136" s="16">
+        <v>40305</v>
+      </c>
+      <c r="I136" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J136" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K136" s="16"/>
+      <c r="L136" s="41"/>
       <c r="M136" s="31"/>
       <c r="N136" s="7"/>
     </row>
@@ -5648,21 +6879,37 @@
       <c r="B137" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C137" s="15"/>
-      <c r="D137" s="12"/>
-      <c r="E137" s="13"/>
+      <c r="C137" s="15">
+        <v>859</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="E137" s="13" t="s">
+        <v>313</v>
+      </c>
       <c r="F137" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G137" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H137" s="16"/>
-      <c r="I137" s="15"/>
-      <c r="J137" s="14"/>
-      <c r="K137" s="16"/>
-      <c r="L137" s="7"/>
-      <c r="M137" s="5"/>
+        <v>210</v>
+      </c>
+      <c r="H137" s="16">
+        <v>40515</v>
+      </c>
+      <c r="I137" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J137" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K137" s="5"/>
+      <c r="L137" s="41" t="s">
+        <v>314</v>
+      </c>
+      <c r="M137" s="41" t="s">
+        <v>315</v>
+      </c>
       <c r="N137" s="7"/>
     </row>
     <row r="138" spans="1:14" ht="15.75">
@@ -5672,46 +6919,78 @@
       <c r="B138" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C138" s="15"/>
-      <c r="D138" s="12"/>
-      <c r="E138" s="13"/>
+      <c r="C138" s="15">
+        <v>615</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="E138" s="13" t="s">
+        <v>320</v>
+      </c>
       <c r="F138" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G138" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H138" s="16"/>
-      <c r="I138" s="15"/>
-      <c r="J138" s="14"/>
+        <v>57</v>
+      </c>
+      <c r="G138" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="H138" s="16">
+        <v>40774</v>
+      </c>
+      <c r="I138" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J138" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K138" s="16"/>
-      <c r="L138" s="7"/>
-      <c r="M138" s="31"/>
-      <c r="N138" s="14"/>
-    </row>
-    <row r="139" spans="1:14" ht="15.75">
+      <c r="L138" s="44" t="s">
+        <v>369</v>
+      </c>
+      <c r="M138" s="45" t="s">
+        <v>370</v>
+      </c>
+      <c r="N138" s="7"/>
+    </row>
+    <row r="139" spans="1:14">
       <c r="A139" s="14">
         <v>137</v>
       </c>
       <c r="B139" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C139" s="15"/>
-      <c r="D139" s="12"/>
-      <c r="E139" s="13"/>
+      <c r="C139" s="15">
+        <v>343</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="E139" s="13" t="s">
+        <v>24</v>
+      </c>
       <c r="F139" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G139" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H139" s="16"/>
-      <c r="I139" s="15"/>
-      <c r="J139" s="14"/>
+        <v>57</v>
+      </c>
+      <c r="G139" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="H139" s="16">
+        <v>41581</v>
+      </c>
+      <c r="I139" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J139" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K139" s="16"/>
-      <c r="L139" s="7"/>
-      <c r="M139" s="20"/>
-      <c r="N139" s="7"/>
+      <c r="L139" s="44" t="s">
+        <v>371</v>
+      </c>
+      <c r="M139" s="44" t="s">
+        <v>372</v>
+      </c>
+      <c r="N139" s="14"/>
     </row>
     <row r="140" spans="1:14" ht="15.75">
       <c r="A140" s="14">
@@ -5720,21 +6999,35 @@
       <c r="B140" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C140" s="15"/>
-      <c r="D140" s="12"/>
-      <c r="E140" s="13"/>
+      <c r="C140" s="15">
+        <v>565</v>
+      </c>
+      <c r="D140" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="E140" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="F140" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G140" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H140" s="16"/>
-      <c r="I140" s="15"/>
-      <c r="J140" s="14"/>
+        <v>57</v>
+      </c>
+      <c r="G140" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="H140" s="16">
+        <v>41316</v>
+      </c>
+      <c r="I140" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J140" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K140" s="16"/>
-      <c r="L140" s="7"/>
-      <c r="M140" s="5"/>
+      <c r="L140" s="44" t="s">
+        <v>373</v>
+      </c>
+      <c r="M140" s="20"/>
       <c r="N140" s="7"/>
     </row>
     <row r="141" spans="1:14" ht="15.75">
@@ -5744,21 +7037,35 @@
       <c r="B141" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C141" s="22"/>
-      <c r="D141" s="23"/>
-      <c r="E141" s="28"/>
+      <c r="C141" s="15">
+        <v>635</v>
+      </c>
+      <c r="D141" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="E141" s="13" t="s">
+        <v>172</v>
+      </c>
       <c r="F141" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G141" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H141" s="16"/>
-      <c r="I141" s="15"/>
-      <c r="J141" s="14"/>
+        <v>57</v>
+      </c>
+      <c r="G141" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="H141" s="16">
+        <v>41039</v>
+      </c>
+      <c r="I141" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J141" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K141" s="16"/>
-      <c r="L141" s="7"/>
-      <c r="M141" s="31"/>
+      <c r="L141" s="44" t="s">
+        <v>374</v>
+      </c>
+      <c r="M141" s="5"/>
       <c r="N141" s="7"/>
     </row>
     <row r="142" spans="1:14" ht="15.75">
@@ -5768,20 +7075,30 @@
       <c r="B142" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C142" s="15"/>
-      <c r="D142" s="12"/>
-      <c r="E142" s="13"/>
+      <c r="C142" s="22">
+        <v>250</v>
+      </c>
+      <c r="D142" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="E142" s="28" t="s">
+        <v>93</v>
+      </c>
       <c r="F142" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G142" s="41" t="s">
-        <v>134</v>
+        <v>57</v>
+      </c>
+      <c r="G142" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H142" s="16"/>
-      <c r="I142" s="15"/>
-      <c r="J142" s="14"/>
+      <c r="I142" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J142" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K142" s="16"/>
-      <c r="L142" s="7"/>
+      <c r="L142" s="41"/>
       <c r="M142" s="31"/>
       <c r="N142" s="7"/>
     </row>
@@ -5792,46 +7109,66 @@
       <c r="B143" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C143" s="15"/>
-      <c r="D143" s="12"/>
-      <c r="E143" s="13"/>
+      <c r="C143" s="15">
+        <v>616</v>
+      </c>
+      <c r="D143" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E143" s="13" t="s">
+        <v>137</v>
+      </c>
       <c r="F143" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G143" s="41" t="s">
-        <v>134</v>
+        <v>57</v>
+      </c>
+      <c r="G143" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H143" s="16"/>
-      <c r="I143" s="15"/>
-      <c r="J143" s="14"/>
+      <c r="I143" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J143" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K143" s="16"/>
-      <c r="L143" s="7"/>
+      <c r="L143" s="41"/>
       <c r="M143" s="31"/>
-      <c r="N143" s="14"/>
-    </row>
-    <row r="144" spans="1:14" ht="15.75">
+      <c r="N143" s="7"/>
+    </row>
+    <row r="144" spans="1:14">
       <c r="A144" s="14">
         <v>142</v>
       </c>
       <c r="B144" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C144" s="15"/>
-      <c r="D144" s="12"/>
-      <c r="E144" s="13"/>
+      <c r="C144" s="15">
+        <v>347</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="E144" s="13" t="s">
+        <v>328</v>
+      </c>
       <c r="F144" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G144" s="41" t="s">
-        <v>134</v>
+        <v>57</v>
+      </c>
+      <c r="G144" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H144" s="16"/>
-      <c r="I144" s="15"/>
-      <c r="J144" s="14"/>
+      <c r="I144" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J144" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K144" s="16"/>
-      <c r="L144" s="7"/>
+      <c r="L144" s="41"/>
       <c r="M144" s="31"/>
-      <c r="N144" s="7"/>
+      <c r="N144" s="14"/>
     </row>
     <row r="145" spans="1:14" ht="15.75">
       <c r="A145" s="14">
@@ -5840,21 +7177,31 @@
       <c r="B145" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C145" s="15"/>
-      <c r="D145" s="12"/>
-      <c r="E145" s="13"/>
+      <c r="C145" s="15">
+        <v>401</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="E145" s="13" t="s">
+        <v>330</v>
+      </c>
       <c r="F145" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G145" s="41" t="s">
-        <v>134</v>
+        <v>57</v>
+      </c>
+      <c r="G145" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H145" s="16"/>
-      <c r="I145" s="15"/>
-      <c r="J145" s="14"/>
+      <c r="I145" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J145" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K145" s="16"/>
-      <c r="L145" s="7"/>
-      <c r="M145" s="5"/>
+      <c r="L145" s="41"/>
+      <c r="M145" s="31"/>
       <c r="N145" s="7"/>
     </row>
     <row r="146" spans="1:14" ht="15.75">
@@ -5864,70 +7211,100 @@
       <c r="B146" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C146" s="15"/>
-      <c r="D146" s="12"/>
-      <c r="E146" s="13"/>
+      <c r="C146" s="15">
+        <v>568</v>
+      </c>
+      <c r="D146" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="F146" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G146" s="41" t="s">
-        <v>134</v>
+        <v>57</v>
+      </c>
+      <c r="G146" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H146" s="16"/>
-      <c r="I146" s="15"/>
-      <c r="J146" s="14"/>
+      <c r="I146" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J146" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K146" s="16"/>
-      <c r="L146" s="7"/>
-      <c r="M146" s="31"/>
-      <c r="N146" s="14"/>
-    </row>
-    <row r="147" spans="1:14" ht="15.75">
+      <c r="L146" s="41"/>
+      <c r="M146" s="5"/>
+      <c r="N146" s="7"/>
+    </row>
+    <row r="147" spans="1:14">
       <c r="A147" s="14">
         <v>145</v>
       </c>
       <c r="B147" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C147" s="15"/>
-      <c r="D147" s="12"/>
-      <c r="E147" s="13"/>
+      <c r="C147" s="15">
+        <v>715</v>
+      </c>
+      <c r="D147" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="E147" s="13" t="s">
+        <v>333</v>
+      </c>
       <c r="F147" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G147" s="41" t="s">
-        <v>134</v>
+        <v>57</v>
+      </c>
+      <c r="G147" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H147" s="16"/>
-      <c r="I147" s="15"/>
-      <c r="J147" s="14"/>
+      <c r="I147" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J147" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K147" s="16"/>
-      <c r="L147" s="7"/>
+      <c r="L147" s="41"/>
       <c r="M147" s="31"/>
       <c r="N147" s="14"/>
     </row>
-    <row r="148" spans="1:14" ht="15.75">
+    <row r="148" spans="1:14">
       <c r="A148" s="14">
         <v>146</v>
       </c>
       <c r="B148" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C148" s="15"/>
-      <c r="D148" s="12"/>
-      <c r="E148" s="13"/>
+      <c r="C148" s="15">
+        <v>474</v>
+      </c>
+      <c r="D148" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>137</v>
+      </c>
       <c r="F148" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G148" s="41" t="s">
-        <v>134</v>
+        <v>57</v>
+      </c>
+      <c r="G148" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H148" s="16"/>
-      <c r="I148" s="15"/>
-      <c r="J148" s="14"/>
+      <c r="I148" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J148" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K148" s="16"/>
-      <c r="L148" s="7"/>
+      <c r="L148" s="41"/>
       <c r="M148" s="31"/>
-      <c r="N148" s="7"/>
+      <c r="N148" s="14"/>
     </row>
     <row r="149" spans="1:14" ht="15.75">
       <c r="A149" s="14">
@@ -5936,20 +7313,30 @@
       <c r="B149" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C149" s="15"/>
-      <c r="D149" s="12"/>
-      <c r="E149" s="13"/>
+      <c r="C149" s="15">
+        <v>475</v>
+      </c>
+      <c r="D149" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="E149" s="13" t="s">
+        <v>137</v>
+      </c>
       <c r="F149" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G149" s="41" t="s">
-        <v>134</v>
+        <v>57</v>
+      </c>
+      <c r="G149" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H149" s="16"/>
-      <c r="I149" s="15"/>
-      <c r="J149" s="14"/>
+      <c r="I149" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J149" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K149" s="16"/>
-      <c r="L149" s="7"/>
+      <c r="L149" s="41"/>
       <c r="M149" s="31"/>
       <c r="N149" s="7"/>
     </row>
@@ -5960,20 +7347,30 @@
       <c r="B150" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C150" s="15"/>
-      <c r="D150" s="12"/>
-      <c r="E150" s="13"/>
+      <c r="C150" s="15">
+        <v>620</v>
+      </c>
+      <c r="D150" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="E150" s="13" t="s">
+        <v>187</v>
+      </c>
       <c r="F150" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G150" s="41" t="s">
-        <v>134</v>
+        <v>57</v>
+      </c>
+      <c r="G150" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H150" s="16"/>
-      <c r="I150" s="15"/>
-      <c r="J150" s="14"/>
+      <c r="I150" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J150" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K150" s="16"/>
-      <c r="L150" s="7"/>
+      <c r="L150" s="41"/>
       <c r="M150" s="31"/>
       <c r="N150" s="7"/>
     </row>
@@ -5984,45 +7381,65 @@
       <c r="B151" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C151" s="15"/>
-      <c r="D151" s="12"/>
-      <c r="E151" s="13"/>
+      <c r="C151" s="15">
+        <v>426</v>
+      </c>
+      <c r="D151" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E151" s="13" t="s">
+        <v>336</v>
+      </c>
       <c r="F151" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G151" s="41" t="s">
-        <v>134</v>
+        <v>57</v>
+      </c>
+      <c r="G151" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H151" s="16"/>
-      <c r="I151" s="15"/>
-      <c r="J151" s="14"/>
+      <c r="I151" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J151" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K151" s="16"/>
-      <c r="L151" s="7"/>
+      <c r="L151" s="41"/>
       <c r="M151" s="31"/>
-      <c r="N151" s="14"/>
-    </row>
-    <row r="152" spans="1:14" ht="15.75">
+      <c r="N151" s="7"/>
+    </row>
+    <row r="152" spans="1:14">
       <c r="A152" s="14">
         <v>150</v>
       </c>
       <c r="B152" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C152" s="15"/>
-      <c r="D152" s="12"/>
-      <c r="E152" s="13"/>
+      <c r="C152" s="15">
+        <v>790</v>
+      </c>
+      <c r="D152" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="E152" s="13" t="s">
+        <v>151</v>
+      </c>
       <c r="F152" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G152" s="41" t="s">
-        <v>134</v>
+        <v>57</v>
+      </c>
+      <c r="G152" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H152" s="16"/>
-      <c r="I152" s="15"/>
-      <c r="J152" s="14"/>
+      <c r="I152" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J152" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K152" s="16"/>
-      <c r="L152" s="7"/>
-      <c r="M152" s="5"/>
+      <c r="L152" s="41"/>
+      <c r="M152" s="31"/>
       <c r="N152" s="14"/>
     </row>
     <row r="153" spans="1:14" ht="15.75">
@@ -6032,46 +7449,66 @@
       <c r="B153" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C153" s="15"/>
-      <c r="D153" s="12"/>
-      <c r="E153" s="13"/>
-      <c r="F153" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G153" s="41" t="s">
-        <v>134</v>
+      <c r="C153" s="15">
+        <v>436</v>
+      </c>
+      <c r="D153" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="E153" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="F153" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G153" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H153" s="16"/>
-      <c r="I153" s="15"/>
-      <c r="J153" s="14"/>
+      <c r="I153" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J153" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K153" s="16"/>
-      <c r="L153" s="7"/>
-      <c r="M153" s="20"/>
+      <c r="L153" s="41"/>
+      <c r="M153" s="5"/>
       <c r="N153" s="14"/>
     </row>
-    <row r="154" spans="1:14" ht="15.75">
+    <row r="154" spans="1:14">
       <c r="A154" s="14">
         <v>152</v>
       </c>
       <c r="B154" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C154" s="15"/>
-      <c r="D154" s="12"/>
-      <c r="E154" s="13"/>
-      <c r="F154" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G154" s="41" t="s">
-        <v>134</v>
+      <c r="C154" s="15">
+        <v>443</v>
+      </c>
+      <c r="D154" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E154" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="F154" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G154" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H154" s="16"/>
-      <c r="I154" s="15"/>
-      <c r="J154" s="14"/>
-      <c r="K154" s="5"/>
-      <c r="L154" s="7"/>
-      <c r="M154" s="31"/>
-      <c r="N154" s="7"/>
+      <c r="I154" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J154" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K154" s="16"/>
+      <c r="L154" s="41"/>
+      <c r="M154" s="20"/>
+      <c r="N154" s="14"/>
     </row>
     <row r="155" spans="1:14" ht="15.75">
       <c r="A155" s="14">
@@ -6080,21 +7517,31 @@
       <c r="B155" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C155" s="15"/>
-      <c r="D155" s="12"/>
-      <c r="E155" s="13"/>
-      <c r="F155" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G155" s="41" t="s">
-        <v>134</v>
+      <c r="C155" s="15">
+        <v>348</v>
+      </c>
+      <c r="D155" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="E155" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="F155" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G155" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H155" s="16"/>
-      <c r="I155" s="15"/>
-      <c r="J155" s="14"/>
+      <c r="I155" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J155" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K155" s="5"/>
-      <c r="L155" s="7"/>
-      <c r="M155" s="5"/>
+      <c r="L155" s="41"/>
+      <c r="M155" s="31"/>
       <c r="N155" s="7"/>
     </row>
     <row r="156" spans="1:14" ht="15.75">
@@ -6104,21 +7551,31 @@
       <c r="B156" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C156" s="15"/>
-      <c r="D156" s="12"/>
-      <c r="E156" s="13"/>
-      <c r="F156" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G156" s="41" t="s">
-        <v>134</v>
+      <c r="C156" s="15">
+        <v>619</v>
+      </c>
+      <c r="D156" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="E156" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="F156" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G156" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H156" s="16"/>
-      <c r="I156" s="15"/>
-      <c r="J156" s="14"/>
-      <c r="K156" s="16"/>
-      <c r="L156" s="7"/>
-      <c r="M156" s="31"/>
+      <c r="I156" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J156" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K156" s="5"/>
+      <c r="L156" s="41"/>
+      <c r="M156" s="5"/>
       <c r="N156" s="7"/>
     </row>
     <row r="157" spans="1:14" ht="15.75">
@@ -6128,22 +7585,32 @@
       <c r="B157" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C157" s="15"/>
-      <c r="D157" s="12"/>
-      <c r="E157" s="13"/>
-      <c r="F157" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G157" s="41" t="s">
-        <v>134</v>
+      <c r="C157" s="15">
+        <v>442</v>
+      </c>
+      <c r="D157" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="E157" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="F157" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G157" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H157" s="16"/>
-      <c r="I157" s="15"/>
-      <c r="J157" s="14"/>
+      <c r="I157" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J157" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K157" s="16"/>
-      <c r="L157" s="7"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="14"/>
+      <c r="L157" s="41"/>
+      <c r="M157" s="31"/>
+      <c r="N157" s="7"/>
     </row>
     <row r="158" spans="1:14" ht="15.75">
       <c r="A158" s="14">
@@ -6152,20 +7619,30 @@
       <c r="B158" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C158" s="15"/>
-      <c r="D158" s="12"/>
-      <c r="E158" s="13"/>
-      <c r="F158" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G158" s="41" t="s">
-        <v>134</v>
+      <c r="C158" s="15">
+        <v>618</v>
+      </c>
+      <c r="D158" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="E158" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="F158" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G158" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H158" s="16"/>
-      <c r="I158" s="15"/>
-      <c r="J158" s="14"/>
+      <c r="I158" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J158" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K158" s="16"/>
-      <c r="L158" s="7"/>
+      <c r="L158" s="41"/>
       <c r="M158" s="5"/>
       <c r="N158" s="14"/>
     </row>
@@ -6176,22 +7653,32 @@
       <c r="B159" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C159" s="15"/>
-      <c r="D159" s="12"/>
-      <c r="E159" s="13"/>
-      <c r="F159" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G159" s="41" t="s">
-        <v>134</v>
+      <c r="C159" s="15">
+        <v>633</v>
+      </c>
+      <c r="D159" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="E159" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="F159" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G159" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H159" s="16"/>
-      <c r="I159" s="15"/>
-      <c r="J159" s="14"/>
+      <c r="I159" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J159" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K159" s="16"/>
-      <c r="L159" s="7"/>
+      <c r="L159" s="41"/>
       <c r="M159" s="5"/>
-      <c r="N159" s="7"/>
+      <c r="N159" s="14"/>
     </row>
     <row r="160" spans="1:14" ht="15.75">
       <c r="A160" s="14">
@@ -6200,46 +7687,66 @@
       <c r="B160" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C160" s="15"/>
-      <c r="D160" s="12"/>
-      <c r="E160" s="13"/>
-      <c r="F160" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G160" s="41" t="s">
-        <v>134</v>
+      <c r="C160" s="15">
+        <v>614</v>
+      </c>
+      <c r="D160" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E160" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F160" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G160" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H160" s="16"/>
-      <c r="I160" s="15"/>
-      <c r="J160" s="14"/>
+      <c r="I160" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J160" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K160" s="16"/>
-      <c r="L160" s="7"/>
-      <c r="M160" s="14"/>
-      <c r="N160" s="14"/>
-    </row>
-    <row r="161" spans="1:14" ht="15.75">
+      <c r="L160" s="41"/>
+      <c r="M160" s="5"/>
+      <c r="N160" s="7"/>
+    </row>
+    <row r="161" spans="1:14">
       <c r="A161" s="14">
         <v>159</v>
       </c>
       <c r="B161" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C161" s="15"/>
-      <c r="D161" s="12"/>
-      <c r="E161" s="13"/>
-      <c r="F161" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G161" s="41" t="s">
-        <v>134</v>
+      <c r="C161" s="15">
+        <v>778</v>
+      </c>
+      <c r="D161" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="E161" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F161" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G161" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H161" s="16"/>
-      <c r="I161" s="15"/>
-      <c r="J161" s="14"/>
+      <c r="I161" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J161" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K161" s="16"/>
-      <c r="L161" s="7"/>
+      <c r="L161" s="41"/>
       <c r="M161" s="14"/>
-      <c r="N161" s="7"/>
+      <c r="N161" s="14"/>
     </row>
     <row r="162" spans="1:14" ht="15.75">
       <c r="A162" s="14">
@@ -6248,20 +7755,30 @@
       <c r="B162" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C162" s="15"/>
-      <c r="D162" s="12"/>
-      <c r="E162" s="13"/>
-      <c r="F162" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G162" s="41" t="s">
-        <v>134</v>
+      <c r="C162" s="15">
+        <v>379</v>
+      </c>
+      <c r="D162" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="E162" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="F162" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G162" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H162" s="16"/>
-      <c r="I162" s="15"/>
-      <c r="J162" s="14"/>
-      <c r="K162" s="5"/>
-      <c r="L162" s="7"/>
+      <c r="I162" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J162" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K162" s="16"/>
+      <c r="L162" s="41"/>
       <c r="M162" s="14"/>
       <c r="N162" s="7"/>
     </row>
@@ -6272,21 +7789,31 @@
       <c r="B163" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C163" s="15"/>
-      <c r="D163" s="12"/>
-      <c r="E163" s="13"/>
-      <c r="F163" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G163" s="41" t="s">
-        <v>134</v>
+      <c r="C163" s="15">
+        <v>506</v>
+      </c>
+      <c r="D163" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="E163" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="F163" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G163" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H163" s="16"/>
-      <c r="I163" s="15"/>
-      <c r="J163" s="14"/>
-      <c r="K163" s="16"/>
-      <c r="L163" s="7"/>
-      <c r="M163" s="31"/>
+      <c r="I163" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J163" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K163" s="5"/>
+      <c r="L163" s="41"/>
+      <c r="M163" s="14"/>
       <c r="N163" s="7"/>
     </row>
     <row r="164" spans="1:14" ht="15.75">
@@ -6296,20 +7823,30 @@
       <c r="B164" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C164" s="15"/>
-      <c r="D164" s="12"/>
-      <c r="E164" s="13"/>
-      <c r="F164" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G164" s="41" t="s">
-        <v>134</v>
+      <c r="C164" s="15">
+        <v>716</v>
+      </c>
+      <c r="D164" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="E164" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F164" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G164" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H164" s="16"/>
-      <c r="I164" s="15"/>
-      <c r="J164" s="14"/>
+      <c r="I164" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J164" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K164" s="16"/>
-      <c r="L164" s="7"/>
+      <c r="L164" s="41"/>
       <c r="M164" s="31"/>
       <c r="N164" s="7"/>
     </row>
@@ -6320,21 +7857,31 @@
       <c r="B165" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C165" s="22"/>
-      <c r="D165" s="23"/>
-      <c r="E165" s="28"/>
-      <c r="F165" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G165" s="41" t="s">
-        <v>134</v>
+      <c r="C165" s="15">
+        <v>769</v>
+      </c>
+      <c r="D165" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E165" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="F165" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G165" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H165" s="16"/>
-      <c r="I165" s="15"/>
-      <c r="J165" s="14"/>
+      <c r="I165" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J165" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K165" s="16"/>
-      <c r="L165" s="7"/>
-      <c r="M165" s="14"/>
+      <c r="L165" s="41"/>
+      <c r="M165" s="31"/>
       <c r="N165" s="7"/>
     </row>
     <row r="166" spans="1:14" ht="15.75">
@@ -6344,21 +7891,31 @@
       <c r="B166" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C166" s="15"/>
-      <c r="D166" s="12"/>
-      <c r="E166" s="13"/>
-      <c r="F166" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G166" s="41" t="s">
-        <v>134</v>
+      <c r="C166" s="15">
+        <v>613</v>
+      </c>
+      <c r="D166" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="E166" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F166" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G166" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H166" s="16"/>
-      <c r="I166" s="15"/>
-      <c r="J166" s="14"/>
+      <c r="I166" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J166" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K166" s="16"/>
-      <c r="L166" s="7"/>
-      <c r="M166" s="33"/>
+      <c r="L166" s="41"/>
+      <c r="M166" s="14"/>
       <c r="N166" s="7"/>
     </row>
     <row r="167" spans="1:14" ht="15.75">
@@ -6369,20 +7926,28 @@
         <v>18</v>
       </c>
       <c r="C167" s="15"/>
-      <c r="D167" s="12"/>
-      <c r="E167" s="13"/>
-      <c r="F167" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G167" s="41" t="s">
-        <v>134</v>
+      <c r="D167" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="E167" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="F167" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G167" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H167" s="16"/>
-      <c r="I167" s="15"/>
-      <c r="J167" s="14"/>
+      <c r="I167" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J167" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K167" s="16"/>
-      <c r="L167" s="5"/>
-      <c r="M167" s="20"/>
+      <c r="L167" s="41"/>
+      <c r="M167" s="33"/>
       <c r="N167" s="7"/>
     </row>
     <row r="168" spans="1:14" ht="15.75">
@@ -6392,21 +7957,31 @@
       <c r="B168" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C168" s="15"/>
-      <c r="D168" s="12"/>
-      <c r="E168" s="13"/>
-      <c r="F168" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G168" s="41" t="s">
-        <v>134</v>
+      <c r="C168" s="15">
+        <v>354</v>
+      </c>
+      <c r="D168" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="E168" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F168" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G168" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H168" s="16"/>
-      <c r="I168" s="15"/>
-      <c r="J168" s="14"/>
+      <c r="I168" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J168" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K168" s="16"/>
-      <c r="L168" s="7"/>
-      <c r="M168" s="14"/>
+      <c r="L168" s="42"/>
+      <c r="M168" s="20"/>
       <c r="N168" s="7"/>
     </row>
     <row r="169" spans="1:14" ht="15.75">
@@ -6416,20 +7991,30 @@
       <c r="B169" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C169" s="15"/>
-      <c r="D169" s="12"/>
-      <c r="E169" s="13"/>
-      <c r="F169" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G169" s="41" t="s">
-        <v>134</v>
+      <c r="C169" s="15">
+        <v>339</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="E169" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="F169" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G169" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H169" s="16"/>
-      <c r="I169" s="15"/>
-      <c r="J169" s="14"/>
+      <c r="I169" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J169" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K169" s="16"/>
-      <c r="L169" s="7"/>
+      <c r="L169" s="41"/>
       <c r="M169" s="14"/>
       <c r="N169" s="7"/>
     </row>
@@ -6440,21 +8025,31 @@
       <c r="B170" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C170" s="15"/>
-      <c r="D170" s="12"/>
-      <c r="E170" s="13"/>
-      <c r="F170" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G170" s="41" t="s">
-        <v>134</v>
+      <c r="C170" s="15">
+        <v>855</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E170" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="F170" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G170" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H170" s="16"/>
-      <c r="I170" s="15"/>
-      <c r="J170" s="14"/>
+      <c r="I170" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J170" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K170" s="16"/>
-      <c r="L170" s="7"/>
-      <c r="M170" s="20"/>
+      <c r="L170" s="41"/>
+      <c r="M170" s="14"/>
       <c r="N170" s="7"/>
     </row>
     <row r="171" spans="1:14" ht="15.75">
@@ -6464,21 +8059,31 @@
       <c r="B171" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C171" s="15"/>
-      <c r="D171" s="12"/>
-      <c r="E171" s="13"/>
-      <c r="F171" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G171" s="41" t="s">
-        <v>134</v>
+      <c r="C171" s="15">
+        <v>879</v>
+      </c>
+      <c r="D171" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="E171" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="F171" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G171" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H171" s="16"/>
-      <c r="I171" s="15"/>
-      <c r="J171" s="14"/>
+      <c r="I171" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J171" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K171" s="16"/>
-      <c r="L171" s="7"/>
-      <c r="M171" s="14"/>
+      <c r="L171" s="41"/>
+      <c r="M171" s="20"/>
       <c r="N171" s="7"/>
     </row>
     <row r="172" spans="1:14" ht="15.75">
@@ -6488,20 +8093,30 @@
       <c r="B172" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C172" s="15"/>
-      <c r="D172" s="12"/>
-      <c r="E172" s="13"/>
-      <c r="F172" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G172" s="41" t="s">
-        <v>134</v>
+      <c r="C172" s="15">
+        <v>618</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="E172" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="F172" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G172" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H172" s="16"/>
-      <c r="I172" s="15"/>
-      <c r="J172" s="14"/>
+      <c r="I172" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J172" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K172" s="16"/>
-      <c r="L172" s="7"/>
+      <c r="L172" s="41"/>
       <c r="M172" s="14"/>
       <c r="N172" s="7"/>
     </row>
@@ -6512,21 +8127,31 @@
       <c r="B173" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C173" s="15"/>
-      <c r="D173" s="12"/>
-      <c r="E173" s="13"/>
-      <c r="F173" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G173" s="41" t="s">
-        <v>134</v>
+      <c r="C173" s="15">
+        <v>305</v>
+      </c>
+      <c r="D173" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="E173" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F173" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G173" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H173" s="16"/>
-      <c r="I173" s="15"/>
-      <c r="J173" s="14"/>
+      <c r="I173" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J173" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K173" s="16"/>
-      <c r="L173" s="7"/>
-      <c r="M173" s="20"/>
+      <c r="L173" s="41"/>
+      <c r="M173" s="14"/>
       <c r="N173" s="7"/>
     </row>
     <row r="174" spans="1:14" ht="15.75">
@@ -6536,21 +8161,31 @@
       <c r="B174" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C174" s="15"/>
-      <c r="D174" s="12"/>
-      <c r="E174" s="13"/>
-      <c r="F174" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G174" s="41" t="s">
-        <v>134</v>
+      <c r="C174" s="15">
+        <v>713</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E174" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="F174" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G174" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H174" s="16"/>
-      <c r="I174" s="15"/>
-      <c r="J174" s="14"/>
+      <c r="I174" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J174" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K174" s="16"/>
-      <c r="L174" s="7"/>
-      <c r="M174" s="7"/>
+      <c r="L174" s="41"/>
+      <c r="M174" s="20"/>
       <c r="N174" s="7"/>
     </row>
     <row r="175" spans="1:14" ht="15.75">
@@ -6560,21 +8195,31 @@
       <c r="B175" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C175" s="15"/>
-      <c r="D175" s="12"/>
-      <c r="E175" s="13"/>
-      <c r="F175" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G175" s="41" t="s">
-        <v>134</v>
+      <c r="C175" s="15">
+        <v>789</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="E175" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="F175" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G175" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H175" s="16"/>
-      <c r="I175" s="15"/>
-      <c r="J175" s="14"/>
+      <c r="I175" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J175" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K175" s="16"/>
-      <c r="L175" s="7"/>
-      <c r="M175" s="14"/>
+      <c r="L175" s="41"/>
+      <c r="M175" s="7"/>
       <c r="N175" s="7"/>
     </row>
     <row r="176" spans="1:14" ht="15.75">
@@ -6587,17 +8232,21 @@
       <c r="C176" s="15"/>
       <c r="D176" s="12"/>
       <c r="E176" s="13"/>
-      <c r="F176" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G176" s="41" t="s">
-        <v>134</v>
+      <c r="F176" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G176" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H176" s="16"/>
-      <c r="I176" s="15"/>
-      <c r="J176" s="14"/>
+      <c r="I176" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J176" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K176" s="16"/>
-      <c r="L176" s="7"/>
+      <c r="L176" s="41"/>
       <c r="M176" s="14"/>
       <c r="N176" s="7"/>
     </row>
@@ -6611,17 +8260,21 @@
       <c r="C177" s="15"/>
       <c r="D177" s="12"/>
       <c r="E177" s="13"/>
-      <c r="F177" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G177" s="41" t="s">
-        <v>134</v>
+      <c r="F177" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G177" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H177" s="16"/>
-      <c r="I177" s="15"/>
-      <c r="J177" s="14"/>
+      <c r="I177" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J177" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K177" s="16"/>
-      <c r="L177" s="7"/>
+      <c r="L177" s="41"/>
       <c r="M177" s="14"/>
       <c r="N177" s="7"/>
     </row>
@@ -6635,21 +8288,25 @@
       <c r="C178" s="15"/>
       <c r="D178" s="12"/>
       <c r="E178" s="13"/>
-      <c r="F178" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G178" s="41" t="s">
-        <v>134</v>
+      <c r="F178" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G178" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H178" s="16"/>
-      <c r="I178" s="15"/>
-      <c r="J178" s="14"/>
+      <c r="I178" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J178" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K178" s="16"/>
-      <c r="L178" s="7"/>
+      <c r="L178" s="41"/>
       <c r="M178" s="14"/>
-      <c r="N178" s="14"/>
-    </row>
-    <row r="179" spans="1:14" ht="15.75">
+      <c r="N178" s="7"/>
+    </row>
+    <row r="179" spans="1:14">
       <c r="A179" s="14">
         <v>177</v>
       </c>
@@ -6659,21 +8316,25 @@
       <c r="C179" s="15"/>
       <c r="D179" s="12"/>
       <c r="E179" s="13"/>
-      <c r="F179" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G179" s="41" t="s">
-        <v>134</v>
+      <c r="F179" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G179" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H179" s="16"/>
-      <c r="I179" s="15"/>
-      <c r="J179" s="14"/>
+      <c r="I179" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J179" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K179" s="16"/>
-      <c r="L179" s="7"/>
+      <c r="L179" s="41"/>
       <c r="M179" s="14"/>
       <c r="N179" s="14"/>
     </row>
-    <row r="180" spans="1:14" ht="15.75">
+    <row r="180" spans="1:14">
       <c r="A180" s="14">
         <v>178</v>
       </c>
@@ -6683,19 +8344,23 @@
       <c r="C180" s="15"/>
       <c r="D180" s="12"/>
       <c r="E180" s="13"/>
-      <c r="F180" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G180" s="41" t="s">
-        <v>134</v>
+      <c r="F180" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G180" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H180" s="16"/>
-      <c r="I180" s="15"/>
-      <c r="J180" s="14"/>
+      <c r="I180" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J180" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K180" s="16"/>
-      <c r="L180" s="7"/>
-      <c r="M180" s="21"/>
-      <c r="N180" s="7"/>
+      <c r="L180" s="41"/>
+      <c r="M180" s="14"/>
+      <c r="N180" s="14"/>
     </row>
     <row r="181" spans="1:14" ht="15.75">
       <c r="A181" s="14">
@@ -6707,17 +8372,21 @@
       <c r="C181" s="15"/>
       <c r="D181" s="12"/>
       <c r="E181" s="13"/>
-      <c r="F181" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G181" s="41" t="s">
-        <v>134</v>
+      <c r="F181" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G181" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H181" s="16"/>
-      <c r="I181" s="15"/>
-      <c r="J181" s="14"/>
+      <c r="I181" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J181" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K181" s="16"/>
-      <c r="L181" s="7"/>
+      <c r="L181" s="41"/>
       <c r="M181" s="21"/>
       <c r="N181" s="7"/>
     </row>
@@ -6731,18 +8400,22 @@
       <c r="C182" s="15"/>
       <c r="D182" s="12"/>
       <c r="E182" s="13"/>
-      <c r="F182" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G182" s="41" t="s">
-        <v>134</v>
+      <c r="F182" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G182" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H182" s="16"/>
-      <c r="I182" s="15"/>
-      <c r="J182" s="14"/>
+      <c r="I182" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J182" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K182" s="16"/>
-      <c r="L182" s="7"/>
-      <c r="M182" s="14"/>
+      <c r="L182" s="41"/>
+      <c r="M182" s="21"/>
       <c r="N182" s="7"/>
     </row>
     <row r="183" spans="1:14" ht="15.75">
@@ -6755,18 +8428,22 @@
       <c r="C183" s="15"/>
       <c r="D183" s="12"/>
       <c r="E183" s="13"/>
-      <c r="F183" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G183" s="41" t="s">
-        <v>134</v>
+      <c r="F183" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G183" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H183" s="16"/>
-      <c r="I183" s="15"/>
-      <c r="J183" s="14"/>
+      <c r="I183" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J183" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K183" s="16"/>
-      <c r="L183" s="7"/>
-      <c r="M183" s="21"/>
+      <c r="L183" s="41"/>
+      <c r="M183" s="14"/>
       <c r="N183" s="7"/>
     </row>
     <row r="184" spans="1:14" ht="15.75">
@@ -6779,18 +8456,22 @@
       <c r="C184" s="15"/>
       <c r="D184" s="12"/>
       <c r="E184" s="13"/>
-      <c r="F184" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G184" s="41" t="s">
-        <v>134</v>
+      <c r="F184" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G184" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H184" s="16"/>
-      <c r="I184" s="15"/>
-      <c r="J184" s="14"/>
+      <c r="I184" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J184" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K184" s="16"/>
-      <c r="L184" s="7"/>
-      <c r="M184" s="33"/>
+      <c r="L184" s="41"/>
+      <c r="M184" s="21"/>
       <c r="N184" s="7"/>
     </row>
     <row r="185" spans="1:14" ht="15.75">
@@ -6803,18 +8484,22 @@
       <c r="C185" s="15"/>
       <c r="D185" s="12"/>
       <c r="E185" s="13"/>
-      <c r="F185" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G185" s="41" t="s">
-        <v>134</v>
+      <c r="F185" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G185" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H185" s="16"/>
-      <c r="I185" s="15"/>
-      <c r="J185" s="14"/>
+      <c r="I185" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J185" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K185" s="16"/>
-      <c r="L185" s="7"/>
-      <c r="M185" s="14"/>
+      <c r="L185" s="41"/>
+      <c r="M185" s="33"/>
       <c r="N185" s="7"/>
     </row>
     <row r="186" spans="1:14" ht="15.75">
@@ -6827,17 +8512,21 @@
       <c r="C186" s="15"/>
       <c r="D186" s="12"/>
       <c r="E186" s="13"/>
-      <c r="F186" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G186" s="41" t="s">
-        <v>134</v>
+      <c r="F186" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G186" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H186" s="16"/>
-      <c r="I186" s="15"/>
-      <c r="J186" s="14"/>
+      <c r="I186" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J186" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K186" s="16"/>
-      <c r="L186" s="7"/>
+      <c r="L186" s="41"/>
       <c r="M186" s="14"/>
       <c r="N186" s="7"/>
     </row>
@@ -6851,17 +8540,21 @@
       <c r="C187" s="15"/>
       <c r="D187" s="12"/>
       <c r="E187" s="13"/>
-      <c r="F187" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G187" s="41" t="s">
-        <v>134</v>
+      <c r="F187" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G187" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H187" s="16"/>
-      <c r="I187" s="15"/>
-      <c r="J187" s="14"/>
+      <c r="I187" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J187" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K187" s="16"/>
-      <c r="L187" s="7"/>
+      <c r="L187" s="41"/>
       <c r="M187" s="14"/>
       <c r="N187" s="7"/>
     </row>
@@ -6875,17 +8568,21 @@
       <c r="C188" s="15"/>
       <c r="D188" s="12"/>
       <c r="E188" s="13"/>
-      <c r="F188" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G188" s="41" t="s">
-        <v>134</v>
+      <c r="F188" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G188" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H188" s="16"/>
-      <c r="I188" s="15"/>
-      <c r="J188" s="14"/>
+      <c r="I188" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J188" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K188" s="16"/>
-      <c r="L188" s="7"/>
+      <c r="L188" s="41"/>
       <c r="M188" s="14"/>
       <c r="N188" s="7"/>
     </row>
@@ -6899,18 +8596,22 @@
       <c r="C189" s="15"/>
       <c r="D189" s="12"/>
       <c r="E189" s="13"/>
-      <c r="F189" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G189" s="41" t="s">
-        <v>134</v>
+      <c r="F189" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G189" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H189" s="16"/>
-      <c r="I189" s="15"/>
-      <c r="J189" s="14"/>
+      <c r="I189" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J189" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K189" s="16"/>
-      <c r="L189" s="7"/>
-      <c r="M189" s="33"/>
+      <c r="L189" s="41"/>
+      <c r="M189" s="14"/>
       <c r="N189" s="7"/>
     </row>
     <row r="190" spans="1:14" ht="15.75">
@@ -6923,18 +8624,22 @@
       <c r="C190" s="15"/>
       <c r="D190" s="12"/>
       <c r="E190" s="13"/>
-      <c r="F190" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G190" s="41" t="s">
-        <v>134</v>
+      <c r="F190" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G190" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H190" s="16"/>
-      <c r="I190" s="15"/>
-      <c r="J190" s="14"/>
+      <c r="I190" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J190" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K190" s="16"/>
-      <c r="L190" s="7"/>
-      <c r="M190" s="14"/>
+      <c r="L190" s="41"/>
+      <c r="M190" s="33"/>
       <c r="N190" s="7"/>
     </row>
     <row r="191" spans="1:14" ht="15.75">
@@ -6947,17 +8652,21 @@
       <c r="C191" s="15"/>
       <c r="D191" s="12"/>
       <c r="E191" s="13"/>
-      <c r="F191" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G191" s="41" t="s">
-        <v>134</v>
+      <c r="F191" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G191" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H191" s="16"/>
-      <c r="I191" s="15"/>
-      <c r="J191" s="14"/>
+      <c r="I191" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J191" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K191" s="16"/>
-      <c r="L191" s="7"/>
+      <c r="L191" s="41"/>
       <c r="M191" s="14"/>
       <c r="N191" s="7"/>
     </row>
@@ -6971,18 +8680,22 @@
       <c r="C192" s="15"/>
       <c r="D192" s="12"/>
       <c r="E192" s="13"/>
-      <c r="F192" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G192" s="41" t="s">
-        <v>134</v>
+      <c r="F192" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G192" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H192" s="16"/>
-      <c r="I192" s="15"/>
-      <c r="J192" s="14"/>
+      <c r="I192" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J192" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K192" s="16"/>
-      <c r="L192" s="7"/>
-      <c r="M192" s="20"/>
+      <c r="L192" s="41"/>
+      <c r="M192" s="14"/>
       <c r="N192" s="7"/>
     </row>
     <row r="193" spans="1:14" ht="15.75">
@@ -6995,18 +8708,22 @@
       <c r="C193" s="15"/>
       <c r="D193" s="12"/>
       <c r="E193" s="13"/>
-      <c r="F193" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G193" s="41" t="s">
-        <v>134</v>
+      <c r="F193" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G193" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H193" s="16"/>
-      <c r="I193" s="15"/>
-      <c r="J193" s="14"/>
+      <c r="I193" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J193" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K193" s="16"/>
-      <c r="L193" s="7"/>
-      <c r="M193" s="14"/>
+      <c r="L193" s="41"/>
+      <c r="M193" s="20"/>
       <c r="N193" s="7"/>
     </row>
     <row r="194" spans="1:14" ht="15.75">
@@ -7019,17 +8736,21 @@
       <c r="C194" s="15"/>
       <c r="D194" s="12"/>
       <c r="E194" s="13"/>
-      <c r="F194" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G194" s="41" t="s">
-        <v>134</v>
+      <c r="F194" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G194" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H194" s="16"/>
-      <c r="I194" s="15"/>
-      <c r="J194" s="14"/>
+      <c r="I194" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J194" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K194" s="16"/>
-      <c r="L194" s="7"/>
+      <c r="L194" s="41"/>
       <c r="M194" s="14"/>
       <c r="N194" s="7"/>
     </row>
@@ -7043,17 +8764,21 @@
       <c r="C195" s="15"/>
       <c r="D195" s="12"/>
       <c r="E195" s="13"/>
-      <c r="F195" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G195" s="41" t="s">
-        <v>134</v>
+      <c r="F195" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G195" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H195" s="16"/>
-      <c r="I195" s="15"/>
-      <c r="J195" s="14"/>
+      <c r="I195" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J195" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K195" s="16"/>
-      <c r="L195" s="7"/>
+      <c r="L195" s="41"/>
       <c r="M195" s="14"/>
       <c r="N195" s="7"/>
     </row>
@@ -7067,18 +8792,22 @@
       <c r="C196" s="15"/>
       <c r="D196" s="12"/>
       <c r="E196" s="13"/>
-      <c r="F196" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G196" s="41" t="s">
-        <v>134</v>
+      <c r="F196" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G196" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H196" s="16"/>
-      <c r="I196" s="15"/>
-      <c r="J196" s="14"/>
+      <c r="I196" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J196" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K196" s="16"/>
-      <c r="L196" s="7"/>
-      <c r="M196" s="20"/>
+      <c r="L196" s="41"/>
+      <c r="M196" s="14"/>
       <c r="N196" s="7"/>
     </row>
     <row r="197" spans="1:14" ht="15.75">
@@ -7091,17 +8820,21 @@
       <c r="C197" s="15"/>
       <c r="D197" s="12"/>
       <c r="E197" s="13"/>
-      <c r="F197" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G197" s="41" t="s">
-        <v>134</v>
+      <c r="F197" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G197" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H197" s="16"/>
-      <c r="I197" s="15"/>
-      <c r="J197" s="14"/>
+      <c r="I197" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J197" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K197" s="16"/>
-      <c r="L197" s="7"/>
+      <c r="L197" s="41"/>
       <c r="M197" s="20"/>
       <c r="N197" s="7"/>
     </row>
@@ -7115,17 +8848,21 @@
       <c r="C198" s="15"/>
       <c r="D198" s="12"/>
       <c r="E198" s="13"/>
-      <c r="F198" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G198" s="41" t="s">
-        <v>134</v>
+      <c r="F198" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G198" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H198" s="16"/>
-      <c r="I198" s="15"/>
-      <c r="J198" s="14"/>
+      <c r="I198" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J198" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K198" s="16"/>
-      <c r="L198" s="7"/>
+      <c r="L198" s="41"/>
       <c r="M198" s="20"/>
       <c r="N198" s="7"/>
     </row>
@@ -7139,18 +8876,22 @@
       <c r="C199" s="15"/>
       <c r="D199" s="12"/>
       <c r="E199" s="13"/>
-      <c r="F199" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G199" s="41" t="s">
-        <v>134</v>
+      <c r="F199" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G199" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H199" s="16"/>
-      <c r="I199" s="15"/>
-      <c r="J199" s="14"/>
+      <c r="I199" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J199" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K199" s="16"/>
-      <c r="L199" s="7"/>
-      <c r="M199" s="14"/>
+      <c r="L199" s="41"/>
+      <c r="M199" s="20"/>
       <c r="N199" s="7"/>
     </row>
     <row r="200" spans="1:14" ht="15.75">
@@ -7163,17 +8904,21 @@
       <c r="C200" s="15"/>
       <c r="D200" s="12"/>
       <c r="E200" s="13"/>
-      <c r="F200" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G200" s="41" t="s">
-        <v>134</v>
+      <c r="F200" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G200" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H200" s="16"/>
-      <c r="I200" s="15"/>
-      <c r="J200" s="14"/>
+      <c r="I200" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J200" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K200" s="16"/>
-      <c r="L200" s="7"/>
+      <c r="L200" s="41"/>
       <c r="M200" s="14"/>
       <c r="N200" s="7"/>
     </row>
@@ -7187,18 +8932,22 @@
       <c r="C201" s="15"/>
       <c r="D201" s="12"/>
       <c r="E201" s="13"/>
-      <c r="F201" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G201" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H201" s="32"/>
-      <c r="I201" s="15"/>
-      <c r="J201" s="14"/>
+      <c r="F201" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G201" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="H201" s="16"/>
+      <c r="I201" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J201" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K201" s="16"/>
-      <c r="L201" s="7"/>
-      <c r="M201" s="33"/>
+      <c r="L201" s="41"/>
+      <c r="M201" s="14"/>
       <c r="N201" s="7"/>
     </row>
     <row r="202" spans="1:14" ht="15.75">
@@ -7211,18 +8960,22 @@
       <c r="C202" s="15"/>
       <c r="D202" s="12"/>
       <c r="E202" s="13"/>
-      <c r="F202" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G202" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H202" s="16"/>
-      <c r="I202" s="15"/>
-      <c r="J202" s="14"/>
+      <c r="F202" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G202" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="H202" s="32"/>
+      <c r="I202" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J202" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K202" s="16"/>
-      <c r="L202" s="7"/>
-      <c r="M202" s="20"/>
+      <c r="L202" s="41"/>
+      <c r="M202" s="33"/>
       <c r="N202" s="7"/>
     </row>
     <row r="203" spans="1:14" ht="15.75">
@@ -7235,18 +8988,22 @@
       <c r="C203" s="15"/>
       <c r="D203" s="12"/>
       <c r="E203" s="13"/>
-      <c r="F203" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G203" s="41" t="s">
-        <v>134</v>
+      <c r="F203" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G203" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H203" s="16"/>
-      <c r="I203" s="15"/>
-      <c r="J203" s="14"/>
+      <c r="I203" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J203" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K203" s="16"/>
-      <c r="L203" s="7"/>
-      <c r="M203" s="14"/>
+      <c r="L203" s="41"/>
+      <c r="M203" s="20"/>
       <c r="N203" s="7"/>
     </row>
     <row r="204" spans="1:14" ht="15.75">
@@ -7259,18 +9016,22 @@
       <c r="C204" s="15"/>
       <c r="D204" s="12"/>
       <c r="E204" s="13"/>
-      <c r="F204" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G204" s="41" t="s">
-        <v>134</v>
+      <c r="F204" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G204" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H204" s="16"/>
-      <c r="I204" s="15"/>
-      <c r="J204" s="14"/>
-      <c r="K204" s="32"/>
-      <c r="L204" s="7"/>
-      <c r="M204" s="20"/>
+      <c r="I204" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J204" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K204" s="16"/>
+      <c r="L204" s="41"/>
+      <c r="M204" s="14"/>
       <c r="N204" s="7"/>
     </row>
     <row r="205" spans="1:14" ht="15.75">
@@ -7283,18 +9044,22 @@
       <c r="C205" s="15"/>
       <c r="D205" s="12"/>
       <c r="E205" s="13"/>
-      <c r="F205" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G205" s="41" t="s">
-        <v>134</v>
+      <c r="F205" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G205" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H205" s="16"/>
-      <c r="I205" s="15"/>
-      <c r="J205" s="14"/>
-      <c r="K205" s="16"/>
-      <c r="L205" s="7"/>
-      <c r="M205" s="29"/>
+      <c r="I205" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J205" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K205" s="32"/>
+      <c r="L205" s="41"/>
+      <c r="M205" s="20"/>
       <c r="N205" s="7"/>
     </row>
     <row r="206" spans="1:14" ht="15.75">
@@ -7307,18 +9072,22 @@
       <c r="C206" s="15"/>
       <c r="D206" s="12"/>
       <c r="E206" s="13"/>
-      <c r="F206" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G206" s="41" t="s">
-        <v>134</v>
+      <c r="F206" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G206" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H206" s="16"/>
-      <c r="I206" s="15"/>
-      <c r="J206" s="14"/>
+      <c r="I206" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J206" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K206" s="16"/>
-      <c r="L206" s="7"/>
-      <c r="M206" s="14"/>
+      <c r="L206" s="41"/>
+      <c r="M206" s="29"/>
       <c r="N206" s="7"/>
     </row>
     <row r="207" spans="1:14" ht="15.75">
@@ -7331,18 +9100,22 @@
       <c r="C207" s="15"/>
       <c r="D207" s="12"/>
       <c r="E207" s="13"/>
-      <c r="F207" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G207" s="41" t="s">
-        <v>134</v>
+      <c r="F207" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G207" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H207" s="16"/>
-      <c r="I207" s="15"/>
-      <c r="J207" s="14"/>
+      <c r="I207" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J207" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K207" s="16"/>
-      <c r="L207" s="7"/>
-      <c r="M207" s="20"/>
+      <c r="L207" s="41"/>
+      <c r="M207" s="14"/>
       <c r="N207" s="7"/>
     </row>
     <row r="208" spans="1:14" ht="15.75">
@@ -7355,18 +9128,22 @@
       <c r="C208" s="15"/>
       <c r="D208" s="12"/>
       <c r="E208" s="13"/>
-      <c r="F208" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G208" s="41" t="s">
-        <v>134</v>
+      <c r="F208" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G208" s="44" t="s">
+        <v>321</v>
       </c>
       <c r="H208" s="16"/>
-      <c r="I208" s="15"/>
-      <c r="J208" s="14"/>
+      <c r="I208" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J208" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K208" s="16"/>
-      <c r="L208" s="7"/>
-      <c r="M208" s="33"/>
+      <c r="L208" s="41"/>
+      <c r="M208" s="20"/>
       <c r="N208" s="7"/>
     </row>
     <row r="209" spans="1:14" ht="15.75">
@@ -7379,15 +9156,21 @@
       <c r="C209" s="15"/>
       <c r="D209" s="12"/>
       <c r="E209" s="13"/>
-      <c r="F209" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G209" s="14"/>
+      <c r="F209" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G209" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H209" s="16"/>
-      <c r="I209" s="15"/>
-      <c r="J209" s="14"/>
+      <c r="I209" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J209" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K209" s="16"/>
-      <c r="L209" s="7"/>
+      <c r="L209" s="41"/>
       <c r="M209" s="33"/>
       <c r="N209" s="7"/>
     </row>
@@ -7401,15 +9184,21 @@
       <c r="C210" s="15"/>
       <c r="D210" s="12"/>
       <c r="E210" s="13"/>
-      <c r="F210" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G210" s="14"/>
+      <c r="F210" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G210" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H210" s="16"/>
-      <c r="I210" s="15"/>
-      <c r="J210" s="14"/>
+      <c r="I210" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J210" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K210" s="16"/>
-      <c r="L210" s="7"/>
+      <c r="L210" s="41"/>
       <c r="M210" s="33"/>
       <c r="N210" s="7"/>
     </row>
@@ -7423,16 +9212,22 @@
       <c r="C211" s="15"/>
       <c r="D211" s="12"/>
       <c r="E211" s="13"/>
-      <c r="F211" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G211" s="14"/>
+      <c r="F211" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G211" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H211" s="16"/>
-      <c r="I211" s="15"/>
-      <c r="J211" s="14"/>
+      <c r="I211" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J211" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K211" s="16"/>
-      <c r="L211" s="7"/>
-      <c r="M211" s="20"/>
+      <c r="L211" s="41"/>
+      <c r="M211" s="33"/>
       <c r="N211" s="7"/>
     </row>
     <row r="212" spans="1:14" ht="15.75">
@@ -7445,15 +9240,21 @@
       <c r="C212" s="15"/>
       <c r="D212" s="12"/>
       <c r="E212" s="13"/>
-      <c r="F212" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G212" s="14"/>
+      <c r="F212" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G212" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H212" s="16"/>
-      <c r="I212" s="15"/>
-      <c r="J212" s="14"/>
+      <c r="I212" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J212" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K212" s="16"/>
-      <c r="L212" s="7"/>
+      <c r="L212" s="41"/>
       <c r="M212" s="20"/>
       <c r="N212" s="7"/>
     </row>
@@ -7467,16 +9268,22 @@
       <c r="C213" s="15"/>
       <c r="D213" s="12"/>
       <c r="E213" s="13"/>
-      <c r="F213" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G213" s="14"/>
+      <c r="F213" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G213" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H213" s="16"/>
-      <c r="I213" s="15"/>
-      <c r="J213" s="14"/>
+      <c r="I213" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J213" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K213" s="16"/>
-      <c r="L213" s="7"/>
-      <c r="M213" s="14"/>
+      <c r="L213" s="41"/>
+      <c r="M213" s="20"/>
       <c r="N213" s="7"/>
     </row>
     <row r="214" spans="1:14" ht="15.75">
@@ -7489,16 +9296,22 @@
       <c r="C214" s="15"/>
       <c r="D214" s="12"/>
       <c r="E214" s="13"/>
-      <c r="F214" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G214" s="14"/>
+      <c r="F214" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G214" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H214" s="16"/>
-      <c r="I214" s="15"/>
-      <c r="J214" s="14"/>
+      <c r="I214" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J214" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K214" s="16"/>
-      <c r="L214" s="7"/>
-      <c r="M214" s="33"/>
+      <c r="L214" s="41"/>
+      <c r="M214" s="14"/>
       <c r="N214" s="7"/>
     </row>
     <row r="215" spans="1:14" ht="15.75">
@@ -7511,16 +9324,22 @@
       <c r="C215" s="15"/>
       <c r="D215" s="12"/>
       <c r="E215" s="13"/>
-      <c r="F215" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G215" s="14"/>
+      <c r="F215" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G215" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H215" s="16"/>
-      <c r="I215" s="15"/>
-      <c r="J215" s="14"/>
+      <c r="I215" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J215" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K215" s="16"/>
-      <c r="L215" s="7"/>
-      <c r="M215" s="20"/>
+      <c r="L215" s="41"/>
+      <c r="M215" s="33"/>
       <c r="N215" s="7"/>
     </row>
     <row r="216" spans="1:14" ht="15.75">
@@ -7533,16 +9352,22 @@
       <c r="C216" s="15"/>
       <c r="D216" s="12"/>
       <c r="E216" s="13"/>
-      <c r="F216" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G216" s="14"/>
+      <c r="F216" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G216" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H216" s="16"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="14"/>
+      <c r="I216" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J216" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K216" s="16"/>
-      <c r="L216" s="7"/>
-      <c r="M216" s="14"/>
+      <c r="L216" s="41"/>
+      <c r="M216" s="20"/>
       <c r="N216" s="7"/>
     </row>
     <row r="217" spans="1:14" ht="15.75">
@@ -7552,19 +9377,25 @@
       <c r="B217" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C217" s="22"/>
-      <c r="D217" s="23"/>
-      <c r="E217" s="28"/>
-      <c r="F217" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G217" s="14"/>
+      <c r="C217" s="15"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="13"/>
+      <c r="F217" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G217" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H217" s="16"/>
-      <c r="I217" s="15"/>
-      <c r="J217" s="14"/>
+      <c r="I217" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J217" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K217" s="16"/>
-      <c r="L217" s="7"/>
-      <c r="M217" s="20"/>
+      <c r="L217" s="41"/>
+      <c r="M217" s="14"/>
       <c r="N217" s="7"/>
     </row>
     <row r="218" spans="1:14" ht="15.75">
@@ -7574,19 +9405,25 @@
       <c r="B218" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C218" s="15"/>
-      <c r="D218" s="12"/>
-      <c r="E218" s="13"/>
-      <c r="F218" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G218" s="14"/>
+      <c r="C218" s="22"/>
+      <c r="D218" s="23"/>
+      <c r="E218" s="28"/>
+      <c r="F218" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G218" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H218" s="16"/>
-      <c r="I218" s="15"/>
-      <c r="J218" s="14"/>
+      <c r="I218" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J218" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K218" s="16"/>
-      <c r="L218" s="7"/>
-      <c r="M218" s="31"/>
+      <c r="L218" s="41"/>
+      <c r="M218" s="20"/>
       <c r="N218" s="7"/>
     </row>
     <row r="219" spans="1:14" ht="15.75">
@@ -7599,16 +9436,22 @@
       <c r="C219" s="15"/>
       <c r="D219" s="12"/>
       <c r="E219" s="13"/>
-      <c r="F219" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G219" s="14"/>
+      <c r="F219" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G219" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H219" s="16"/>
-      <c r="I219" s="15"/>
-      <c r="J219" s="14"/>
+      <c r="I219" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J219" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K219" s="16"/>
-      <c r="L219" s="7"/>
-      <c r="M219" s="20"/>
+      <c r="L219" s="41"/>
+      <c r="M219" s="31"/>
       <c r="N219" s="7"/>
     </row>
     <row r="220" spans="1:14" ht="15.75">
@@ -7621,16 +9464,22 @@
       <c r="C220" s="15"/>
       <c r="D220" s="12"/>
       <c r="E220" s="13"/>
-      <c r="F220" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G220" s="14"/>
+      <c r="F220" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G220" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H220" s="16"/>
-      <c r="I220" s="15"/>
-      <c r="J220" s="14"/>
+      <c r="I220" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J220" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K220" s="16"/>
-      <c r="L220" s="7"/>
-      <c r="M220" s="14"/>
+      <c r="L220" s="41"/>
+      <c r="M220" s="20"/>
       <c r="N220" s="7"/>
     </row>
     <row r="221" spans="1:14" ht="15.75">
@@ -7643,16 +9492,22 @@
       <c r="C221" s="15"/>
       <c r="D221" s="12"/>
       <c r="E221" s="13"/>
-      <c r="F221" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G221" s="14"/>
+      <c r="F221" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G221" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H221" s="16"/>
-      <c r="I221" s="15"/>
-      <c r="J221" s="14"/>
+      <c r="I221" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J221" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K221" s="16"/>
-      <c r="L221" s="7"/>
-      <c r="M221" s="20"/>
+      <c r="L221" s="41"/>
+      <c r="M221" s="14"/>
       <c r="N221" s="7"/>
     </row>
     <row r="222" spans="1:14" ht="15.75">
@@ -7665,16 +9520,22 @@
       <c r="C222" s="15"/>
       <c r="D222" s="12"/>
       <c r="E222" s="13"/>
-      <c r="F222" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G222" s="14"/>
+      <c r="F222" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G222" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H222" s="16"/>
-      <c r="I222" s="15"/>
-      <c r="J222" s="14"/>
+      <c r="I222" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J222" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K222" s="16"/>
-      <c r="L222" s="7"/>
-      <c r="M222" s="33"/>
+      <c r="L222" s="41"/>
+      <c r="M222" s="20"/>
       <c r="N222" s="7"/>
     </row>
     <row r="223" spans="1:14" ht="15.75">
@@ -7687,16 +9548,22 @@
       <c r="C223" s="15"/>
       <c r="D223" s="12"/>
       <c r="E223" s="13"/>
-      <c r="F223" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G223" s="14"/>
+      <c r="F223" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G223" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H223" s="16"/>
-      <c r="I223" s="15"/>
-      <c r="J223" s="14"/>
+      <c r="I223" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J223" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K223" s="16"/>
-      <c r="L223" s="7"/>
-      <c r="M223" s="7"/>
+      <c r="L223" s="41"/>
+      <c r="M223" s="33"/>
       <c r="N223" s="7"/>
     </row>
     <row r="224" spans="1:14" ht="15.75">
@@ -7709,16 +9576,22 @@
       <c r="C224" s="15"/>
       <c r="D224" s="12"/>
       <c r="E224" s="13"/>
-      <c r="F224" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G224" s="14"/>
+      <c r="F224" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G224" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H224" s="16"/>
-      <c r="I224" s="15"/>
-      <c r="J224" s="14"/>
-      <c r="K224" s="34"/>
-      <c r="L224" s="7"/>
-      <c r="M224" s="21"/>
+      <c r="I224" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J224" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K224" s="16"/>
+      <c r="L224" s="41"/>
+      <c r="M224" s="7"/>
       <c r="N224" s="7"/>
     </row>
     <row r="225" spans="1:14" ht="15.75">
@@ -7731,16 +9604,22 @@
       <c r="C225" s="15"/>
       <c r="D225" s="12"/>
       <c r="E225" s="13"/>
-      <c r="F225" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G225" s="14"/>
+      <c r="F225" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G225" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H225" s="16"/>
-      <c r="I225" s="15"/>
-      <c r="J225" s="14"/>
-      <c r="K225" s="16"/>
-      <c r="L225" s="7"/>
-      <c r="M225" s="20"/>
+      <c r="I225" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J225" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K225" s="34"/>
+      <c r="L225" s="41"/>
+      <c r="M225" s="21"/>
       <c r="N225" s="7"/>
     </row>
     <row r="226" spans="1:14" ht="15.75">
@@ -7753,16 +9632,22 @@
       <c r="C226" s="15"/>
       <c r="D226" s="12"/>
       <c r="E226" s="13"/>
-      <c r="F226" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G226" s="14"/>
+      <c r="F226" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G226" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H226" s="16"/>
-      <c r="I226" s="15"/>
-      <c r="J226" s="14"/>
+      <c r="I226" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J226" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K226" s="16"/>
-      <c r="L226" s="7"/>
-      <c r="M226" s="14"/>
+      <c r="L226" s="41"/>
+      <c r="M226" s="20"/>
       <c r="N226" s="7"/>
     </row>
     <row r="227" spans="1:14" ht="15.75">
@@ -7775,16 +9660,22 @@
       <c r="C227" s="15"/>
       <c r="D227" s="12"/>
       <c r="E227" s="13"/>
-      <c r="F227" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G227" s="14"/>
+      <c r="F227" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G227" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H227" s="16"/>
-      <c r="I227" s="15"/>
-      <c r="J227" s="14"/>
+      <c r="I227" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J227" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K227" s="16"/>
-      <c r="L227" s="7"/>
-      <c r="M227" s="20"/>
+      <c r="L227" s="41"/>
+      <c r="M227" s="14"/>
       <c r="N227" s="7"/>
     </row>
     <row r="228" spans="1:14" ht="15.75">
@@ -7797,16 +9688,22 @@
       <c r="C228" s="15"/>
       <c r="D228" s="12"/>
       <c r="E228" s="13"/>
-      <c r="F228" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G228" s="14"/>
+      <c r="F228" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G228" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H228" s="16"/>
-      <c r="I228" s="15"/>
-      <c r="J228" s="14"/>
+      <c r="I228" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J228" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K228" s="16"/>
-      <c r="L228" s="7"/>
-      <c r="M228" s="14"/>
+      <c r="L228" s="41"/>
+      <c r="M228" s="20"/>
       <c r="N228" s="7"/>
     </row>
     <row r="229" spans="1:14" ht="15.75">
@@ -7819,16 +9716,22 @@
       <c r="C229" s="15"/>
       <c r="D229" s="12"/>
       <c r="E229" s="13"/>
-      <c r="F229" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G229" s="14"/>
+      <c r="F229" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G229" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H229" s="16"/>
-      <c r="I229" s="15"/>
-      <c r="J229" s="14"/>
+      <c r="I229" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J229" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K229" s="16"/>
-      <c r="L229" s="7"/>
-      <c r="M229" s="20"/>
+      <c r="L229" s="41"/>
+      <c r="M229" s="14"/>
       <c r="N229" s="7"/>
     </row>
     <row r="230" spans="1:14" ht="15.75">
@@ -7841,16 +9744,22 @@
       <c r="C230" s="15"/>
       <c r="D230" s="12"/>
       <c r="E230" s="13"/>
-      <c r="F230" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G230" s="14"/>
+      <c r="F230" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G230" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H230" s="16"/>
-      <c r="I230" s="15"/>
-      <c r="J230" s="14"/>
+      <c r="I230" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J230" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K230" s="16"/>
-      <c r="L230" s="7"/>
-      <c r="M230" s="7"/>
+      <c r="L230" s="41"/>
+      <c r="M230" s="20"/>
       <c r="N230" s="7"/>
     </row>
     <row r="231" spans="1:14" ht="15.75">
@@ -7862,17 +9771,23 @@
       </c>
       <c r="C231" s="15"/>
       <c r="D231" s="12"/>
-      <c r="E231" s="28"/>
-      <c r="F231" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G231" s="14"/>
+      <c r="E231" s="13"/>
+      <c r="F231" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G231" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H231" s="16"/>
-      <c r="I231" s="15"/>
-      <c r="J231" s="14"/>
+      <c r="I231" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J231" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K231" s="16"/>
-      <c r="L231" s="7"/>
-      <c r="M231" s="31"/>
+      <c r="L231" s="41"/>
+      <c r="M231" s="7"/>
       <c r="N231" s="7"/>
     </row>
     <row r="232" spans="1:14" ht="15.75">
@@ -7884,17 +9799,23 @@
       </c>
       <c r="C232" s="15"/>
       <c r="D232" s="12"/>
-      <c r="E232" s="13"/>
-      <c r="F232" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G232" s="14"/>
+      <c r="E232" s="28"/>
+      <c r="F232" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G232" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H232" s="16"/>
-      <c r="I232" s="15"/>
-      <c r="J232" s="14"/>
+      <c r="I232" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J232" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K232" s="16"/>
-      <c r="L232" s="7"/>
-      <c r="M232" s="20"/>
+      <c r="L232" s="41"/>
+      <c r="M232" s="31"/>
       <c r="N232" s="7"/>
     </row>
     <row r="233" spans="1:14" ht="15.75">
@@ -7907,16 +9828,22 @@
       <c r="C233" s="15"/>
       <c r="D233" s="12"/>
       <c r="E233" s="13"/>
-      <c r="F233" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G233" s="14"/>
+      <c r="F233" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G233" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H233" s="16"/>
-      <c r="I233" s="15"/>
-      <c r="J233" s="14"/>
+      <c r="I233" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J233" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K233" s="16"/>
-      <c r="L233" s="7"/>
-      <c r="M233" s="14"/>
+      <c r="L233" s="41"/>
+      <c r="M233" s="20"/>
       <c r="N233" s="7"/>
     </row>
     <row r="234" spans="1:14" ht="15.75">
@@ -7929,16 +9856,22 @@
       <c r="C234" s="15"/>
       <c r="D234" s="12"/>
       <c r="E234" s="13"/>
-      <c r="F234" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G234" s="14"/>
+      <c r="F234" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G234" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H234" s="16"/>
-      <c r="I234" s="15"/>
-      <c r="J234" s="14"/>
+      <c r="I234" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J234" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K234" s="16"/>
-      <c r="L234" s="7"/>
-      <c r="M234" s="20"/>
+      <c r="L234" s="41"/>
+      <c r="M234" s="14"/>
       <c r="N234" s="7"/>
     </row>
     <row r="235" spans="1:14" ht="15.75">
@@ -7951,15 +9884,21 @@
       <c r="C235" s="15"/>
       <c r="D235" s="12"/>
       <c r="E235" s="13"/>
-      <c r="F235" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G235" s="14"/>
+      <c r="F235" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G235" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H235" s="16"/>
-      <c r="I235" s="15"/>
-      <c r="J235" s="14"/>
+      <c r="I235" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J235" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K235" s="16"/>
-      <c r="L235" s="7"/>
+      <c r="L235" s="41"/>
       <c r="M235" s="20"/>
       <c r="N235" s="7"/>
     </row>
@@ -7973,15 +9912,21 @@
       <c r="C236" s="15"/>
       <c r="D236" s="12"/>
       <c r="E236" s="13"/>
-      <c r="F236" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G236" s="14"/>
+      <c r="F236" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G236" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H236" s="16"/>
-      <c r="I236" s="15"/>
-      <c r="J236" s="14"/>
+      <c r="I236" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J236" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K236" s="16"/>
-      <c r="L236" s="7"/>
+      <c r="L236" s="41"/>
       <c r="M236" s="20"/>
       <c r="N236" s="7"/>
     </row>
@@ -7995,16 +9940,22 @@
       <c r="C237" s="15"/>
       <c r="D237" s="12"/>
       <c r="E237" s="13"/>
-      <c r="F237" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G237" s="14"/>
+      <c r="F237" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G237" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H237" s="16"/>
-      <c r="I237" s="15"/>
-      <c r="J237" s="14"/>
+      <c r="I237" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J237" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K237" s="16"/>
-      <c r="L237" s="7"/>
-      <c r="M237" s="14"/>
+      <c r="L237" s="41"/>
+      <c r="M237" s="20"/>
       <c r="N237" s="7"/>
     </row>
     <row r="238" spans="1:14" ht="15.75">
@@ -8017,16 +9968,22 @@
       <c r="C238" s="15"/>
       <c r="D238" s="12"/>
       <c r="E238" s="13"/>
-      <c r="F238" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G238" s="14"/>
+      <c r="F238" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G238" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H238" s="16"/>
-      <c r="I238" s="15"/>
-      <c r="J238" s="14"/>
+      <c r="I238" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J238" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K238" s="16"/>
-      <c r="L238" s="7"/>
-      <c r="M238" s="20"/>
+      <c r="L238" s="41"/>
+      <c r="M238" s="14"/>
       <c r="N238" s="7"/>
     </row>
     <row r="239" spans="1:14" ht="15.75">
@@ -8039,15 +9996,21 @@
       <c r="C239" s="15"/>
       <c r="D239" s="12"/>
       <c r="E239" s="13"/>
-      <c r="F239" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G239" s="14"/>
+      <c r="F239" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G239" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H239" s="16"/>
-      <c r="I239" s="15"/>
-      <c r="J239" s="14"/>
+      <c r="I239" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J239" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K239" s="16"/>
-      <c r="L239" s="7"/>
+      <c r="L239" s="41"/>
       <c r="M239" s="20"/>
       <c r="N239" s="7"/>
     </row>
@@ -8061,15 +10024,21 @@
       <c r="C240" s="15"/>
       <c r="D240" s="12"/>
       <c r="E240" s="13"/>
-      <c r="F240" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G240" s="14"/>
+      <c r="F240" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G240" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H240" s="16"/>
-      <c r="I240" s="15"/>
-      <c r="J240" s="14"/>
+      <c r="I240" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J240" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K240" s="16"/>
-      <c r="L240" s="7"/>
+      <c r="L240" s="41"/>
       <c r="M240" s="20"/>
       <c r="N240" s="7"/>
     </row>
@@ -8083,15 +10052,21 @@
       <c r="C241" s="15"/>
       <c r="D241" s="12"/>
       <c r="E241" s="13"/>
-      <c r="F241" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G241" s="14"/>
+      <c r="F241" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G241" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H241" s="16"/>
-      <c r="I241" s="15"/>
-      <c r="J241" s="14"/>
+      <c r="I241" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J241" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K241" s="16"/>
-      <c r="L241" s="7"/>
+      <c r="L241" s="41"/>
       <c r="M241" s="20"/>
       <c r="N241" s="7"/>
     </row>
@@ -8105,16 +10080,22 @@
       <c r="C242" s="15"/>
       <c r="D242" s="12"/>
       <c r="E242" s="13"/>
-      <c r="F242" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G242" s="14"/>
+      <c r="F242" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G242" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H242" s="16"/>
-      <c r="I242" s="15"/>
-      <c r="J242" s="14"/>
+      <c r="I242" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J242" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K242" s="16"/>
-      <c r="L242" s="7"/>
-      <c r="M242" s="21"/>
+      <c r="L242" s="41"/>
+      <c r="M242" s="20"/>
       <c r="N242" s="7"/>
     </row>
     <row r="243" spans="1:14" ht="15.75">
@@ -8127,16 +10108,22 @@
       <c r="C243" s="15"/>
       <c r="D243" s="12"/>
       <c r="E243" s="13"/>
-      <c r="F243" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G243" s="14"/>
+      <c r="F243" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G243" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H243" s="16"/>
-      <c r="I243" s="15"/>
-      <c r="J243" s="14"/>
+      <c r="I243" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J243" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K243" s="16"/>
-      <c r="L243" s="7"/>
-      <c r="M243" s="20"/>
+      <c r="L243" s="41"/>
+      <c r="M243" s="21"/>
       <c r="N243" s="7"/>
     </row>
     <row r="244" spans="1:14" ht="15.75">
@@ -8149,15 +10136,21 @@
       <c r="C244" s="15"/>
       <c r="D244" s="12"/>
       <c r="E244" s="13"/>
-      <c r="F244" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G244" s="14"/>
+      <c r="F244" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G244" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H244" s="16"/>
-      <c r="I244" s="15"/>
-      <c r="J244" s="14"/>
+      <c r="I244" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J244" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K244" s="16"/>
-      <c r="L244" s="7"/>
+      <c r="L244" s="41"/>
       <c r="M244" s="20"/>
       <c r="N244" s="7"/>
     </row>
@@ -8171,16 +10164,22 @@
       <c r="C245" s="15"/>
       <c r="D245" s="12"/>
       <c r="E245" s="13"/>
-      <c r="F245" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G245" s="14"/>
+      <c r="F245" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G245" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H245" s="16"/>
-      <c r="I245" s="15"/>
-      <c r="J245" s="14"/>
+      <c r="I245" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J245" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K245" s="16"/>
-      <c r="L245" s="7"/>
-      <c r="M245" s="14"/>
+      <c r="L245" s="41"/>
+      <c r="M245" s="20"/>
       <c r="N245" s="7"/>
     </row>
     <row r="246" spans="1:14" ht="15.75">
@@ -8193,16 +10192,22 @@
       <c r="C246" s="15"/>
       <c r="D246" s="12"/>
       <c r="E246" s="13"/>
-      <c r="F246" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G246" s="14"/>
+      <c r="F246" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G246" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H246" s="16"/>
-      <c r="I246" s="15"/>
-      <c r="J246" s="14"/>
+      <c r="I246" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J246" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K246" s="16"/>
-      <c r="L246" s="7"/>
-      <c r="M246" s="7"/>
+      <c r="L246" s="41"/>
+      <c r="M246" s="14"/>
       <c r="N246" s="7"/>
     </row>
     <row r="247" spans="1:14" ht="15.75">
@@ -8215,16 +10220,22 @@
       <c r="C247" s="15"/>
       <c r="D247" s="12"/>
       <c r="E247" s="13"/>
-      <c r="F247" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G247" s="14"/>
+      <c r="F247" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G247" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H247" s="16"/>
-      <c r="I247" s="15"/>
-      <c r="J247" s="14"/>
+      <c r="I247" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J247" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K247" s="16"/>
-      <c r="L247" s="7"/>
-      <c r="M247" s="20"/>
+      <c r="L247" s="41"/>
+      <c r="M247" s="7"/>
       <c r="N247" s="7"/>
     </row>
     <row r="248" spans="1:14" ht="15.75">
@@ -8237,16 +10248,22 @@
       <c r="C248" s="15"/>
       <c r="D248" s="12"/>
       <c r="E248" s="13"/>
-      <c r="F248" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G248" s="14"/>
+      <c r="F248" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G248" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H248" s="16"/>
-      <c r="I248" s="15"/>
-      <c r="J248" s="14"/>
+      <c r="I248" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J248" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K248" s="16"/>
-      <c r="L248" s="7"/>
-      <c r="M248" s="21"/>
+      <c r="L248" s="41"/>
+      <c r="M248" s="20"/>
       <c r="N248" s="7"/>
     </row>
     <row r="249" spans="1:14" ht="15.75">
@@ -8259,16 +10276,22 @@
       <c r="C249" s="15"/>
       <c r="D249" s="12"/>
       <c r="E249" s="13"/>
-      <c r="F249" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G249" s="14"/>
+      <c r="F249" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G249" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H249" s="16"/>
-      <c r="I249" s="15"/>
-      <c r="J249" s="14"/>
+      <c r="I249" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J249" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K249" s="16"/>
-      <c r="L249" s="7"/>
-      <c r="M249" s="20"/>
+      <c r="L249" s="41"/>
+      <c r="M249" s="21"/>
       <c r="N249" s="7"/>
     </row>
     <row r="250" spans="1:14" ht="15.75">
@@ -8281,16 +10304,22 @@
       <c r="C250" s="15"/>
       <c r="D250" s="12"/>
       <c r="E250" s="13"/>
-      <c r="F250" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G250" s="14"/>
+      <c r="F250" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G250" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H250" s="16"/>
-      <c r="I250" s="15"/>
-      <c r="J250" s="14"/>
+      <c r="I250" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J250" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K250" s="16"/>
-      <c r="L250" s="7"/>
-      <c r="M250" s="21"/>
+      <c r="L250" s="41"/>
+      <c r="M250" s="20"/>
       <c r="N250" s="7"/>
     </row>
     <row r="251" spans="1:14" ht="15.75">
@@ -8303,16 +10332,22 @@
       <c r="C251" s="15"/>
       <c r="D251" s="12"/>
       <c r="E251" s="13"/>
-      <c r="F251" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G251" s="14"/>
+      <c r="F251" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G251" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H251" s="16"/>
-      <c r="I251" s="15"/>
-      <c r="J251" s="14"/>
+      <c r="I251" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J251" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K251" s="16"/>
-      <c r="L251" s="7"/>
-      <c r="M251" s="20"/>
+      <c r="L251" s="41"/>
+      <c r="M251" s="21"/>
       <c r="N251" s="7"/>
     </row>
     <row r="252" spans="1:14" ht="15.75">
@@ -8325,16 +10360,22 @@
       <c r="C252" s="15"/>
       <c r="D252" s="12"/>
       <c r="E252" s="13"/>
-      <c r="F252" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G252" s="14"/>
+      <c r="F252" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G252" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H252" s="16"/>
-      <c r="I252" s="15"/>
-      <c r="J252" s="14"/>
+      <c r="I252" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J252" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K252" s="16"/>
       <c r="L252" s="7"/>
-      <c r="M252" s="31"/>
+      <c r="M252" s="20"/>
       <c r="N252" s="7"/>
     </row>
     <row r="253" spans="1:14" ht="15.75">
@@ -8347,16 +10388,22 @@
       <c r="C253" s="15"/>
       <c r="D253" s="12"/>
       <c r="E253" s="13"/>
-      <c r="F253" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G253" s="14"/>
+      <c r="F253" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G253" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H253" s="16"/>
-      <c r="I253" s="15"/>
-      <c r="J253" s="14"/>
+      <c r="I253" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J253" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K253" s="16"/>
       <c r="L253" s="7"/>
-      <c r="M253" s="21"/>
+      <c r="M253" s="31"/>
       <c r="N253" s="7"/>
     </row>
     <row r="254" spans="1:14" ht="15.75">
@@ -8369,16 +10416,22 @@
       <c r="C254" s="15"/>
       <c r="D254" s="12"/>
       <c r="E254" s="13"/>
-      <c r="F254" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G254" s="14"/>
+      <c r="F254" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G254" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H254" s="16"/>
-      <c r="I254" s="15"/>
-      <c r="J254" s="14"/>
+      <c r="I254" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J254" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K254" s="16"/>
       <c r="L254" s="7"/>
-      <c r="M254" s="14"/>
+      <c r="M254" s="21"/>
       <c r="N254" s="7"/>
     </row>
     <row r="255" spans="1:14" ht="15.75">
@@ -8391,16 +10444,22 @@
       <c r="C255" s="15"/>
       <c r="D255" s="12"/>
       <c r="E255" s="13"/>
-      <c r="F255" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G255" s="14"/>
+      <c r="F255" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G255" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H255" s="16"/>
-      <c r="I255" s="15"/>
-      <c r="J255" s="14"/>
+      <c r="I255" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J255" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K255" s="16"/>
       <c r="L255" s="7"/>
-      <c r="M255" s="21"/>
+      <c r="M255" s="14"/>
       <c r="N255" s="7"/>
     </row>
     <row r="256" spans="1:14" ht="15.75">
@@ -8413,16 +10472,22 @@
       <c r="C256" s="15"/>
       <c r="D256" s="12"/>
       <c r="E256" s="13"/>
-      <c r="F256" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G256" s="14"/>
+      <c r="F256" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G256" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H256" s="16"/>
-      <c r="I256" s="15"/>
-      <c r="J256" s="14"/>
+      <c r="I256" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J256" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K256" s="16"/>
       <c r="L256" s="7"/>
-      <c r="M256" s="7"/>
+      <c r="M256" s="21"/>
       <c r="N256" s="7"/>
     </row>
     <row r="257" spans="1:16" ht="15.75">
@@ -8435,16 +10500,22 @@
       <c r="C257" s="15"/>
       <c r="D257" s="12"/>
       <c r="E257" s="13"/>
-      <c r="F257" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G257" s="14"/>
+      <c r="F257" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G257" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H257" s="16"/>
-      <c r="I257" s="15"/>
-      <c r="J257" s="14"/>
+      <c r="I257" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J257" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K257" s="16"/>
       <c r="L257" s="7"/>
-      <c r="M257" s="14"/>
+      <c r="M257" s="7"/>
       <c r="N257" s="7"/>
     </row>
     <row r="258" spans="1:16" ht="15.75">
@@ -8457,16 +10528,22 @@
       <c r="C258" s="15"/>
       <c r="D258" s="12"/>
       <c r="E258" s="13"/>
-      <c r="F258" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G258" s="14"/>
+      <c r="F258" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G258" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H258" s="16"/>
-      <c r="I258" s="15"/>
-      <c r="J258" s="14"/>
+      <c r="I258" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J258" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K258" s="16"/>
       <c r="L258" s="7"/>
-      <c r="M258" s="20"/>
+      <c r="M258" s="14"/>
       <c r="N258" s="7"/>
     </row>
     <row r="259" spans="1:16" ht="15.75">
@@ -8479,16 +10556,22 @@
       <c r="C259" s="15"/>
       <c r="D259" s="12"/>
       <c r="E259" s="13"/>
-      <c r="F259" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G259" s="14"/>
+      <c r="F259" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G259" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H259" s="16"/>
-      <c r="I259" s="15"/>
-      <c r="J259" s="14"/>
+      <c r="I259" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J259" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K259" s="16"/>
       <c r="L259" s="7"/>
-      <c r="M259" s="14"/>
+      <c r="M259" s="20"/>
       <c r="N259" s="7"/>
     </row>
     <row r="260" spans="1:16" ht="15.75">
@@ -8501,16 +10584,22 @@
       <c r="C260" s="15"/>
       <c r="D260" s="12"/>
       <c r="E260" s="13"/>
-      <c r="F260" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G260" s="14"/>
+      <c r="F260" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G260" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H260" s="16"/>
-      <c r="I260" s="15"/>
-      <c r="J260" s="14"/>
+      <c r="I260" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J260" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K260" s="16"/>
       <c r="L260" s="7"/>
-      <c r="M260" s="20"/>
+      <c r="M260" s="14"/>
       <c r="N260" s="7"/>
     </row>
     <row r="261" spans="1:16" ht="15.75">
@@ -8523,18 +10612,23 @@
       <c r="C261" s="15"/>
       <c r="D261" s="12"/>
       <c r="E261" s="13"/>
-      <c r="F261" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G261" s="14"/>
+      <c r="F261" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G261" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H261" s="16"/>
-      <c r="I261" s="15"/>
-      <c r="J261" s="14"/>
+      <c r="I261" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J261" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K261" s="16"/>
       <c r="L261" s="7"/>
       <c r="M261" s="20"/>
       <c r="N261" s="7"/>
-      <c r="P261" s="35"/>
     </row>
     <row r="262" spans="1:16" ht="15.75">
       <c r="A262" s="14">
@@ -8546,17 +10640,24 @@
       <c r="C262" s="15"/>
       <c r="D262" s="12"/>
       <c r="E262" s="13"/>
-      <c r="F262" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G262" s="14"/>
+      <c r="F262" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G262" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H262" s="16"/>
-      <c r="I262" s="15"/>
-      <c r="J262" s="14"/>
+      <c r="I262" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J262" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K262" s="16"/>
       <c r="L262" s="7"/>
       <c r="M262" s="20"/>
       <c r="N262" s="7"/>
+      <c r="P262" s="35"/>
     </row>
     <row r="263" spans="1:16" ht="15.75">
       <c r="A263" s="14">
@@ -8568,13 +10669,19 @@
       <c r="C263" s="15"/>
       <c r="D263" s="12"/>
       <c r="E263" s="13"/>
-      <c r="F263" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G263" s="14"/>
+      <c r="F263" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G263" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H263" s="16"/>
-      <c r="I263" s="15"/>
-      <c r="J263" s="14"/>
+      <c r="I263" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J263" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K263" s="16"/>
       <c r="L263" s="7"/>
       <c r="M263" s="20"/>
@@ -8590,17 +10697,23 @@
       <c r="C264" s="15"/>
       <c r="D264" s="12"/>
       <c r="E264" s="13"/>
-      <c r="F264" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G264" s="14"/>
+      <c r="F264" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G264" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H264" s="16"/>
-      <c r="I264" s="15"/>
-      <c r="J264" s="14"/>
+      <c r="I264" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J264" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K264" s="16"/>
       <c r="L264" s="7"/>
-      <c r="M264" s="14"/>
-      <c r="N264" s="14"/>
+      <c r="M264" s="20"/>
+      <c r="N264" s="7"/>
     </row>
     <row r="265" spans="1:16" ht="15.75">
       <c r="A265" s="14">
@@ -8612,13 +10725,19 @@
       <c r="C265" s="15"/>
       <c r="D265" s="12"/>
       <c r="E265" s="13"/>
-      <c r="F265" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G265" s="14"/>
+      <c r="F265" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G265" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H265" s="16"/>
-      <c r="I265" s="15"/>
-      <c r="J265" s="14"/>
+      <c r="I265" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J265" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K265" s="16"/>
       <c r="L265" s="7"/>
       <c r="M265" s="14"/>
@@ -8634,17 +10753,23 @@
       <c r="C266" s="15"/>
       <c r="D266" s="12"/>
       <c r="E266" s="13"/>
-      <c r="F266" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G266" s="14"/>
+      <c r="F266" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G266" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H266" s="16"/>
-      <c r="I266" s="15"/>
-      <c r="J266" s="14"/>
-      <c r="K266" s="5"/>
+      <c r="I266" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J266" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K266" s="16"/>
       <c r="L266" s="7"/>
-      <c r="M266" s="7"/>
-      <c r="N266" s="7"/>
+      <c r="M266" s="14"/>
+      <c r="N266" s="14"/>
     </row>
     <row r="267" spans="1:16" ht="15.75">
       <c r="A267" s="14">
@@ -8656,16 +10781,22 @@
       <c r="C267" s="15"/>
       <c r="D267" s="12"/>
       <c r="E267" s="13"/>
-      <c r="F267" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G267" s="14"/>
+      <c r="F267" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G267" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H267" s="16"/>
-      <c r="I267" s="15"/>
-      <c r="J267" s="14"/>
-      <c r="K267" s="16"/>
+      <c r="I267" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J267" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K267" s="5"/>
       <c r="L267" s="7"/>
-      <c r="M267" s="21"/>
+      <c r="M267" s="7"/>
       <c r="N267" s="7"/>
     </row>
     <row r="268" spans="1:16" ht="15.75">
@@ -8678,16 +10809,22 @@
       <c r="C268" s="15"/>
       <c r="D268" s="12"/>
       <c r="E268" s="13"/>
-      <c r="F268" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G268" s="14"/>
+      <c r="F268" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G268" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H268" s="16"/>
-      <c r="I268" s="15"/>
-      <c r="J268" s="14"/>
+      <c r="I268" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J268" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K268" s="16"/>
       <c r="L268" s="7"/>
-      <c r="M268" s="20"/>
+      <c r="M268" s="21"/>
       <c r="N268" s="7"/>
     </row>
     <row r="269" spans="1:16" ht="15.75">
@@ -8700,16 +10837,22 @@
       <c r="C269" s="15"/>
       <c r="D269" s="12"/>
       <c r="E269" s="13"/>
-      <c r="F269" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G269" s="14"/>
+      <c r="F269" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G269" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H269" s="16"/>
-      <c r="I269" s="15"/>
-      <c r="J269" s="14"/>
+      <c r="I269" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J269" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K269" s="16"/>
       <c r="L269" s="7"/>
-      <c r="M269" s="14"/>
+      <c r="M269" s="20"/>
       <c r="N269" s="7"/>
     </row>
     <row r="270" spans="1:16" ht="15.75">
@@ -8722,23 +10865,57 @@
       <c r="C270" s="15"/>
       <c r="D270" s="12"/>
       <c r="E270" s="13"/>
-      <c r="F270" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G270" s="14"/>
+      <c r="F270" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G270" s="44" t="s">
+        <v>321</v>
+      </c>
       <c r="H270" s="16"/>
-      <c r="I270" s="15"/>
-      <c r="J270" s="14"/>
+      <c r="I270" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J270" s="36" t="s">
+        <v>119</v>
+      </c>
       <c r="K270" s="16"/>
       <c r="L270" s="7"/>
       <c r="M270" s="14"/>
       <c r="N270" s="7"/>
     </row>
+    <row r="271" spans="1:16" ht="15.75">
+      <c r="A271" s="14">
+        <v>269</v>
+      </c>
+      <c r="B271" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C271" s="15"/>
+      <c r="D271" s="12"/>
+      <c r="E271" s="13"/>
+      <c r="F271" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G271" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="H271" s="16"/>
+      <c r="I271" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J271" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K271" s="16"/>
+      <c r="L271" s="7"/>
+      <c r="M271" s="14"/>
+      <c r="N271" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <phoneticPr fontId="20" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
@@ -8751,22 +10928,22 @@
   <conditionalFormatting sqref="C108">
     <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C109:C140">
+  <conditionalFormatting sqref="C109:C141">
     <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C141:C164">
+  <conditionalFormatting sqref="C142:C166">
     <cfRule type="duplicateValues" dxfId="4" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C217:C245">
+  <conditionalFormatting sqref="C218:C246">
     <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C246:C270">
+  <conditionalFormatting sqref="C247:C271">
     <cfRule type="duplicateValues" dxfId="2" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L125:L166 L168:L1048576 L1:L123">
+  <conditionalFormatting sqref="L169:L1048576 L126:L167 L1:L124">
     <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M120:M126 M128:M136 M138:M139 M141:M144 M146:M151 M153:M154 M156 M160:M1048576 M1:M118">
+  <conditionalFormatting sqref="M121:M127 M139:M140 M142:M145 M147:M152 M154:M155 M157 M161:M1048576 M1:M118 M129:M137">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.75" header="0.2" footer="0.3"/>
@@ -8791,7 +10968,7 @@
       </c>
       <c r="B2" s="4">
         <f>COUNTIF('All Record'!$F$2:$F$1048576,"Female")</f>
-        <v>223</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="21">
@@ -8800,7 +10977,7 @@
       </c>
       <c r="B3" s="4">
         <f>COUNTIF('All Record'!$F$2:$F$1048576,"Male")</f>
-        <v>45</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="21">
@@ -8809,7 +10986,7 @@
       </c>
       <c r="B4" s="4">
         <f>B2+B3</f>
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
